--- a/02_sources/extracted/design_handoff_professions_catalog/data/professions.xlsx
+++ b/02_sources/extracted/design_handoff_professions_catalog/data/professions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\рс\Desktop\ПРОФТРЕКЕР\ВЭБ СТУДИЯ сайты, графика, бренд\ИИ\сайт 160 карт\02_sources\extracted\design_handoff_professions_catalog\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9912F8BB-9878-4808-8CD1-9AA0AAF31478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79772DD5-35A0-4041-B1CC-2B6891D795CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1774,9 +1774,6 @@
     <t>Инженер по строительству АЭС.jpg</t>
   </si>
   <si>
-    <t>Инженер - атомщик</t>
-  </si>
-  <si>
     <t>Рассчитывает, как реактор будет работать и остывать.</t>
   </si>
   <si>
@@ -1784,9 +1781,6 @@
   </si>
   <si>
     <t>90–170 тыс ₽</t>
-  </si>
-  <si>
-    <t>Инженер - атомщик.jpg</t>
   </si>
   <si>
     <t>Специалист по обслуживанию и ремонту механического оборудования АЭС</t>
@@ -1816,9 +1810,6 @@
     <t>Специалист по обслуживанию и ремонту механического оборудования АЭС.jpg</t>
   </si>
   <si>
-    <t>Специалист в области учета и контроляядерных материалов в области атомной энергетики</t>
-  </si>
-  <si>
     <t>Считает каждый грамм ядерного материала.</t>
   </si>
   <si>
@@ -1829,9 +1820,6 @@
   </si>
   <si>
     <t>14.02.02 «Радиационная безопасность»</t>
-  </si>
-  <si>
-    <t>Специалист в области учета и контроляядерных материалов в области атомной энергетики.jpg</t>
   </si>
   <si>
     <t>Металлургия</t>
@@ -5927,6 +5915,18 @@
   </si>
   <si>
     <t>Массажист перед процедурой готовит массажный кабинет — застилает стол одноразовой простынёй, подбирает масло и валики для удобного положения конечностей пациента. Выполняет массаж по методике, назначенной врачом или фельдшером, учитывая возраст, анатомические особенности и текущее состояние здоровья пациента. Контролирует эффективность процедуры по ощущениям и реакции пациента, корректируя силу нажима и технику, если человек испытывает боль или дискомфорт. Работает с разными видами медицинского массажа — лечебным, восстановительным, для реабилитации после травмы, — и под каждый вид подбирает свою последовательность приёмов. Между сеансами обрабатывает массажный стол и меняет одноразовое бельё, соблюдая санитарные нормы кабинета. Носит свободную удобную одежду из натуральных материалов и обувь с нескользящей устойчивой подошвой — массажист много часов проводит стоя, прикладывая физическую силу к работе руками.</t>
+  </si>
+  <si>
+    <t>Инженер-атомщик</t>
+  </si>
+  <si>
+    <t>инженер-атомщик.png</t>
+  </si>
+  <si>
+    <t>Специалист в области учета и контроля ядерных материалов в области атомной энергетики</t>
+  </si>
+  <si>
+    <t>специалист-в-области-учета-и-контроля-ядерных-материалов-в-области-атомной-энергетики.png</t>
   </si>
 </sst>
 </file>
@@ -6393,10 +6393,10 @@
         <v>18</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>1385</v>
+        <v>1381</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>1386</v>
+        <v>1382</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>19</v>
@@ -6443,10 +6443,10 @@
         <v>30</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>1387</v>
+        <v>1383</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>1388</v>
+        <v>1384</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>31</v>
@@ -6493,10 +6493,10 @@
         <v>40</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>1389</v>
+        <v>1385</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>1390</v>
+        <v>1386</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>41</v>
@@ -6543,10 +6543,10 @@
         <v>48</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>1349</v>
+        <v>1345</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>1391</v>
+        <v>1387</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>49</v>
@@ -6576,7 +6576,7 @@
         <v>56</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="409.5" x14ac:dyDescent="0.25">
@@ -6593,10 +6593,10 @@
         <v>58</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>1351</v>
+        <v>1347</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>1392</v>
+        <v>1388</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>59</v>
@@ -6626,7 +6626,7 @@
         <v>65</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="362.25" x14ac:dyDescent="0.25">
@@ -6643,10 +6643,10 @@
         <v>67</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>1393</v>
+        <v>1389</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>1394</v>
+        <v>1390</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>68</v>
@@ -6676,7 +6676,7 @@
         <v>74</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -6693,10 +6693,10 @@
         <v>76</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>1395</v>
+        <v>1391</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>1396</v>
+        <v>1392</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>77</v>
@@ -6743,13 +6743,13 @@
         <v>84</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>1397</v>
+        <v>1393</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>1383</v>
+        <v>1379</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>85</v>
@@ -6764,7 +6764,7 @@
         <v>88</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>1384</v>
+        <v>1380</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>25</v>
@@ -6776,7 +6776,7 @@
         <v>89</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="409.5" x14ac:dyDescent="0.25">
@@ -6793,10 +6793,10 @@
         <v>91</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>92</v>
@@ -6843,10 +6843,10 @@
         <v>98</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>99</v>
@@ -6893,10 +6893,10 @@
         <v>107</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>108</v>
@@ -6943,10 +6943,10 @@
         <v>115</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>116</v>
@@ -6993,10 +6993,10 @@
         <v>123</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>1408</v>
+        <v>1404</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>124</v>
@@ -7043,10 +7043,10 @@
         <v>132</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>1409</v>
+        <v>1405</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>1410</v>
+        <v>1406</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>133</v>
@@ -7093,10 +7093,10 @@
         <v>142</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>1412</v>
+        <v>1408</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>143</v>
@@ -7126,7 +7126,7 @@
         <v>151</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="409.5" x14ac:dyDescent="0.25">
@@ -7143,10 +7143,10 @@
         <v>153</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>1413</v>
+        <v>1409</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>1414</v>
+        <v>1410</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>154</v>
@@ -7193,10 +7193,10 @@
         <v>163</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>1415</v>
+        <v>1411</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>1416</v>
+        <v>1412</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>164</v>
@@ -7243,10 +7243,10 @@
         <v>172</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>1417</v>
+        <v>1413</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>1418</v>
+        <v>1414</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>173</v>
@@ -7293,10 +7293,10 @@
         <v>181</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>1419</v>
+        <v>1415</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>1420</v>
+        <v>1416</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>182</v>
@@ -7343,10 +7343,10 @@
         <v>191</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>1421</v>
+        <v>1417</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>1422</v>
+        <v>1418</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>192</v>
@@ -7393,10 +7393,10 @@
         <v>201</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>1423</v>
+        <v>1419</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>1424</v>
+        <v>1420</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>202</v>
@@ -7443,10 +7443,10 @@
         <v>210</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>1425</v>
+        <v>1421</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>1426</v>
+        <v>1422</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>211</v>
@@ -7493,10 +7493,10 @@
         <v>219</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>1427</v>
+        <v>1423</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>1428</v>
+        <v>1424</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>220</v>
@@ -7543,10 +7543,10 @@
         <v>228</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>1429</v>
+        <v>1425</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>1430</v>
+        <v>1426</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>229</v>
@@ -7593,10 +7593,10 @@
         <v>235</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>1431</v>
+        <v>1427</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>1432</v>
+        <v>1428</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>236</v>
@@ -7643,10 +7643,10 @@
         <v>244</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>1433</v>
+        <v>1429</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>1434</v>
+        <v>1430</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>245</v>
@@ -7693,10 +7693,10 @@
         <v>252</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>1435</v>
+        <v>1431</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>1436</v>
+        <v>1432</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>253</v>
@@ -7743,10 +7743,10 @@
         <v>261</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>1437</v>
+        <v>1433</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>1438</v>
+        <v>1434</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>262</v>
@@ -7793,10 +7793,10 @@
         <v>269</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>1439</v>
+        <v>1435</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>1440</v>
+        <v>1436</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>270</v>
@@ -7846,7 +7846,7 @@
         <v>279</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>1441</v>
+        <v>1437</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>280</v>
@@ -7876,7 +7876,7 @@
         <v>286</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>1342</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="32" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -7893,10 +7893,10 @@
         <v>289</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>1442</v>
+        <v>1438</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>1443</v>
+        <v>1439</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>290</v>
@@ -7943,10 +7943,10 @@
         <v>298</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>1444</v>
+        <v>1440</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>1445</v>
+        <v>1441</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>299</v>
@@ -7993,10 +7993,10 @@
         <v>308</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>1446</v>
+        <v>1442</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>1447</v>
+        <v>1443</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>309</v>
@@ -8043,10 +8043,10 @@
         <v>317</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>1448</v>
+        <v>1444</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>1449</v>
+        <v>1445</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>318</v>
@@ -8093,10 +8093,10 @@
         <v>326</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>1450</v>
+        <v>1446</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>1451</v>
+        <v>1447</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>327</v>
@@ -8143,10 +8143,10 @@
         <v>336</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>1452</v>
+        <v>1448</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>1453</v>
+        <v>1449</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>337</v>
@@ -8193,10 +8193,10 @@
         <v>346</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>1454</v>
+        <v>1450</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>1455</v>
+        <v>1451</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>347</v>
@@ -8243,10 +8243,10 @@
         <v>355</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>1456</v>
+        <v>1452</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>1457</v>
+        <v>1453</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>356</v>
@@ -8293,10 +8293,10 @@
         <v>361</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>1458</v>
+        <v>1454</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>1459</v>
+        <v>1455</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>362</v>
@@ -8343,10 +8343,10 @@
         <v>370</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>1460</v>
+        <v>1456</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>1461</v>
+        <v>1457</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>371</v>
@@ -8393,10 +8393,10 @@
         <v>379</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>1462</v>
+        <v>1458</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>1463</v>
+        <v>1459</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>380</v>
@@ -8443,10 +8443,10 @@
         <v>385</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>1464</v>
+        <v>1460</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>1465</v>
+        <v>1461</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>386</v>
@@ -8487,19 +8487,19 @@
         <v>334</v>
       </c>
       <c r="C44" s="1" t="s">
+        <v>1656</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="E44" s="1" t="s">
+        <v>1462</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>1463</v>
+      </c>
+      <c r="G44" s="1" t="s">
         <v>390</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>1466</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>1467</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>391</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>387</v>
@@ -8511,7 +8511,7 @@
         <v>273</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="L44" s="1" t="s">
         <v>376</v>
@@ -8523,7 +8523,7 @@
         <v>367</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>393</v>
+        <v>1657</v>
       </c>
       <c r="P44" s="1" t="s">
         <v>28</v>
@@ -8537,28 +8537,28 @@
         <v>334</v>
       </c>
       <c r="C45" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>1464</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>1465</v>
+      </c>
+      <c r="G45" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="H45" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="E45" s="1" t="s">
-        <v>1468</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>1469</v>
-      </c>
-      <c r="G45" s="1" t="s">
+      <c r="I45" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="H45" s="1" t="s">
+      <c r="J45" s="1" t="s">
         <v>397</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="J45" s="1" t="s">
-        <v>399</v>
       </c>
       <c r="K45" s="1" t="s">
         <v>23</v>
@@ -8573,7 +8573,7 @@
         <v>367</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="P45" s="1" t="s">
         <v>28</v>
@@ -8587,22 +8587,22 @@
         <v>334</v>
       </c>
       <c r="C46" s="1" t="s">
+        <v>1658</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>1466</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>1467</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="H46" s="1" t="s">
         <v>401</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>1470</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>1471</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>404</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>349</v>
@@ -8614,7 +8614,7 @@
         <v>23</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="M46" s="1" t="s">
         <v>342</v>
@@ -8623,7 +8623,7 @@
         <v>367</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>406</v>
+        <v>1659</v>
       </c>
       <c r="P46" s="1" t="s">
         <v>28</v>
@@ -8634,46 +8634,46 @@
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>1468</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>1469</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="H47" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="I47" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="J47" s="1" t="s">
         <v>409</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>1472</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>1473</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="I47" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="J47" s="1" t="s">
-        <v>413</v>
       </c>
       <c r="K47" s="1" t="s">
         <v>23</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="P47" s="1" t="s">
         <v>28</v>
@@ -8684,46 +8684,46 @@
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C48" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>1470</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>1471</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="I48" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="J48" s="1" t="s">
         <v>419</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>1474</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>1475</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="I48" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="J48" s="1" t="s">
-        <v>423</v>
       </c>
       <c r="K48" s="1" t="s">
         <v>206</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="M48" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="P48" s="1" t="s">
         <v>28</v>
@@ -8734,46 +8734,46 @@
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C49" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>1472</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>1473</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="I49" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="J49" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="E49" s="1" t="s">
-        <v>1476</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>1477</v>
-      </c>
-      <c r="G49" s="1" t="s">
+      <c r="K49" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="H49" s="1" t="s">
+      <c r="L49" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="I49" s="1" t="s">
+      <c r="M49" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="N49" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="J49" s="1" t="s">
+      <c r="O49" s="1" t="s">
         <v>432</v>
-      </c>
-      <c r="K49" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="L49" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="M49" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="N49" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="O49" s="1" t="s">
-        <v>436</v>
       </c>
       <c r="P49" s="1" t="s">
         <v>28</v>
@@ -8784,46 +8784,46 @@
         <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C50" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>1474</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>1475</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="I50" s="1" t="s">
         <v>437</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>1478</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>1479</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="I50" s="1" t="s">
-        <v>441</v>
       </c>
       <c r="J50" s="1" t="s">
         <v>312</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="M50" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="P50" s="1" t="s">
         <v>28</v>
@@ -8834,46 +8834,46 @@
         <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>1480</v>
+        <v>1476</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>1481</v>
+        <v>1477</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="J51" s="1" t="s">
         <v>312</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="M51" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="P51" s="1" t="s">
         <v>28</v>
@@ -8884,46 +8884,46 @@
         <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C52" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>1479</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="I52" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="J52" s="1" t="s">
         <v>450</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>1482</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>1483</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="I52" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="J52" s="1" t="s">
-        <v>454</v>
       </c>
       <c r="K52" s="1" t="s">
         <v>35</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P52" s="1" t="s">
         <v>28</v>
@@ -8934,46 +8934,46 @@
         <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C53" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>1480</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>1481</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="I53" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="J53" s="1" t="s">
         <v>457</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>1484</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>1485</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="I53" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="J53" s="1" t="s">
-        <v>461</v>
       </c>
       <c r="K53" s="1" t="s">
         <v>63</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="M53" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="P53" s="1" t="s">
         <v>28</v>
@@ -8984,46 +8984,46 @@
         <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C54" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="H54" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="I54" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="J54" s="1" t="s">
         <v>466</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>1486</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="I54" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="J54" s="1" t="s">
-        <v>470</v>
       </c>
       <c r="K54" s="1" t="s">
         <v>81</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="P54" s="1" t="s">
         <v>28</v>
@@ -9034,46 +9034,46 @@
         <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C55" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>1484</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="I55" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="J55" s="1" t="s">
         <v>474</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>1487</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>1488</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="I55" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="J55" s="1" t="s">
-        <v>478</v>
       </c>
       <c r="K55" s="1" t="s">
         <v>53</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="P55" s="1" t="s">
         <v>28</v>
@@ -9084,46 +9084,46 @@
         <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C56" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>1485</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>1486</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="I56" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="J56" s="1" t="s">
         <v>482</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>1489</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>1490</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="I56" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="J56" s="1" t="s">
-        <v>486</v>
       </c>
       <c r="K56" s="1" t="s">
         <v>53</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="O56" s="1" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="P56" s="1" t="s">
         <v>28</v>
@@ -9134,46 +9134,46 @@
         <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>1487</v>
+      </c>
+      <c r="G57" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="H57" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="I57" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="E57" s="1" t="s">
+      <c r="J57" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="K57" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="F57" s="1" t="s">
-        <v>1491</v>
-      </c>
-      <c r="G57" s="1" t="s">
+      <c r="L57" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="H57" s="1" t="s">
+      <c r="M57" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="I57" s="1" t="s">
+      <c r="N57" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="J57" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="K57" s="1" t="s">
+      <c r="O57" s="1" t="s">
         <v>495</v>
-      </c>
-      <c r="L57" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="M57" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="N57" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="O57" s="1" t="s">
-        <v>499</v>
       </c>
       <c r="P57" s="1" t="s">
         <v>28</v>
@@ -9184,28 +9184,28 @@
         <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="C58" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>1488</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>1489</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="I58" s="1" t="s">
         <v>500</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>1492</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>1493</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="H58" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="I58" s="1" t="s">
-        <v>504</v>
       </c>
       <c r="J58" s="1" t="s">
         <v>239</v>
@@ -9214,16 +9214,16 @@
         <v>206</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="M58" s="1" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="P58" s="1" t="s">
         <v>28</v>
@@ -9234,46 +9234,46 @@
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="C59" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>1491</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="I59" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="J59" s="1" t="s">
         <v>509</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>1494</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>1495</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="I59" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="J59" s="1" t="s">
-        <v>513</v>
       </c>
       <c r="K59" s="1" t="s">
         <v>206</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="M59" s="1" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="P59" s="1" t="s">
         <v>28</v>
@@ -9284,46 +9284,46 @@
         <v>59</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>1497</v>
+        <v>1493</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="J60" s="1" t="s">
         <v>239</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="L60" s="1" t="s">
         <v>382</v>
       </c>
       <c r="M60" s="1" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="O60" s="1" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="P60" s="1" t="s">
         <v>28</v>
@@ -9334,46 +9334,46 @@
         <v>60</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="C61" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>1494</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>1495</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="I61" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="J61" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="K61" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="E61" s="1" t="s">
-        <v>1498</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>1499</v>
-      </c>
-      <c r="G61" s="1" t="s">
+      <c r="L61" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="M61" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="N61" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="O61" s="1" t="s">
         <v>525</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="I61" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="J61" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="L61" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="M61" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="N61" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="O61" s="1" t="s">
-        <v>529</v>
       </c>
       <c r="P61" s="1" t="s">
         <v>28</v>
@@ -9384,46 +9384,46 @@
         <v>61</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="C62" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>1496</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>1497</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="I62" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="J62" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="L62" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="M62" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="N62" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="O62" s="1" t="s">
         <v>531</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>1500</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>1501</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="H62" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="I62" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="J62" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="K62" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="L62" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="M62" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="N62" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="O62" s="1" t="s">
-        <v>535</v>
       </c>
       <c r="P62" s="1" t="s">
         <v>28</v>
@@ -9434,46 +9434,46 @@
         <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="C63" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>1498</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>1499</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="I63" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="J63" s="1" t="s">
         <v>537</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>1502</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>1503</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>538</v>
-      </c>
-      <c r="H63" s="1" t="s">
-        <v>539</v>
-      </c>
-      <c r="I63" s="1" t="s">
-        <v>540</v>
-      </c>
-      <c r="J63" s="1" t="s">
-        <v>541</v>
       </c>
       <c r="K63" s="1" t="s">
         <v>274</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="M63" s="1" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="N63" s="1" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="O63" s="1" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="P63" s="1" t="s">
         <v>28</v>
@@ -9484,46 +9484,46 @@
         <v>63</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="C64" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>1500</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>1501</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="I64" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="J64" s="1" t="s">
         <v>545</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>1504</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>1505</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="I64" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="J64" s="1" t="s">
-        <v>549</v>
       </c>
       <c r="K64" s="1" t="s">
         <v>35</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="M64" s="1" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="N64" s="1" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="O64" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="P64" s="1" t="s">
         <v>28</v>
@@ -9534,46 +9534,46 @@
         <v>64</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="C65" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>1502</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>1503</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="I65" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="D65" s="1" t="s">
+      <c r="J65" s="1" t="s">
         <v>553</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>1506</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>1507</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="H65" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="I65" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="J65" s="1" t="s">
-        <v>557</v>
       </c>
       <c r="K65" s="1" t="s">
         <v>23</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="M65" s="1" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="N65" s="1" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="O65" s="1" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="P65" s="1" t="s">
         <v>28</v>
@@ -9584,46 +9584,46 @@
         <v>65</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="C66" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>1504</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>1505</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="I66" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="D66" s="1" t="s">
+      <c r="J66" s="1" t="s">
         <v>561</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>1508</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>1509</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="H66" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="I66" s="1" t="s">
-        <v>564</v>
-      </c>
-      <c r="J66" s="1" t="s">
-        <v>565</v>
       </c>
       <c r="K66" s="1" t="s">
         <v>274</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="M66" s="1" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="O66" s="1" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="P66" s="1" t="s">
         <v>28</v>
@@ -9634,46 +9634,46 @@
         <v>66</v>
       </c>
       <c r="B67" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>1506</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>1507</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="H67" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="I67" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="J67" s="1" t="s">
         <v>570</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>1510</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>1511</v>
-      </c>
-      <c r="G67" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="H67" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="I67" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="J67" s="1" t="s">
-        <v>574</v>
       </c>
       <c r="K67" s="1" t="s">
         <v>331</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="M67" s="1" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="O67" s="1" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="P67" s="1" t="s">
         <v>28</v>
@@ -9684,46 +9684,46 @@
         <v>67</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="C68" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>1508</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>1509</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="I68" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="D68" s="1" t="s">
+      <c r="J68" s="1" t="s">
         <v>580</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>1512</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>1513</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="H68" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="I68" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="J68" s="1" t="s">
-        <v>584</v>
       </c>
       <c r="K68" s="1" t="s">
         <v>23</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="M68" s="1" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="O68" s="1" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="P68" s="1" t="s">
         <v>28</v>
@@ -9734,46 +9734,46 @@
         <v>68</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="C69" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>1510</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>1511</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="I69" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="D69" s="1" t="s">
+      <c r="J69" s="1" t="s">
         <v>589</v>
       </c>
-      <c r="E69" s="1" t="s">
-        <v>1514</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>1515</v>
-      </c>
-      <c r="G69" s="1" t="s">
+      <c r="K69" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="L69" s="1" t="s">
         <v>590</v>
       </c>
-      <c r="H69" s="1" t="s">
+      <c r="M69" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="N69" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="I69" s="1" t="s">
+      <c r="O69" s="1" t="s">
         <v>592</v>
-      </c>
-      <c r="J69" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="K69" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="L69" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="M69" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="N69" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="O69" s="1" t="s">
-        <v>596</v>
       </c>
       <c r="P69" s="1" t="s">
         <v>28</v>
@@ -9784,46 +9784,46 @@
         <v>69</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="C70" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>1512</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>1513</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="I70" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="D70" s="1" t="s">
+      <c r="J70" s="1" t="s">
         <v>598</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>1516</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>1517</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>599</v>
-      </c>
-      <c r="H70" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="I70" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="J70" s="1" t="s">
-        <v>602</v>
       </c>
       <c r="K70" s="1" t="s">
         <v>103</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="M70" s="1" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="O70" s="1" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="P70" s="1" t="s">
         <v>28</v>
@@ -9834,46 +9834,46 @@
         <v>70</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="C71" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>1515</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="I71" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="D71" s="1" t="s">
+      <c r="J71" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="E71" s="1" t="s">
-        <v>1518</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>1519</v>
-      </c>
-      <c r="G71" s="1" t="s">
+      <c r="K71" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="L71" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="H71" s="1" t="s">
+      <c r="M71" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="N71" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="O71" s="1" t="s">
         <v>609</v>
-      </c>
-      <c r="I71" s="1" t="s">
-        <v>610</v>
-      </c>
-      <c r="J71" s="1" t="s">
-        <v>611</v>
-      </c>
-      <c r="K71" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="L71" s="1" t="s">
-        <v>612</v>
-      </c>
-      <c r="M71" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="N71" s="1" t="s">
-        <v>604</v>
-      </c>
-      <c r="O71" s="1" t="s">
-        <v>613</v>
       </c>
       <c r="P71" s="1" t="s">
         <v>28</v>
@@ -9884,46 +9884,46 @@
         <v>71</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="C72" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>1516</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>1517</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="I72" s="1" t="s">
         <v>614</v>
       </c>
-      <c r="D72" s="1" t="s">
+      <c r="J72" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="E72" s="1" t="s">
-        <v>1520</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>1521</v>
-      </c>
-      <c r="G72" s="1" t="s">
+      <c r="K72" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="L72" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="M72" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="N72" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="O72" s="1" t="s">
         <v>616</v>
-      </c>
-      <c r="H72" s="1" t="s">
-        <v>617</v>
-      </c>
-      <c r="I72" s="1" t="s">
-        <v>618</v>
-      </c>
-      <c r="J72" s="1" t="s">
-        <v>619</v>
-      </c>
-      <c r="K72" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="L72" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="M72" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="N72" s="1" t="s">
-        <v>604</v>
-      </c>
-      <c r="O72" s="1" t="s">
-        <v>620</v>
       </c>
       <c r="P72" s="1" t="s">
         <v>28</v>
@@ -9934,46 +9934,46 @@
         <v>72</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="C73" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>1518</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>1519</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="I73" s="1" t="s">
         <v>621</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>622</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>1522</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>1523</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>623</v>
-      </c>
-      <c r="H73" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="I73" s="1" t="s">
-        <v>625</v>
       </c>
       <c r="J73" s="1" t="s">
         <v>239</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="M73" s="1" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="N73" s="1" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="O73" s="1" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="P73" s="1" t="s">
         <v>28</v>
@@ -9984,46 +9984,46 @@
         <v>73</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="C74" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>1520</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>1521</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="I74" s="1" t="s">
         <v>629</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>630</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>1524</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>1525</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="H74" s="1" t="s">
-        <v>632</v>
-      </c>
-      <c r="I74" s="1" t="s">
-        <v>633</v>
       </c>
       <c r="J74" s="1" t="s">
         <v>239</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="M74" s="1" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="N74" s="1" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="P74" s="1" t="s">
         <v>28</v>
@@ -10034,49 +10034,49 @@
         <v>74</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="D75" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>1522</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>1523</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>1373</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>1374</v>
+      </c>
+      <c r="J75" s="1" t="s">
+        <v>1375</v>
+      </c>
+      <c r="K75" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="L75" s="1" t="s">
+        <v>1376</v>
+      </c>
+      <c r="M75" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="N75" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="O75" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="E75" s="1" t="s">
-        <v>1526</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>1527</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>1377</v>
-      </c>
-      <c r="H75" s="1" t="s">
-        <v>639</v>
-      </c>
-      <c r="I75" s="1" t="s">
-        <v>1378</v>
-      </c>
-      <c r="J75" s="1" t="s">
-        <v>1379</v>
-      </c>
-      <c r="K75" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="L75" s="1" t="s">
-        <v>1380</v>
-      </c>
-      <c r="M75" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="N75" s="1" t="s">
-        <v>604</v>
-      </c>
-      <c r="O75" s="1" t="s">
-        <v>642</v>
-      </c>
       <c r="P75" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="76" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -10084,46 +10084,46 @@
         <v>75</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>1528</v>
+        <v>1524</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>1529</v>
+        <v>1525</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="K76" s="1" t="s">
         <v>206</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="M76" s="1" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="N76" s="1" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="O76" s="1" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="P76" s="1" t="s">
         <v>28</v>
@@ -10134,46 +10134,46 @@
         <v>76</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="C77" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>1526</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>1527</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="J77" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="L77" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="D77" s="1" t="s">
+      <c r="M77" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="N77" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="O77" s="1" t="s">
         <v>649</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>1530</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>1531</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>650</v>
-      </c>
-      <c r="H77" s="1" t="s">
-        <v>639</v>
-      </c>
-      <c r="I77" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="J77" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="K77" s="1" t="s">
-        <v>651</v>
-      </c>
-      <c r="L77" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="M77" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="N77" s="1" t="s">
-        <v>604</v>
-      </c>
-      <c r="O77" s="1" t="s">
-        <v>653</v>
       </c>
       <c r="P77" s="1" t="s">
         <v>28</v>
@@ -10184,49 +10184,49 @@
         <v>77</v>
       </c>
       <c r="B78" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>1348</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>1528</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="H78" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="I78" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="D78" s="1" t="s">
+      <c r="J78" s="1" t="s">
         <v>656</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>1352</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>1532</v>
-      </c>
-      <c r="G78" s="1" t="s">
-        <v>657</v>
-      </c>
-      <c r="H78" s="1" t="s">
-        <v>658</v>
-      </c>
-      <c r="I78" s="1" t="s">
-        <v>659</v>
-      </c>
-      <c r="J78" s="1" t="s">
-        <v>660</v>
       </c>
       <c r="K78" s="1" t="s">
         <v>274</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="M78" s="1" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="N78" s="1" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="O78" s="1" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="P78" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="79" spans="1:16" ht="252" x14ac:dyDescent="0.25">
@@ -10234,49 +10234,49 @@
         <v>78</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="C79" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>1529</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="I79" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="D79" s="1" t="s">
+      <c r="J79" s="1" t="s">
         <v>666</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>1353</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>1533</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>667</v>
-      </c>
-      <c r="H79" s="1" t="s">
-        <v>668</v>
-      </c>
-      <c r="I79" s="1" t="s">
-        <v>669</v>
-      </c>
-      <c r="J79" s="1" t="s">
-        <v>670</v>
       </c>
       <c r="K79" s="1" t="s">
         <v>274</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="M79" s="1" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="N79" s="1" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="P79" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="80" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -10284,49 +10284,49 @@
         <v>79</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="C80" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>1350</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>1530</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="I80" s="1" t="s">
         <v>674</v>
       </c>
-      <c r="D80" s="1" t="s">
+      <c r="J80" s="1" t="s">
         <v>675</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>1354</v>
-      </c>
-      <c r="F80" s="1" t="s">
-        <v>1534</v>
-      </c>
-      <c r="G80" s="1" t="s">
-        <v>676</v>
-      </c>
-      <c r="H80" s="1" t="s">
-        <v>677</v>
-      </c>
-      <c r="I80" s="1" t="s">
-        <v>678</v>
-      </c>
-      <c r="J80" s="1" t="s">
-        <v>679</v>
       </c>
       <c r="K80" s="1" t="s">
         <v>53</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="M80" s="1" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="N80" s="1" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="O80" s="1" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="P80" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="81" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -10334,49 +10334,49 @@
         <v>80</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>1381</v>
+        <v>1377</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>1535</v>
+        <v>1531</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="K81" s="1" t="s">
         <v>53</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>1382</v>
+        <v>1378</v>
       </c>
       <c r="M81" s="1" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="N81" s="1" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="O81" s="1" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="P81" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="82" spans="1:16" ht="267.75" x14ac:dyDescent="0.25">
@@ -10384,49 +10384,49 @@
         <v>81</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="C82" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>1532</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>1533</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="I82" s="1" t="s">
         <v>689</v>
       </c>
-      <c r="D82" s="1" t="s">
+      <c r="J82" s="1" t="s">
         <v>690</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>1536</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>1537</v>
-      </c>
-      <c r="G82" s="1" t="s">
-        <v>691</v>
-      </c>
-      <c r="H82" s="1" t="s">
-        <v>692</v>
-      </c>
-      <c r="I82" s="1" t="s">
-        <v>693</v>
-      </c>
-      <c r="J82" s="1" t="s">
-        <v>694</v>
       </c>
       <c r="K82" s="1" t="s">
         <v>206</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="M82" s="1" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="N82" s="1" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="O82" s="1" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="P82" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="83" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -10434,49 +10434,49 @@
         <v>82</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="C83" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>1534</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>1535</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="I83" s="1" t="s">
         <v>697</v>
       </c>
-      <c r="D83" s="1" t="s">
-        <v>698</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>1538</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>1539</v>
-      </c>
-      <c r="G83" s="1" t="s">
-        <v>699</v>
-      </c>
-      <c r="H83" s="1" t="s">
-        <v>700</v>
-      </c>
-      <c r="I83" s="1" t="s">
-        <v>701</v>
-      </c>
       <c r="J83" s="1" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="K83" s="1" t="s">
         <v>23</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="M83" s="1" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="N83" s="1" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="O83" s="1" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="P83" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="84" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -10484,46 +10484,46 @@
         <v>83</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="C84" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>1536</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>1537</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="I84" s="1" t="s">
         <v>703</v>
       </c>
-      <c r="D84" s="1" t="s">
+      <c r="J84" s="1" t="s">
         <v>704</v>
       </c>
-      <c r="E84" s="1" t="s">
-        <v>1540</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>1541</v>
-      </c>
-      <c r="G84" s="1" t="s">
+      <c r="K84" s="1" t="s">
         <v>705</v>
       </c>
-      <c r="H84" s="1" t="s">
+      <c r="L84" s="1" t="s">
         <v>706</v>
       </c>
-      <c r="I84" s="1" t="s">
+      <c r="M84" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="N84" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="O84" s="1" t="s">
         <v>707</v>
-      </c>
-      <c r="J84" s="1" t="s">
-        <v>708</v>
-      </c>
-      <c r="K84" s="1" t="s">
-        <v>709</v>
-      </c>
-      <c r="L84" s="1" t="s">
-        <v>710</v>
-      </c>
-      <c r="M84" s="1" t="s">
-        <v>662</v>
-      </c>
-      <c r="N84" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="O84" s="1" t="s">
-        <v>711</v>
       </c>
       <c r="P84" s="1" t="s">
         <v>28</v>
@@ -10534,49 +10534,49 @@
         <v>84</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="C85" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>1538</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>1539</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="I85" s="1" t="s">
         <v>712</v>
       </c>
-      <c r="D85" s="1" t="s">
-        <v>713</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>1542</v>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>1543</v>
-      </c>
-      <c r="G85" s="1" t="s">
-        <v>714</v>
-      </c>
-      <c r="H85" s="1" t="s">
-        <v>715</v>
-      </c>
-      <c r="I85" s="1" t="s">
-        <v>716</v>
-      </c>
       <c r="J85" s="1" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="K85" s="1" t="s">
         <v>23</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="M85" s="1" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="N85" s="1" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="O85" s="1" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="P85" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="86" spans="1:16" ht="409.5" x14ac:dyDescent="0.25">
@@ -10584,31 +10584,31 @@
         <v>85</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="C86" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>1540</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>1541</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="I86" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="D86" s="1" t="s">
+      <c r="J86" s="1" t="s">
         <v>720</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>1544</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>1545</v>
-      </c>
-      <c r="G86" s="1" t="s">
-        <v>721</v>
-      </c>
-      <c r="H86" s="1" t="s">
-        <v>722</v>
-      </c>
-      <c r="I86" s="1" t="s">
-        <v>723</v>
-      </c>
-      <c r="J86" s="1" t="s">
-        <v>724</v>
       </c>
       <c r="K86" s="1" t="s">
         <v>35</v>
@@ -10617,16 +10617,16 @@
         <v>366</v>
       </c>
       <c r="M86" s="1" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="N86" s="1" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="O86" s="1" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="P86" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="87" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -10634,28 +10634,28 @@
         <v>86</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="C87" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>1542</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>1543</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="I87" s="1" t="s">
         <v>726</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>727</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>1546</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>1547</v>
-      </c>
-      <c r="G87" s="1" t="s">
-        <v>728</v>
-      </c>
-      <c r="H87" s="1" t="s">
-        <v>729</v>
-      </c>
-      <c r="I87" s="1" t="s">
-        <v>730</v>
       </c>
       <c r="J87" s="1" t="s">
         <v>167</v>
@@ -10664,19 +10664,19 @@
         <v>158</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="M87" s="1" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="N87" s="1" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="O87" s="1" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="P87" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="88" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -10684,49 +10684,49 @@
         <v>87</v>
       </c>
       <c r="B88" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>1544</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>1545</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>1351</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="I88" s="1" t="s">
         <v>733</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="J88" s="1" t="s">
         <v>734</v>
       </c>
-      <c r="D88" s="1" t="s">
+      <c r="K88" s="1" t="s">
         <v>735</v>
       </c>
-      <c r="E88" s="1" t="s">
-        <v>1548</v>
-      </c>
-      <c r="F88" s="1" t="s">
-        <v>1549</v>
-      </c>
-      <c r="G88" s="1" t="s">
-        <v>1355</v>
-      </c>
-      <c r="H88" s="1" t="s">
+      <c r="L88" s="1" t="s">
         <v>736</v>
       </c>
-      <c r="I88" s="1" t="s">
+      <c r="M88" s="1" t="s">
         <v>737</v>
       </c>
-      <c r="J88" s="1" t="s">
+      <c r="N88" s="1" t="s">
         <v>738</v>
       </c>
-      <c r="K88" s="1" t="s">
+      <c r="O88" s="1" t="s">
         <v>739</v>
       </c>
-      <c r="L88" s="1" t="s">
-        <v>740</v>
-      </c>
-      <c r="M88" s="1" t="s">
-        <v>741</v>
-      </c>
-      <c r="N88" s="1" t="s">
-        <v>742</v>
-      </c>
-      <c r="O88" s="1" t="s">
-        <v>743</v>
-      </c>
       <c r="P88" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="89" spans="1:16" ht="252" x14ac:dyDescent="0.25">
@@ -10734,49 +10734,49 @@
         <v>88</v>
       </c>
       <c r="B89" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>1325</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>1546</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>1328</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="I89" s="1" t="s">
         <v>733</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="J89" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="K89" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="L89" s="1" t="s">
+        <v>1327</v>
+      </c>
+      <c r="M89" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="N89" s="1" t="s">
         <v>744</v>
       </c>
-      <c r="D89" s="1" t="s">
+      <c r="O89" s="1" t="s">
         <v>745</v>
       </c>
-      <c r="E89" s="1" t="s">
-        <v>1329</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>1550</v>
-      </c>
-      <c r="G89" s="1" t="s">
-        <v>1332</v>
-      </c>
-      <c r="H89" s="1" t="s">
-        <v>736</v>
-      </c>
-      <c r="I89" s="1" t="s">
-        <v>737</v>
-      </c>
-      <c r="J89" s="1" t="s">
-        <v>738</v>
-      </c>
-      <c r="K89" s="1" t="s">
-        <v>747</v>
-      </c>
-      <c r="L89" s="1" t="s">
-        <v>1331</v>
-      </c>
-      <c r="M89" s="1" t="s">
-        <v>741</v>
-      </c>
-      <c r="N89" s="1" t="s">
-        <v>748</v>
-      </c>
-      <c r="O89" s="1" t="s">
-        <v>749</v>
-      </c>
       <c r="P89" s="1" t="s">
-        <v>1330</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="90" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -10784,49 +10784,49 @@
         <v>89</v>
       </c>
       <c r="B90" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>1547</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>1548</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="I90" s="1" t="s">
         <v>733</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="J90" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="K90" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="L90" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="M90" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="N90" s="1" t="s">
         <v>750</v>
       </c>
-      <c r="D90" s="1" t="s">
+      <c r="O90" s="1" t="s">
         <v>751</v>
       </c>
-      <c r="E90" s="1" t="s">
-        <v>1551</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>1552</v>
-      </c>
-      <c r="G90" s="1" t="s">
-        <v>746</v>
-      </c>
-      <c r="H90" s="1" t="s">
-        <v>736</v>
-      </c>
-      <c r="I90" s="1" t="s">
-        <v>737</v>
-      </c>
-      <c r="J90" s="1" t="s">
-        <v>738</v>
-      </c>
-      <c r="K90" s="1" t="s">
-        <v>752</v>
-      </c>
-      <c r="L90" s="1" t="s">
-        <v>753</v>
-      </c>
-      <c r="M90" s="1" t="s">
-        <v>741</v>
-      </c>
-      <c r="N90" s="1" t="s">
-        <v>754</v>
-      </c>
-      <c r="O90" s="1" t="s">
-        <v>755</v>
-      </c>
       <c r="P90" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="91" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -10834,49 +10834,49 @@
         <v>90</v>
       </c>
       <c r="B91" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>1549</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>1550</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>1352</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="I91" s="1" t="s">
         <v>733</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="J91" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="L91" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="M91" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="N91" s="1" t="s">
         <v>756</v>
       </c>
-      <c r="D91" s="1" t="s">
+      <c r="O91" s="1" t="s">
         <v>757</v>
       </c>
-      <c r="E91" s="1" t="s">
-        <v>1553</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>1554</v>
-      </c>
-      <c r="G91" s="1" t="s">
-        <v>1356</v>
-      </c>
-      <c r="H91" s="1" t="s">
-        <v>736</v>
-      </c>
-      <c r="I91" s="1" t="s">
-        <v>737</v>
-      </c>
-      <c r="J91" s="1" t="s">
-        <v>738</v>
-      </c>
-      <c r="K91" s="1" t="s">
-        <v>758</v>
-      </c>
-      <c r="L91" s="1" t="s">
-        <v>759</v>
-      </c>
-      <c r="M91" s="1" t="s">
-        <v>741</v>
-      </c>
-      <c r="N91" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="O91" s="1" t="s">
-        <v>761</v>
-      </c>
       <c r="P91" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="92" spans="1:16" ht="252" x14ac:dyDescent="0.25">
@@ -10884,46 +10884,46 @@
         <v>91</v>
       </c>
       <c r="B92" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>1551</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>1552</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="I92" s="1" t="s">
         <v>733</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="J92" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="L92" s="1" t="s">
         <v>762</v>
       </c>
-      <c r="D92" s="1" t="s">
+      <c r="M92" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="N92" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="O92" s="1" t="s">
         <v>763</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>1555</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>1556</v>
-      </c>
-      <c r="G92" s="1" t="s">
-        <v>764</v>
-      </c>
-      <c r="H92" s="1" t="s">
-        <v>736</v>
-      </c>
-      <c r="I92" s="1" t="s">
-        <v>737</v>
-      </c>
-      <c r="J92" s="1" t="s">
-        <v>738</v>
-      </c>
-      <c r="K92" s="1" t="s">
-        <v>765</v>
-      </c>
-      <c r="L92" s="1" t="s">
-        <v>766</v>
-      </c>
-      <c r="M92" s="1" t="s">
-        <v>741</v>
-      </c>
-      <c r="N92" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="O92" s="1" t="s">
-        <v>767</v>
       </c>
       <c r="P92" s="1" t="s">
         <v>28</v>
@@ -10934,46 +10934,46 @@
         <v>92</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="C93" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>1553</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>1554</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="I93" s="1" t="s">
         <v>768</v>
       </c>
-      <c r="D93" s="1" t="s">
+      <c r="J93" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="L93" s="1" t="s">
         <v>769</v>
       </c>
-      <c r="E93" s="1" t="s">
-        <v>1557</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>1558</v>
-      </c>
-      <c r="G93" s="1" t="s">
+      <c r="M93" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="N93" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="O93" s="1" t="s">
         <v>770</v>
-      </c>
-      <c r="H93" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="I93" s="1" t="s">
-        <v>772</v>
-      </c>
-      <c r="J93" s="1" t="s">
-        <v>738</v>
-      </c>
-      <c r="K93" s="1" t="s">
-        <v>765</v>
-      </c>
-      <c r="L93" s="1" t="s">
-        <v>773</v>
-      </c>
-      <c r="M93" s="1" t="s">
-        <v>741</v>
-      </c>
-      <c r="N93" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="O93" s="1" t="s">
-        <v>774</v>
       </c>
       <c r="P93" s="1" t="s">
         <v>28</v>
@@ -10984,49 +10984,49 @@
         <v>93</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="C94" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>1329</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>1555</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>1331</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="J94" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="K94" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="L94" s="1" t="s">
+        <v>1330</v>
+      </c>
+      <c r="M94" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="N94" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="O94" s="1" t="s">
         <v>775</v>
       </c>
-      <c r="D94" s="1" t="s">
-        <v>776</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>1333</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>1559</v>
-      </c>
-      <c r="G94" s="1" t="s">
-        <v>1335</v>
-      </c>
-      <c r="H94" s="1" t="s">
-        <v>777</v>
-      </c>
-      <c r="I94" s="1" t="s">
-        <v>772</v>
-      </c>
-      <c r="J94" s="1" t="s">
-        <v>738</v>
-      </c>
-      <c r="K94" s="1" t="s">
-        <v>778</v>
-      </c>
-      <c r="L94" s="1" t="s">
-        <v>1334</v>
-      </c>
-      <c r="M94" s="1" t="s">
-        <v>741</v>
-      </c>
-      <c r="N94" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="O94" s="1" t="s">
-        <v>779</v>
-      </c>
       <c r="P94" s="1" t="s">
-        <v>1330</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="95" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -11034,46 +11034,46 @@
         <v>94</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="C95" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>1556</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>1557</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="J95" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="K95" s="1" t="s">
         <v>780</v>
       </c>
-      <c r="D95" s="1" t="s">
+      <c r="L95" s="1" t="s">
         <v>781</v>
       </c>
-      <c r="E95" s="1" t="s">
-        <v>1560</v>
-      </c>
-      <c r="F95" s="1" t="s">
-        <v>1561</v>
-      </c>
-      <c r="G95" s="1" t="s">
+      <c r="M95" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="N95" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="O95" s="1" t="s">
         <v>782</v>
-      </c>
-      <c r="H95" s="1" t="s">
-        <v>783</v>
-      </c>
-      <c r="I95" s="1" t="s">
-        <v>772</v>
-      </c>
-      <c r="J95" s="1" t="s">
-        <v>738</v>
-      </c>
-      <c r="K95" s="1" t="s">
-        <v>784</v>
-      </c>
-      <c r="L95" s="1" t="s">
-        <v>785</v>
-      </c>
-      <c r="M95" s="1" t="s">
-        <v>741</v>
-      </c>
-      <c r="N95" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="O95" s="1" t="s">
-        <v>786</v>
       </c>
       <c r="P95" s="1" t="s">
         <v>28</v>
@@ -11084,49 +11084,49 @@
         <v>95</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="C96" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>1558</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="J96" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="K96" s="1" t="s">
         <v>787</v>
       </c>
-      <c r="D96" s="1" t="s">
+      <c r="L96" s="1" t="s">
         <v>788</v>
       </c>
-      <c r="E96" s="1" t="s">
-        <v>1357</v>
-      </c>
-      <c r="F96" s="1" t="s">
-        <v>1562</v>
-      </c>
-      <c r="G96" s="1" t="s">
+      <c r="M96" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="N96" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="O96" s="1" t="s">
         <v>789</v>
       </c>
-      <c r="H96" s="1" t="s">
-        <v>790</v>
-      </c>
-      <c r="I96" s="1" t="s">
-        <v>772</v>
-      </c>
-      <c r="J96" s="1" t="s">
-        <v>738</v>
-      </c>
-      <c r="K96" s="1" t="s">
-        <v>791</v>
-      </c>
-      <c r="L96" s="1" t="s">
-        <v>792</v>
-      </c>
-      <c r="M96" s="1" t="s">
-        <v>741</v>
-      </c>
-      <c r="N96" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="O96" s="1" t="s">
-        <v>793</v>
-      </c>
       <c r="P96" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="97" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -11134,49 +11134,49 @@
         <v>96</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="C97" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>1354</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>1559</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="J97" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="K97" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="L97" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="M97" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="N97" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="O97" s="1" t="s">
         <v>794</v>
       </c>
-      <c r="D97" s="1" t="s">
-        <v>795</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>1358</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>1563</v>
-      </c>
-      <c r="G97" s="1" t="s">
-        <v>796</v>
-      </c>
-      <c r="H97" s="1" t="s">
-        <v>797</v>
-      </c>
-      <c r="I97" s="1" t="s">
-        <v>772</v>
-      </c>
-      <c r="J97" s="1" t="s">
-        <v>738</v>
-      </c>
-      <c r="K97" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="L97" s="1" t="s">
-        <v>785</v>
-      </c>
-      <c r="M97" s="1" t="s">
-        <v>741</v>
-      </c>
-      <c r="N97" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="O97" s="1" t="s">
-        <v>798</v>
-      </c>
       <c r="P97" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="98" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -11184,49 +11184,49 @@
         <v>97</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="C98" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>1355</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>1560</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="J98" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="K98" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="L98" s="1" t="s">
         <v>799</v>
       </c>
-      <c r="D98" s="1" t="s">
+      <c r="M98" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="N98" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="O98" s="1" t="s">
         <v>800</v>
       </c>
-      <c r="E98" s="1" t="s">
-        <v>1359</v>
-      </c>
-      <c r="F98" s="1" t="s">
-        <v>1564</v>
-      </c>
-      <c r="G98" s="1" t="s">
-        <v>801</v>
-      </c>
-      <c r="H98" s="1" t="s">
-        <v>802</v>
-      </c>
-      <c r="I98" s="1" t="s">
-        <v>772</v>
-      </c>
-      <c r="J98" s="1" t="s">
-        <v>738</v>
-      </c>
-      <c r="K98" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="L98" s="1" t="s">
-        <v>803</v>
-      </c>
-      <c r="M98" s="1" t="s">
-        <v>741</v>
-      </c>
-      <c r="N98" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="O98" s="1" t="s">
-        <v>804</v>
-      </c>
       <c r="P98" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="99" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -11234,46 +11234,46 @@
         <v>98</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="C99" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>1561</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="H99" s="1" t="s">
         <v>805</v>
       </c>
-      <c r="D99" s="1" t="s">
+      <c r="I99" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="J99" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="K99" s="1" t="s">
         <v>806</v>
       </c>
-      <c r="E99" s="1" t="s">
+      <c r="L99" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="M99" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="N99" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="O99" s="1" t="s">
         <v>807</v>
-      </c>
-      <c r="F99" s="1" t="s">
-        <v>1565</v>
-      </c>
-      <c r="G99" s="1" t="s">
-        <v>808</v>
-      </c>
-      <c r="H99" s="1" t="s">
-        <v>809</v>
-      </c>
-      <c r="I99" s="1" t="s">
-        <v>772</v>
-      </c>
-      <c r="J99" s="1" t="s">
-        <v>738</v>
-      </c>
-      <c r="K99" s="1" t="s">
-        <v>810</v>
-      </c>
-      <c r="L99" s="1" t="s">
-        <v>753</v>
-      </c>
-      <c r="M99" s="1" t="s">
-        <v>741</v>
-      </c>
-      <c r="N99" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="O99" s="1" t="s">
-        <v>811</v>
       </c>
       <c r="P99" s="1" t="s">
         <v>28</v>
@@ -11284,46 +11284,46 @@
         <v>99</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="C100" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>1562</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>1563</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>811</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="J100" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="K100" s="1" t="s">
         <v>812</v>
       </c>
-      <c r="D100" s="1" t="s">
+      <c r="L100" s="1" t="s">
         <v>813</v>
       </c>
-      <c r="E100" s="1" t="s">
-        <v>1566</v>
-      </c>
-      <c r="F100" s="1" t="s">
-        <v>1567</v>
-      </c>
-      <c r="G100" s="1" t="s">
+      <c r="M100" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="N100" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="O100" s="1" t="s">
         <v>814</v>
-      </c>
-      <c r="H100" s="1" t="s">
-        <v>815</v>
-      </c>
-      <c r="I100" s="1" t="s">
-        <v>772</v>
-      </c>
-      <c r="J100" s="1" t="s">
-        <v>738</v>
-      </c>
-      <c r="K100" s="1" t="s">
-        <v>816</v>
-      </c>
-      <c r="L100" s="1" t="s">
-        <v>817</v>
-      </c>
-      <c r="M100" s="1" t="s">
-        <v>741</v>
-      </c>
-      <c r="N100" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="O100" s="1" t="s">
-        <v>818</v>
       </c>
       <c r="P100" s="1" t="s">
         <v>28</v>
@@ -11334,49 +11334,49 @@
         <v>100</v>
       </c>
       <c r="B101" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>816</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>1356</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>1564</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="H101" s="1" t="s">
         <v>819</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="I101" s="1" t="s">
         <v>820</v>
       </c>
-      <c r="D101" s="1" t="s">
+      <c r="J101" s="1" t="s">
         <v>821</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>1360</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>1568</v>
-      </c>
-      <c r="G101" s="1" t="s">
-        <v>822</v>
-      </c>
-      <c r="H101" s="1" t="s">
-        <v>823</v>
-      </c>
-      <c r="I101" s="1" t="s">
-        <v>824</v>
-      </c>
-      <c r="J101" s="1" t="s">
-        <v>825</v>
       </c>
       <c r="K101" s="1" t="s">
         <v>147</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="M101" s="1" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="N101" s="1" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="O101" s="1" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="P101" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="102" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -11384,49 +11384,49 @@
         <v>101</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="C102" s="1" t="s">
+        <v>826</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>827</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>1357</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>828</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="I102" s="1" t="s">
         <v>830</v>
       </c>
-      <c r="D102" s="1" t="s">
+      <c r="J102" s="1" t="s">
         <v>831</v>
       </c>
-      <c r="E102" s="1" t="s">
-        <v>1361</v>
-      </c>
-      <c r="F102" s="1" t="s">
-        <v>1569</v>
-      </c>
-      <c r="G102" s="1" t="s">
+      <c r="K102" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="L102" s="1" t="s">
         <v>832</v>
       </c>
-      <c r="H102" s="1" t="s">
+      <c r="M102" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="N102" s="1" t="s">
         <v>833</v>
       </c>
-      <c r="I102" s="1" t="s">
+      <c r="O102" s="1" t="s">
         <v>834</v>
       </c>
-      <c r="J102" s="1" t="s">
-        <v>835</v>
-      </c>
-      <c r="K102" s="1" t="s">
-        <v>651</v>
-      </c>
-      <c r="L102" s="1" t="s">
-        <v>836</v>
-      </c>
-      <c r="M102" s="1" t="s">
-        <v>827</v>
-      </c>
-      <c r="N102" s="1" t="s">
-        <v>837</v>
-      </c>
-      <c r="O102" s="1" t="s">
-        <v>838</v>
-      </c>
       <c r="P102" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="103" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -11434,46 +11434,46 @@
         <v>102</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>1570</v>
+        <v>1566</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>1571</v>
+        <v>1567</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="J103" s="1" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="K103" s="1" t="s">
         <v>147</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="M103" s="1" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="N103" s="1" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="O103" s="1" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="P103" s="1" t="s">
         <v>28</v>
@@ -11484,49 +11484,49 @@
         <v>103</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="C104" s="1" t="s">
+        <v>841</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>842</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>1568</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>1569</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>844</v>
+      </c>
+      <c r="I104" s="1" t="s">
         <v>845</v>
       </c>
-      <c r="D104" s="1" t="s">
+      <c r="J104" s="1" t="s">
         <v>846</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>1572</v>
-      </c>
-      <c r="F104" s="1" t="s">
-        <v>1573</v>
-      </c>
-      <c r="G104" s="1" t="s">
-        <v>847</v>
-      </c>
-      <c r="H104" s="1" t="s">
-        <v>848</v>
-      </c>
-      <c r="I104" s="1" t="s">
-        <v>849</v>
-      </c>
-      <c r="J104" s="1" t="s">
-        <v>850</v>
       </c>
       <c r="K104" s="1" t="s">
         <v>186</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="M104" s="1" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="N104" s="1" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="O104" s="1" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="P104" s="1" t="s">
-        <v>1342</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="105" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -11534,49 +11534,49 @@
         <v>104</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="C105" s="1" t="s">
+        <v>850</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>851</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>1570</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>1571</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>852</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="I105" s="1" t="s">
         <v>854</v>
       </c>
-      <c r="D105" s="1" t="s">
+      <c r="J105" s="1" t="s">
         <v>855</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>1574</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>1575</v>
-      </c>
-      <c r="G105" s="1" t="s">
-        <v>856</v>
-      </c>
-      <c r="H105" s="1" t="s">
-        <v>857</v>
-      </c>
-      <c r="I105" s="1" t="s">
-        <v>858</v>
-      </c>
-      <c r="J105" s="1" t="s">
-        <v>859</v>
       </c>
       <c r="K105" s="1" t="s">
         <v>147</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="M105" s="1" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="N105" s="1" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="O105" s="1" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="P105" s="1" t="s">
-        <v>1342</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="106" spans="1:16" ht="204.75" x14ac:dyDescent="0.25">
@@ -11584,46 +11584,46 @@
         <v>105</v>
       </c>
       <c r="B106" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>859</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>1572</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>1573</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>861</v>
+      </c>
+      <c r="H106" s="1" t="s">
         <v>862</v>
       </c>
-      <c r="C106" s="1" t="s">
+      <c r="I106" s="1" t="s">
         <v>863</v>
       </c>
-      <c r="D106" s="1" t="s">
+      <c r="J106" s="1" t="s">
         <v>864</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>1576</v>
-      </c>
-      <c r="F106" s="1" t="s">
-        <v>1577</v>
-      </c>
-      <c r="G106" s="1" t="s">
-        <v>865</v>
-      </c>
-      <c r="H106" s="1" t="s">
-        <v>866</v>
-      </c>
-      <c r="I106" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="J106" s="1" t="s">
-        <v>868</v>
       </c>
       <c r="K106" s="1" t="s">
         <v>147</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="M106" s="1" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="N106" s="1" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="O106" s="1" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="P106" s="1" t="s">
         <v>28</v>
@@ -11634,49 +11634,49 @@
         <v>106</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="C107" s="1" t="s">
+        <v>869</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>1574</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>1575</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>872</v>
+      </c>
+      <c r="I107" s="1" t="s">
         <v>873</v>
       </c>
-      <c r="D107" s="1" t="s">
+      <c r="J107" s="1" t="s">
         <v>874</v>
       </c>
-      <c r="E107" s="1" t="s">
-        <v>1578</v>
-      </c>
-      <c r="F107" s="1" t="s">
-        <v>1579</v>
-      </c>
-      <c r="G107" s="1" t="s">
+      <c r="K107" s="1" t="s">
         <v>875</v>
       </c>
-      <c r="H107" s="1" t="s">
+      <c r="L107" s="1" t="s">
         <v>876</v>
       </c>
-      <c r="I107" s="1" t="s">
+      <c r="M107" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="N107" s="1" t="s">
         <v>877</v>
       </c>
-      <c r="J107" s="1" t="s">
+      <c r="O107" s="1" t="s">
         <v>878</v>
       </c>
-      <c r="K107" s="1" t="s">
-        <v>879</v>
-      </c>
-      <c r="L107" s="1" t="s">
-        <v>880</v>
-      </c>
-      <c r="M107" s="1" t="s">
-        <v>870</v>
-      </c>
-      <c r="N107" s="1" t="s">
-        <v>881</v>
-      </c>
-      <c r="O107" s="1" t="s">
-        <v>882</v>
-      </c>
       <c r="P107" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="108" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -11684,49 +11684,49 @@
         <v>107</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="C108" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>880</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>1576</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>1577</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>881</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>882</v>
+      </c>
+      <c r="I108" s="1" t="s">
         <v>883</v>
       </c>
-      <c r="D108" s="1" t="s">
+      <c r="J108" s="1" t="s">
+        <v>874</v>
+      </c>
+      <c r="K108" s="1" t="s">
+        <v>875</v>
+      </c>
+      <c r="L108" s="1" t="s">
+        <v>876</v>
+      </c>
+      <c r="M108" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="N108" s="1" t="s">
         <v>884</v>
       </c>
-      <c r="E108" s="1" t="s">
-        <v>1580</v>
-      </c>
-      <c r="F108" s="1" t="s">
-        <v>1581</v>
-      </c>
-      <c r="G108" s="1" t="s">
+      <c r="O108" s="1" t="s">
         <v>885</v>
       </c>
-      <c r="H108" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="I108" s="1" t="s">
-        <v>887</v>
-      </c>
-      <c r="J108" s="1" t="s">
-        <v>878</v>
-      </c>
-      <c r="K108" s="1" t="s">
-        <v>879</v>
-      </c>
-      <c r="L108" s="1" t="s">
-        <v>880</v>
-      </c>
-      <c r="M108" s="1" t="s">
-        <v>870</v>
-      </c>
-      <c r="N108" s="1" t="s">
-        <v>888</v>
-      </c>
-      <c r="O108" s="1" t="s">
-        <v>889</v>
-      </c>
       <c r="P108" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="109" spans="1:16" ht="189" x14ac:dyDescent="0.25">
@@ -11734,46 +11734,46 @@
         <v>108</v>
       </c>
       <c r="B109" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>887</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>1578</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>1579</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>888</v>
+      </c>
+      <c r="H109" s="1" t="s">
         <v>862</v>
       </c>
-      <c r="C109" s="1" t="s">
+      <c r="I109" s="1" t="s">
+        <v>863</v>
+      </c>
+      <c r="J109" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="K109" s="1" t="s">
+        <v>889</v>
+      </c>
+      <c r="L109" s="1" t="s">
+        <v>865</v>
+      </c>
+      <c r="M109" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="N109" s="1" t="s">
         <v>890</v>
       </c>
-      <c r="D109" s="1" t="s">
+      <c r="O109" s="1" t="s">
         <v>891</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>1582</v>
-      </c>
-      <c r="F109" s="1" t="s">
-        <v>1583</v>
-      </c>
-      <c r="G109" s="1" t="s">
-        <v>892</v>
-      </c>
-      <c r="H109" s="1" t="s">
-        <v>866</v>
-      </c>
-      <c r="I109" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="J109" s="1" t="s">
-        <v>868</v>
-      </c>
-      <c r="K109" s="1" t="s">
-        <v>893</v>
-      </c>
-      <c r="L109" s="1" t="s">
-        <v>869</v>
-      </c>
-      <c r="M109" s="1" t="s">
-        <v>870</v>
-      </c>
-      <c r="N109" s="1" t="s">
-        <v>894</v>
-      </c>
-      <c r="O109" s="1" t="s">
-        <v>895</v>
       </c>
       <c r="P109" s="1" t="s">
         <v>28</v>
@@ -11784,49 +11784,49 @@
         <v>109</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="C110" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>893</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>1580</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>1581</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>894</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="I110" s="1" t="s">
         <v>896</v>
       </c>
-      <c r="D110" s="1" t="s">
+      <c r="J110" s="1" t="s">
         <v>897</v>
       </c>
-      <c r="E110" s="1" t="s">
-        <v>1584</v>
-      </c>
-      <c r="F110" s="1" t="s">
-        <v>1585</v>
-      </c>
-      <c r="G110" s="1" t="s">
+      <c r="K110" s="1" t="s">
         <v>898</v>
       </c>
-      <c r="H110" s="1" t="s">
+      <c r="L110" s="1" t="s">
         <v>899</v>
       </c>
-      <c r="I110" s="1" t="s">
+      <c r="M110" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="N110" s="1" t="s">
+        <v>890</v>
+      </c>
+      <c r="O110" s="1" t="s">
         <v>900</v>
       </c>
-      <c r="J110" s="1" t="s">
-        <v>901</v>
-      </c>
-      <c r="K110" s="1" t="s">
-        <v>902</v>
-      </c>
-      <c r="L110" s="1" t="s">
-        <v>903</v>
-      </c>
-      <c r="M110" s="1" t="s">
-        <v>870</v>
-      </c>
-      <c r="N110" s="1" t="s">
-        <v>894</v>
-      </c>
-      <c r="O110" s="1" t="s">
-        <v>904</v>
-      </c>
       <c r="P110" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="111" spans="1:16" ht="189" x14ac:dyDescent="0.25">
@@ -11834,49 +11834,49 @@
         <v>110</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="C111" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>902</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>1358</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>1582</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="H111" s="1" t="s">
+        <v>904</v>
+      </c>
+      <c r="I111" s="1" t="s">
         <v>905</v>
       </c>
-      <c r="D111" s="1" t="s">
-        <v>906</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>1362</v>
-      </c>
-      <c r="F111" s="1" t="s">
-        <v>1586</v>
-      </c>
-      <c r="G111" s="1" t="s">
-        <v>907</v>
-      </c>
-      <c r="H111" s="1" t="s">
-        <v>908</v>
-      </c>
-      <c r="I111" s="1" t="s">
-        <v>909</v>
-      </c>
       <c r="J111" s="1" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="K111" s="1" t="s">
         <v>186</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="M111" s="1" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="N111" s="1" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="O111" s="1" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="P111" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="112" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -11884,49 +11884,49 @@
         <v>111</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="C112" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>1359</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>1583</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>910</v>
+      </c>
+      <c r="H112" s="1" t="s">
+        <v>911</v>
+      </c>
+      <c r="I112" s="1" t="s">
         <v>912</v>
       </c>
-      <c r="D112" s="1" t="s">
+      <c r="J112" s="1" t="s">
+        <v>897</v>
+      </c>
+      <c r="K112" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="L112" s="1" t="s">
         <v>913</v>
       </c>
-      <c r="E112" s="1" t="s">
-        <v>1363</v>
-      </c>
-      <c r="F112" s="1" t="s">
-        <v>1587</v>
-      </c>
-      <c r="G112" s="1" t="s">
+      <c r="M112" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="N112" s="1" t="s">
+        <v>890</v>
+      </c>
+      <c r="O112" s="1" t="s">
         <v>914</v>
       </c>
-      <c r="H112" s="1" t="s">
-        <v>915</v>
-      </c>
-      <c r="I112" s="1" t="s">
-        <v>916</v>
-      </c>
-      <c r="J112" s="1" t="s">
-        <v>901</v>
-      </c>
-      <c r="K112" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="L112" s="1" t="s">
-        <v>917</v>
-      </c>
-      <c r="M112" s="1" t="s">
-        <v>870</v>
-      </c>
-      <c r="N112" s="1" t="s">
-        <v>894</v>
-      </c>
-      <c r="O112" s="1" t="s">
-        <v>918</v>
-      </c>
       <c r="P112" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="113" spans="1:16" ht="204.75" x14ac:dyDescent="0.25">
@@ -11934,49 +11934,49 @@
         <v>112</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="C113" s="1" t="s">
+        <v>915</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>1584</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>1585</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>918</v>
+      </c>
+      <c r="I113" s="1" t="s">
         <v>919</v>
       </c>
-      <c r="D113" s="1" t="s">
+      <c r="J113" s="1" t="s">
         <v>920</v>
       </c>
-      <c r="E113" s="1" t="s">
-        <v>1588</v>
-      </c>
-      <c r="F113" s="1" t="s">
-        <v>1589</v>
-      </c>
-      <c r="G113" s="1" t="s">
+      <c r="K113" s="1" t="s">
         <v>921</v>
       </c>
-      <c r="H113" s="1" t="s">
+      <c r="L113" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="M113" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="N113" s="1" t="s">
+        <v>890</v>
+      </c>
+      <c r="O113" s="1" t="s">
         <v>922</v>
       </c>
-      <c r="I113" s="1" t="s">
-        <v>923</v>
-      </c>
-      <c r="J113" s="1" t="s">
-        <v>924</v>
-      </c>
-      <c r="K113" s="1" t="s">
-        <v>925</v>
-      </c>
-      <c r="L113" s="1" t="s">
-        <v>910</v>
-      </c>
-      <c r="M113" s="1" t="s">
-        <v>870</v>
-      </c>
-      <c r="N113" s="1" t="s">
-        <v>894</v>
-      </c>
-      <c r="O113" s="1" t="s">
-        <v>926</v>
-      </c>
       <c r="P113" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="114" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -11984,49 +11984,49 @@
         <v>113</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="C114" s="1" t="s">
+        <v>923</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>924</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>1586</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>925</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>926</v>
+      </c>
+      <c r="I114" s="1" t="s">
         <v>927</v>
       </c>
-      <c r="D114" s="1" t="s">
+      <c r="J114" s="1" t="s">
         <v>928</v>
       </c>
-      <c r="E114" s="1" t="s">
-        <v>1364</v>
-      </c>
-      <c r="F114" s="1" t="s">
-        <v>1590</v>
-      </c>
-      <c r="G114" s="1" t="s">
+      <c r="K114" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="L114" s="1" t="s">
         <v>929</v>
       </c>
-      <c r="H114" s="1" t="s">
+      <c r="M114" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="N114" s="1" t="s">
+        <v>890</v>
+      </c>
+      <c r="O114" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="I114" s="1" t="s">
-        <v>931</v>
-      </c>
-      <c r="J114" s="1" t="s">
-        <v>932</v>
-      </c>
-      <c r="K114" s="1" t="s">
-        <v>634</v>
-      </c>
-      <c r="L114" s="1" t="s">
-        <v>933</v>
-      </c>
-      <c r="M114" s="1" t="s">
-        <v>870</v>
-      </c>
-      <c r="N114" s="1" t="s">
-        <v>894</v>
-      </c>
-      <c r="O114" s="1" t="s">
-        <v>934</v>
-      </c>
       <c r="P114" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="115" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -12034,49 +12034,49 @@
         <v>114</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="C115" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>1587</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>1588</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>933</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>934</v>
+      </c>
+      <c r="I115" s="1" t="s">
         <v>935</v>
       </c>
-      <c r="D115" s="1" t="s">
+      <c r="J115" s="1" t="s">
         <v>936</v>
       </c>
-      <c r="E115" s="1" t="s">
-        <v>1591</v>
-      </c>
-      <c r="F115" s="1" t="s">
-        <v>1592</v>
-      </c>
-      <c r="G115" s="1" t="s">
+      <c r="K115" s="1" t="s">
         <v>937</v>
       </c>
-      <c r="H115" s="1" t="s">
+      <c r="L115" s="1" t="s">
         <v>938</v>
       </c>
-      <c r="I115" s="1" t="s">
+      <c r="M115" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="N115" s="1" t="s">
+        <v>890</v>
+      </c>
+      <c r="O115" s="1" t="s">
         <v>939</v>
       </c>
-      <c r="J115" s="1" t="s">
-        <v>940</v>
-      </c>
-      <c r="K115" s="1" t="s">
-        <v>941</v>
-      </c>
-      <c r="L115" s="1" t="s">
-        <v>942</v>
-      </c>
-      <c r="M115" s="1" t="s">
-        <v>870</v>
-      </c>
-      <c r="N115" s="1" t="s">
-        <v>894</v>
-      </c>
-      <c r="O115" s="1" t="s">
-        <v>943</v>
-      </c>
       <c r="P115" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="116" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -12084,46 +12084,46 @@
         <v>115</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="C116" s="1" t="s">
+        <v>940</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>941</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>1589</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>1590</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>942</v>
+      </c>
+      <c r="H116" s="1" t="s">
+        <v>943</v>
+      </c>
+      <c r="I116" s="1" t="s">
         <v>944</v>
       </c>
-      <c r="D116" s="1" t="s">
+      <c r="J116" s="1" t="s">
         <v>945</v>
       </c>
-      <c r="E116" s="1" t="s">
-        <v>1593</v>
-      </c>
-      <c r="F116" s="1" t="s">
-        <v>1594</v>
-      </c>
-      <c r="G116" s="1" t="s">
+      <c r="K116" s="1" t="s">
+        <v>937</v>
+      </c>
+      <c r="L116" s="1" t="s">
+        <v>929</v>
+      </c>
+      <c r="M116" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="N116" s="1" t="s">
+        <v>890</v>
+      </c>
+      <c r="O116" s="1" t="s">
         <v>946</v>
-      </c>
-      <c r="H116" s="1" t="s">
-        <v>947</v>
-      </c>
-      <c r="I116" s="1" t="s">
-        <v>948</v>
-      </c>
-      <c r="J116" s="1" t="s">
-        <v>949</v>
-      </c>
-      <c r="K116" s="1" t="s">
-        <v>941</v>
-      </c>
-      <c r="L116" s="1" t="s">
-        <v>933</v>
-      </c>
-      <c r="M116" s="1" t="s">
-        <v>870</v>
-      </c>
-      <c r="N116" s="1" t="s">
-        <v>894</v>
-      </c>
-      <c r="O116" s="1" t="s">
-        <v>950</v>
       </c>
       <c r="P116" s="1" t="s">
         <v>28</v>
@@ -12134,49 +12134,49 @@
         <v>116</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="C117" s="1" t="s">
+        <v>947</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>948</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>1332</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>1591</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>1333</v>
+      </c>
+      <c r="H117" s="1" t="s">
+        <v>1339</v>
+      </c>
+      <c r="I117" s="1" t="s">
+        <v>949</v>
+      </c>
+      <c r="J117" s="1" t="s">
+        <v>950</v>
+      </c>
+      <c r="K117" s="1" t="s">
         <v>951</v>
       </c>
-      <c r="D117" s="1" t="s">
+      <c r="L117" s="1" t="s">
         <v>952</v>
       </c>
-      <c r="E117" s="1" t="s">
-        <v>1336</v>
-      </c>
-      <c r="F117" s="1" t="s">
-        <v>1595</v>
-      </c>
-      <c r="G117" s="1" t="s">
-        <v>1337</v>
-      </c>
-      <c r="H117" s="1" t="s">
-        <v>1343</v>
-      </c>
-      <c r="I117" s="1" t="s">
+      <c r="M117" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="N117" s="1" t="s">
+        <v>890</v>
+      </c>
+      <c r="O117" s="1" t="s">
         <v>953</v>
       </c>
-      <c r="J117" s="1" t="s">
-        <v>954</v>
-      </c>
-      <c r="K117" s="1" t="s">
-        <v>955</v>
-      </c>
-      <c r="L117" s="1" t="s">
-        <v>956</v>
-      </c>
-      <c r="M117" s="1" t="s">
-        <v>870</v>
-      </c>
-      <c r="N117" s="1" t="s">
-        <v>894</v>
-      </c>
-      <c r="O117" s="1" t="s">
-        <v>957</v>
-      </c>
       <c r="P117" s="1" t="s">
-        <v>1330</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="118" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -12184,46 +12184,46 @@
         <v>117</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="C118" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>1592</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>1593</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="H118" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="I118" s="1" t="s">
         <v>958</v>
       </c>
-      <c r="D118" s="1" t="s">
+      <c r="J118" s="1" t="s">
         <v>959</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>1596</v>
-      </c>
-      <c r="F118" s="1" t="s">
-        <v>1597</v>
-      </c>
-      <c r="G118" s="1" t="s">
-        <v>960</v>
-      </c>
-      <c r="H118" s="1" t="s">
-        <v>961</v>
-      </c>
-      <c r="I118" s="1" t="s">
-        <v>962</v>
-      </c>
-      <c r="J118" s="1" t="s">
-        <v>963</v>
       </c>
       <c r="K118" s="1" t="s">
         <v>81</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="M118" s="1" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="N118" s="1" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="O118" s="1" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="P118" s="1" t="s">
         <v>28</v>
@@ -12234,49 +12234,49 @@
         <v>118</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="C119" s="1" t="s">
+        <v>962</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>963</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>1361</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>964</v>
+      </c>
+      <c r="H119" s="1" t="s">
+        <v>965</v>
+      </c>
+      <c r="I119" s="1" t="s">
         <v>966</v>
       </c>
-      <c r="D119" s="1" t="s">
+      <c r="J119" s="1" t="s">
         <v>967</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>1365</v>
-      </c>
-      <c r="F119" s="1" t="s">
-        <v>1598</v>
-      </c>
-      <c r="G119" s="1" t="s">
-        <v>968</v>
-      </c>
-      <c r="H119" s="1" t="s">
-        <v>969</v>
-      </c>
-      <c r="I119" s="1" t="s">
-        <v>970</v>
-      </c>
-      <c r="J119" s="1" t="s">
-        <v>971</v>
       </c>
       <c r="K119" s="1" t="s">
         <v>274</v>
       </c>
       <c r="L119" s="1" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="M119" s="1" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="N119" s="1" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="O119" s="1" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="P119" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="120" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -12284,49 +12284,49 @@
         <v>119</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>1366</v>
+        <v>1362</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>1599</v>
+        <v>1595</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="J120" s="1" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="K120" s="1" t="s">
         <v>265</v>
       </c>
       <c r="L120" s="1" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="M120" s="1" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="N120" s="1" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="O120" s="1" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="P120" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="121" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -12334,49 +12334,49 @@
         <v>120</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="C121" s="1" t="s">
+        <v>976</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>977</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>1363</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>1596</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>978</v>
+      </c>
+      <c r="H121" s="1" t="s">
+        <v>979</v>
+      </c>
+      <c r="I121" s="1" t="s">
+        <v>966</v>
+      </c>
+      <c r="J121" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="K121" s="1" t="s">
+        <v>875</v>
+      </c>
+      <c r="L121" s="1" t="s">
         <v>980</v>
       </c>
-      <c r="D121" s="1" t="s">
+      <c r="M121" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="N121" s="1" t="s">
+        <v>890</v>
+      </c>
+      <c r="O121" s="1" t="s">
         <v>981</v>
       </c>
-      <c r="E121" s="1" t="s">
-        <v>1367</v>
-      </c>
-      <c r="F121" s="1" t="s">
-        <v>1600</v>
-      </c>
-      <c r="G121" s="1" t="s">
-        <v>982</v>
-      </c>
-      <c r="H121" s="1" t="s">
-        <v>983</v>
-      </c>
-      <c r="I121" s="1" t="s">
-        <v>970</v>
-      </c>
-      <c r="J121" s="1" t="s">
-        <v>971</v>
-      </c>
-      <c r="K121" s="1" t="s">
-        <v>879</v>
-      </c>
-      <c r="L121" s="1" t="s">
-        <v>984</v>
-      </c>
-      <c r="M121" s="1" t="s">
-        <v>870</v>
-      </c>
-      <c r="N121" s="1" t="s">
-        <v>894</v>
-      </c>
-      <c r="O121" s="1" t="s">
-        <v>985</v>
-      </c>
       <c r="P121" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="122" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -12384,49 +12384,49 @@
         <v>121</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="C122" s="1" t="s">
+        <v>982</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>983</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>1597</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>1598</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>984</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>985</v>
+      </c>
+      <c r="I122" s="1" t="s">
+        <v>966</v>
+      </c>
+      <c r="J122" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="K122" s="1" t="s">
         <v>986</v>
       </c>
-      <c r="D122" s="1" t="s">
+      <c r="L122" s="1" t="s">
         <v>987</v>
       </c>
-      <c r="E122" s="1" t="s">
-        <v>1601</v>
-      </c>
-      <c r="F122" s="1" t="s">
-        <v>1602</v>
-      </c>
-      <c r="G122" s="1" t="s">
+      <c r="M122" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="N122" s="1" t="s">
+        <v>890</v>
+      </c>
+      <c r="O122" s="1" t="s">
         <v>988</v>
       </c>
-      <c r="H122" s="1" t="s">
-        <v>989</v>
-      </c>
-      <c r="I122" s="1" t="s">
-        <v>970</v>
-      </c>
-      <c r="J122" s="1" t="s">
-        <v>971</v>
-      </c>
-      <c r="K122" s="1" t="s">
-        <v>990</v>
-      </c>
-      <c r="L122" s="1" t="s">
-        <v>991</v>
-      </c>
-      <c r="M122" s="1" t="s">
-        <v>870</v>
-      </c>
-      <c r="N122" s="1" t="s">
-        <v>894</v>
-      </c>
-      <c r="O122" s="1" t="s">
-        <v>992</v>
-      </c>
       <c r="P122" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="123" spans="1:16" ht="204.75" x14ac:dyDescent="0.25">
@@ -12434,49 +12434,49 @@
         <v>122</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="C123" s="1" t="s">
+        <v>989</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>990</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>1599</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>1600</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>991</v>
+      </c>
+      <c r="H123" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="I123" s="1" t="s">
         <v>993</v>
       </c>
-      <c r="D123" s="1" t="s">
+      <c r="J123" s="1" t="s">
         <v>994</v>
       </c>
-      <c r="E123" s="1" t="s">
-        <v>1603</v>
-      </c>
-      <c r="F123" s="1" t="s">
-        <v>1604</v>
-      </c>
-      <c r="G123" s="1" t="s">
+      <c r="K123" s="1" t="s">
         <v>995</v>
       </c>
-      <c r="H123" s="1" t="s">
+      <c r="L123" s="1" t="s">
         <v>996</v>
       </c>
-      <c r="I123" s="1" t="s">
+      <c r="M123" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="N123" s="1" t="s">
+        <v>890</v>
+      </c>
+      <c r="O123" s="1" t="s">
         <v>997</v>
       </c>
-      <c r="J123" s="1" t="s">
-        <v>998</v>
-      </c>
-      <c r="K123" s="1" t="s">
-        <v>999</v>
-      </c>
-      <c r="L123" s="1" t="s">
-        <v>1000</v>
-      </c>
-      <c r="M123" s="1" t="s">
-        <v>870</v>
-      </c>
-      <c r="N123" s="1" t="s">
-        <v>894</v>
-      </c>
-      <c r="O123" s="1" t="s">
-        <v>1001</v>
-      </c>
       <c r="P123" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="124" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -12484,46 +12484,46 @@
         <v>123</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="C124" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>999</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>1601</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>1602</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>1000</v>
+      </c>
+      <c r="H124" s="1" t="s">
+        <v>1001</v>
+      </c>
+      <c r="I124" s="1" t="s">
         <v>1002</v>
       </c>
-      <c r="D124" s="1" t="s">
+      <c r="J124" s="1" t="s">
         <v>1003</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>1605</v>
-      </c>
-      <c r="F124" s="1" t="s">
-        <v>1606</v>
-      </c>
-      <c r="G124" s="1" t="s">
-        <v>1004</v>
-      </c>
-      <c r="H124" s="1" t="s">
-        <v>1005</v>
-      </c>
-      <c r="I124" s="1" t="s">
-        <v>1006</v>
-      </c>
-      <c r="J124" s="1" t="s">
-        <v>1007</v>
       </c>
       <c r="K124" s="1" t="s">
         <v>284</v>
       </c>
       <c r="L124" s="1" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
       <c r="M124" s="1" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="N124" s="1" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="O124" s="1" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
       <c r="P124" s="1" t="s">
         <v>28</v>
@@ -12534,49 +12534,49 @@
         <v>124</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="C125" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>1603</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>1604</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>1008</v>
+      </c>
+      <c r="H125" s="1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="I125" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="J125" s="1" t="s">
         <v>1010</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>1011</v>
-      </c>
-      <c r="E125" s="1" t="s">
-        <v>1607</v>
-      </c>
-      <c r="F125" s="1" t="s">
-        <v>1608</v>
-      </c>
-      <c r="G125" s="1" t="s">
-        <v>1012</v>
-      </c>
-      <c r="H125" s="1" t="s">
-        <v>1013</v>
-      </c>
-      <c r="I125" s="1" t="s">
-        <v>1006</v>
-      </c>
-      <c r="J125" s="1" t="s">
-        <v>1014</v>
       </c>
       <c r="K125" s="1" t="s">
         <v>265</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="M125" s="1" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="N125" s="1" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="O125" s="1" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="P125" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="126" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -12584,46 +12584,46 @@
         <v>125</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="C126" s="1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>1605</v>
+      </c>
+      <c r="G126" s="1" t="s">
+        <v>1016</v>
+      </c>
+      <c r="H126" s="1" t="s">
         <v>1017</v>
       </c>
-      <c r="D126" s="1" t="s">
+      <c r="I126" s="1" t="s">
         <v>1018</v>
       </c>
-      <c r="E126" s="1" t="s">
+      <c r="J126" s="1" t="s">
+        <v>1010</v>
+      </c>
+      <c r="K126" s="1" t="s">
         <v>1019</v>
       </c>
-      <c r="F126" s="1" t="s">
-        <v>1609</v>
-      </c>
-      <c r="G126" s="1" t="s">
+      <c r="L126" s="1" t="s">
         <v>1020</v>
       </c>
-      <c r="H126" s="1" t="s">
+      <c r="M126" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="N126" s="1" t="s">
+        <v>890</v>
+      </c>
+      <c r="O126" s="1" t="s">
         <v>1021</v>
-      </c>
-      <c r="I126" s="1" t="s">
-        <v>1022</v>
-      </c>
-      <c r="J126" s="1" t="s">
-        <v>1014</v>
-      </c>
-      <c r="K126" s="1" t="s">
-        <v>1023</v>
-      </c>
-      <c r="L126" s="1" t="s">
-        <v>1024</v>
-      </c>
-      <c r="M126" s="1" t="s">
-        <v>870</v>
-      </c>
-      <c r="N126" s="1" t="s">
-        <v>894</v>
-      </c>
-      <c r="O126" s="1" t="s">
-        <v>1025</v>
       </c>
       <c r="P126" s="1" t="s">
         <v>28</v>
@@ -12634,49 +12634,49 @@
         <v>126</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="C127" s="1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>1364</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>1606</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>1024</v>
+      </c>
+      <c r="H127" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="I127" s="1" t="s">
         <v>1026</v>
       </c>
-      <c r="D127" s="1" t="s">
+      <c r="J127" s="1" t="s">
+        <v>1010</v>
+      </c>
+      <c r="K127" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="L127" s="1" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M127" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="N127" s="1" t="s">
+        <v>890</v>
+      </c>
+      <c r="O127" s="1" t="s">
         <v>1027</v>
       </c>
-      <c r="E127" s="1" t="s">
-        <v>1368</v>
-      </c>
-      <c r="F127" s="1" t="s">
-        <v>1610</v>
-      </c>
-      <c r="G127" s="1" t="s">
-        <v>1028</v>
-      </c>
-      <c r="H127" s="1" t="s">
-        <v>1029</v>
-      </c>
-      <c r="I127" s="1" t="s">
-        <v>1030</v>
-      </c>
-      <c r="J127" s="1" t="s">
-        <v>1014</v>
-      </c>
-      <c r="K127" s="1" t="s">
-        <v>791</v>
-      </c>
-      <c r="L127" s="1" t="s">
-        <v>1369</v>
-      </c>
-      <c r="M127" s="1" t="s">
-        <v>870</v>
-      </c>
-      <c r="N127" s="1" t="s">
-        <v>894</v>
-      </c>
-      <c r="O127" s="1" t="s">
-        <v>1031</v>
-      </c>
       <c r="P127" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="128" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -12684,49 +12684,49 @@
         <v>127</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="C128" s="1" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>1029</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>1030</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="G128" s="1" t="s">
+        <v>1031</v>
+      </c>
+      <c r="H128" s="1" t="s">
         <v>1032</v>
       </c>
-      <c r="D128" s="1" t="s">
+      <c r="I128" s="1" t="s">
         <v>1033</v>
       </c>
-      <c r="E128" s="1" t="s">
+      <c r="J128" s="1" t="s">
         <v>1034</v>
       </c>
-      <c r="F128" s="1" t="s">
-        <v>1611</v>
-      </c>
-      <c r="G128" s="1" t="s">
+      <c r="K128" s="1" t="s">
+        <v>937</v>
+      </c>
+      <c r="L128" s="1" t="s">
         <v>1035</v>
       </c>
-      <c r="H128" s="1" t="s">
+      <c r="M128" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="N128" s="1" t="s">
+        <v>890</v>
+      </c>
+      <c r="O128" s="1" t="s">
         <v>1036</v>
       </c>
-      <c r="I128" s="1" t="s">
-        <v>1037</v>
-      </c>
-      <c r="J128" s="1" t="s">
-        <v>1038</v>
-      </c>
-      <c r="K128" s="1" t="s">
-        <v>941</v>
-      </c>
-      <c r="L128" s="1" t="s">
-        <v>1039</v>
-      </c>
-      <c r="M128" s="1" t="s">
-        <v>870</v>
-      </c>
-      <c r="N128" s="1" t="s">
-        <v>894</v>
-      </c>
-      <c r="O128" s="1" t="s">
-        <v>1040</v>
-      </c>
       <c r="P128" s="1" t="s">
-        <v>1342</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="129" spans="1:16" ht="204.75" x14ac:dyDescent="0.25">
@@ -12734,49 +12734,49 @@
         <v>128</v>
       </c>
       <c r="B129" s="1" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>1039</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>1366</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>1608</v>
+      </c>
+      <c r="G129" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="H129" s="1" t="s">
         <v>1041</v>
       </c>
-      <c r="C129" s="1" t="s">
+      <c r="I129" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="J129" s="1" t="s">
         <v>1042</v>
       </c>
-      <c r="D129" s="1" t="s">
+      <c r="K129" s="1" t="s">
+        <v>937</v>
+      </c>
+      <c r="L129" s="1" t="s">
         <v>1043</v>
       </c>
-      <c r="E129" s="1" t="s">
-        <v>1370</v>
-      </c>
-      <c r="F129" s="1" t="s">
-        <v>1612</v>
-      </c>
-      <c r="G129" s="1" t="s">
+      <c r="M129" s="1" t="s">
         <v>1044</v>
       </c>
-      <c r="H129" s="1" t="s">
+      <c r="N129" s="1" t="s">
         <v>1045</v>
       </c>
-      <c r="I129" s="1" t="s">
-        <v>1030</v>
-      </c>
-      <c r="J129" s="1" t="s">
+      <c r="O129" s="1" t="s">
         <v>1046</v>
       </c>
-      <c r="K129" s="1" t="s">
-        <v>941</v>
-      </c>
-      <c r="L129" s="1" t="s">
-        <v>1047</v>
-      </c>
-      <c r="M129" s="1" t="s">
-        <v>1048</v>
-      </c>
-      <c r="N129" s="1" t="s">
-        <v>1049</v>
-      </c>
-      <c r="O129" s="1" t="s">
-        <v>1050</v>
-      </c>
       <c r="P129" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="130" spans="1:16" ht="204.75" x14ac:dyDescent="0.25">
@@ -12784,49 +12784,49 @@
         <v>129</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>1041</v>
+        <v>1037</v>
       </c>
       <c r="C130" s="1" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>1048</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>1049</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G130" s="1" t="s">
+        <v>1050</v>
+      </c>
+      <c r="H130" s="1" t="s">
         <v>1051</v>
       </c>
-      <c r="D130" s="1" t="s">
+      <c r="I130" s="1" t="s">
         <v>1052</v>
       </c>
-      <c r="E130" s="1" t="s">
+      <c r="J130" s="1" t="s">
         <v>1053</v>
       </c>
-      <c r="F130" s="1" t="s">
-        <v>1613</v>
-      </c>
-      <c r="G130" s="1" t="s">
+      <c r="K130" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="L130" s="1" t="s">
         <v>1054</v>
       </c>
-      <c r="H130" s="1" t="s">
+      <c r="M130" s="1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="N130" s="1" t="s">
         <v>1055</v>
       </c>
-      <c r="I130" s="1" t="s">
+      <c r="O130" s="1" t="s">
         <v>1056</v>
       </c>
-      <c r="J130" s="1" t="s">
-        <v>1057</v>
-      </c>
-      <c r="K130" s="1" t="s">
-        <v>634</v>
-      </c>
-      <c r="L130" s="1" t="s">
-        <v>1058</v>
-      </c>
-      <c r="M130" s="1" t="s">
-        <v>1048</v>
-      </c>
-      <c r="N130" s="1" t="s">
-        <v>1059</v>
-      </c>
-      <c r="O130" s="1" t="s">
-        <v>1060</v>
-      </c>
       <c r="P130" s="1" t="s">
-        <v>1342</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="131" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -12834,49 +12834,49 @@
         <v>130</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>1041</v>
+        <v>1037</v>
       </c>
       <c r="C131" s="1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>1610</v>
+      </c>
+      <c r="G131" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="H131" s="1" t="s">
         <v>1061</v>
       </c>
-      <c r="D131" s="1" t="s">
+      <c r="I131" s="1" t="s">
         <v>1062</v>
       </c>
-      <c r="E131" s="1" t="s">
+      <c r="J131" s="1" t="s">
         <v>1063</v>
       </c>
-      <c r="F131" s="1" t="s">
-        <v>1614</v>
-      </c>
-      <c r="G131" s="1" t="s">
+      <c r="K131" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="L131" s="1" t="s">
+        <v>1054</v>
+      </c>
+      <c r="M131" s="1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="N131" s="1" t="s">
         <v>1064</v>
       </c>
-      <c r="H131" s="1" t="s">
+      <c r="O131" s="1" t="s">
         <v>1065</v>
       </c>
-      <c r="I131" s="1" t="s">
-        <v>1066</v>
-      </c>
-      <c r="J131" s="1" t="s">
-        <v>1067</v>
-      </c>
-      <c r="K131" s="1" t="s">
-        <v>651</v>
-      </c>
-      <c r="L131" s="1" t="s">
-        <v>1058</v>
-      </c>
-      <c r="M131" s="1" t="s">
-        <v>1048</v>
-      </c>
-      <c r="N131" s="1" t="s">
-        <v>1068</v>
-      </c>
-      <c r="O131" s="1" t="s">
-        <v>1069</v>
-      </c>
       <c r="P131" s="1" t="s">
-        <v>1342</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="132" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -12884,49 +12884,49 @@
         <v>131</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>1041</v>
+        <v>1037</v>
       </c>
       <c r="C132" s="1" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>1067</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>1068</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>1611</v>
+      </c>
+      <c r="G132" s="1" t="s">
+        <v>1069</v>
+      </c>
+      <c r="H132" s="1" t="s">
         <v>1070</v>
       </c>
-      <c r="D132" s="1" t="s">
+      <c r="I132" s="1" t="s">
         <v>1071</v>
       </c>
-      <c r="E132" s="1" t="s">
+      <c r="J132" s="1" t="s">
         <v>1072</v>
       </c>
-      <c r="F132" s="1" t="s">
-        <v>1615</v>
-      </c>
-      <c r="G132" s="1" t="s">
+      <c r="K132" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="L132" s="1" t="s">
         <v>1073</v>
       </c>
-      <c r="H132" s="1" t="s">
+      <c r="M132" s="1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="N132" s="1" t="s">
         <v>1074</v>
       </c>
-      <c r="I132" s="1" t="s">
+      <c r="O132" s="1" t="s">
         <v>1075</v>
       </c>
-      <c r="J132" s="1" t="s">
-        <v>1076</v>
-      </c>
-      <c r="K132" s="1" t="s">
-        <v>758</v>
-      </c>
-      <c r="L132" s="1" t="s">
-        <v>1077</v>
-      </c>
-      <c r="M132" s="1" t="s">
-        <v>1048</v>
-      </c>
-      <c r="N132" s="1" t="s">
-        <v>1078</v>
-      </c>
-      <c r="O132" s="1" t="s">
-        <v>1079</v>
-      </c>
       <c r="P132" s="1" t="s">
-        <v>1342</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="133" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -12934,49 +12934,49 @@
         <v>132</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>1041</v>
+        <v>1037</v>
       </c>
       <c r="C133" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>1077</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>1612</v>
+      </c>
+      <c r="G133" s="1" t="s">
+        <v>1079</v>
+      </c>
+      <c r="H133" s="1" t="s">
         <v>1080</v>
       </c>
-      <c r="D133" s="1" t="s">
+      <c r="I133" s="1" t="s">
         <v>1081</v>
       </c>
-      <c r="E133" s="1" t="s">
+      <c r="J133" s="1" t="s">
         <v>1082</v>
-      </c>
-      <c r="F133" s="1" t="s">
-        <v>1616</v>
-      </c>
-      <c r="G133" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="H133" s="1" t="s">
-        <v>1084</v>
-      </c>
-      <c r="I133" s="1" t="s">
-        <v>1085</v>
-      </c>
-      <c r="J133" s="1" t="s">
-        <v>1086</v>
       </c>
       <c r="K133" s="1" t="s">
         <v>284</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>1087</v>
+        <v>1083</v>
       </c>
       <c r="M133" s="1" t="s">
-        <v>1048</v>
+        <v>1044</v>
       </c>
       <c r="N133" s="1" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="O133" s="1" t="s">
-        <v>1088</v>
+        <v>1084</v>
       </c>
       <c r="P133" s="1" t="s">
-        <v>1342</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="134" spans="1:16" ht="409.5" x14ac:dyDescent="0.25">
@@ -12984,46 +12984,46 @@
         <v>133</v>
       </c>
       <c r="B134" s="1" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>1614</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>1088</v>
+      </c>
+      <c r="H134" s="1" t="s">
         <v>1089</v>
       </c>
-      <c r="C134" s="1" t="s">
+      <c r="I134" s="1" t="s">
         <v>1090</v>
       </c>
-      <c r="D134" s="1" t="s">
+      <c r="J134" s="1" t="s">
         <v>1091</v>
-      </c>
-      <c r="E134" s="1" t="s">
-        <v>1617</v>
-      </c>
-      <c r="F134" s="1" t="s">
-        <v>1618</v>
-      </c>
-      <c r="G134" s="1" t="s">
-        <v>1092</v>
-      </c>
-      <c r="H134" s="1" t="s">
-        <v>1093</v>
-      </c>
-      <c r="I134" s="1" t="s">
-        <v>1094</v>
-      </c>
-      <c r="J134" s="1" t="s">
-        <v>1095</v>
       </c>
       <c r="K134" s="1" t="s">
         <v>53</v>
       </c>
       <c r="L134" s="1" t="s">
-        <v>1096</v>
+        <v>1092</v>
       </c>
       <c r="M134" s="1" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="N134" s="1" t="s">
-        <v>1098</v>
+        <v>1094</v>
       </c>
       <c r="O134" s="1" t="s">
-        <v>1099</v>
+        <v>1095</v>
       </c>
       <c r="P134" s="1" t="s">
         <v>28</v>
@@ -13034,46 +13034,46 @@
         <v>134</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="C135" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>1616</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="H135" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="I135" s="1" t="s">
         <v>1100</v>
       </c>
-      <c r="D135" s="1" t="s">
-        <v>1101</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>1619</v>
-      </c>
-      <c r="F135" s="1" t="s">
-        <v>1620</v>
-      </c>
-      <c r="G135" s="1" t="s">
-        <v>1102</v>
-      </c>
-      <c r="H135" s="1" t="s">
-        <v>1103</v>
-      </c>
-      <c r="I135" s="1" t="s">
-        <v>1104</v>
-      </c>
       <c r="J135" s="1" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="K135" s="1" t="s">
         <v>53</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>1096</v>
+        <v>1092</v>
       </c>
       <c r="M135" s="1" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="N135" s="1" t="s">
-        <v>1105</v>
+        <v>1101</v>
       </c>
       <c r="O135" s="1" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
       <c r="P135" s="1" t="s">
         <v>28</v>
@@ -13084,49 +13084,49 @@
         <v>135</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="C136" s="1" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>1617</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>1618</v>
+      </c>
+      <c r="G136" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="H136" s="1" t="s">
+        <v>1106</v>
+      </c>
+      <c r="I136" s="1" t="s">
         <v>1107</v>
       </c>
-      <c r="D136" s="1" t="s">
+      <c r="J136" s="1" t="s">
         <v>1108</v>
       </c>
-      <c r="E136" s="1" t="s">
-        <v>1621</v>
-      </c>
-      <c r="F136" s="1" t="s">
-        <v>1622</v>
-      </c>
-      <c r="G136" s="1" t="s">
+      <c r="K136" s="1" t="s">
         <v>1109</v>
       </c>
-      <c r="H136" s="1" t="s">
+      <c r="L136" s="1" t="s">
+        <v>1092</v>
+      </c>
+      <c r="M136" s="1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="N136" s="1" t="s">
         <v>1110</v>
       </c>
-      <c r="I136" s="1" t="s">
+      <c r="O136" s="1" t="s">
         <v>1111</v>
       </c>
-      <c r="J136" s="1" t="s">
-        <v>1112</v>
-      </c>
-      <c r="K136" s="1" t="s">
-        <v>1113</v>
-      </c>
-      <c r="L136" s="1" t="s">
-        <v>1096</v>
-      </c>
-      <c r="M136" s="1" t="s">
-        <v>1097</v>
-      </c>
-      <c r="N136" s="1" t="s">
-        <v>1114</v>
-      </c>
-      <c r="O136" s="1" t="s">
-        <v>1115</v>
-      </c>
       <c r="P136" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="137" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -13134,46 +13134,46 @@
         <v>136</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="C137" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>1619</v>
+      </c>
+      <c r="G137" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="H137" s="1" t="s">
         <v>1116</v>
       </c>
-      <c r="D137" s="1" t="s">
+      <c r="I137" s="1" t="s">
         <v>1117</v>
       </c>
-      <c r="E137" s="1" t="s">
+      <c r="J137" s="1" t="s">
         <v>1118</v>
       </c>
-      <c r="F137" s="1" t="s">
-        <v>1623</v>
-      </c>
-      <c r="G137" s="1" t="s">
+      <c r="K137" s="1" t="s">
+        <v>875</v>
+      </c>
+      <c r="L137" s="1" t="s">
         <v>1119</v>
       </c>
-      <c r="H137" s="1" t="s">
+      <c r="M137" s="1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="N137" s="1" t="s">
         <v>1120</v>
       </c>
-      <c r="I137" s="1" t="s">
+      <c r="O137" s="1" t="s">
         <v>1121</v>
-      </c>
-      <c r="J137" s="1" t="s">
-        <v>1122</v>
-      </c>
-      <c r="K137" s="1" t="s">
-        <v>879</v>
-      </c>
-      <c r="L137" s="1" t="s">
-        <v>1123</v>
-      </c>
-      <c r="M137" s="1" t="s">
-        <v>1097</v>
-      </c>
-      <c r="N137" s="1" t="s">
-        <v>1124</v>
-      </c>
-      <c r="O137" s="1" t="s">
-        <v>1125</v>
       </c>
       <c r="P137" s="1" t="s">
         <v>28</v>
@@ -13184,46 +13184,46 @@
         <v>137</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="C138" s="1" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>1123</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>1124</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>1620</v>
+      </c>
+      <c r="G138" s="1" t="s">
+        <v>1125</v>
+      </c>
+      <c r="H138" s="1" t="s">
         <v>1126</v>
       </c>
-      <c r="D138" s="1" t="s">
+      <c r="I138" s="1" t="s">
         <v>1127</v>
       </c>
-      <c r="E138" s="1" t="s">
+      <c r="J138" s="1" t="s">
         <v>1128</v>
       </c>
-      <c r="F138" s="1" t="s">
-        <v>1624</v>
-      </c>
-      <c r="G138" s="1" t="s">
+      <c r="K138" s="1" t="s">
         <v>1129</v>
       </c>
-      <c r="H138" s="1" t="s">
+      <c r="L138" s="1" t="s">
         <v>1130</v>
       </c>
-      <c r="I138" s="1" t="s">
+      <c r="M138" s="1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="N138" s="1" t="s">
+        <v>1120</v>
+      </c>
+      <c r="O138" s="1" t="s">
         <v>1131</v>
-      </c>
-      <c r="J138" s="1" t="s">
-        <v>1132</v>
-      </c>
-      <c r="K138" s="1" t="s">
-        <v>1133</v>
-      </c>
-      <c r="L138" s="1" t="s">
-        <v>1134</v>
-      </c>
-      <c r="M138" s="1" t="s">
-        <v>1097</v>
-      </c>
-      <c r="N138" s="1" t="s">
-        <v>1124</v>
-      </c>
-      <c r="O138" s="1" t="s">
-        <v>1135</v>
       </c>
       <c r="P138" s="1" t="s">
         <v>28</v>
@@ -13234,46 +13234,46 @@
         <v>138</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="C139" s="1" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>1133</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>1622</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>1134</v>
+      </c>
+      <c r="H139" s="1" t="s">
+        <v>1135</v>
+      </c>
+      <c r="I139" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="D139" s="1" t="s">
+      <c r="J139" s="1" t="s">
         <v>1137</v>
       </c>
-      <c r="E139" s="1" t="s">
-        <v>1625</v>
-      </c>
-      <c r="F139" s="1" t="s">
-        <v>1626</v>
-      </c>
-      <c r="G139" s="1" t="s">
+      <c r="K139" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="L139" s="1" t="s">
+        <v>1130</v>
+      </c>
+      <c r="M139" s="1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="N139" s="1" t="s">
+        <v>1120</v>
+      </c>
+      <c r="O139" s="1" t="s">
         <v>1138</v>
-      </c>
-      <c r="H139" s="1" t="s">
-        <v>1139</v>
-      </c>
-      <c r="I139" s="1" t="s">
-        <v>1140</v>
-      </c>
-      <c r="J139" s="1" t="s">
-        <v>1141</v>
-      </c>
-      <c r="K139" s="1" t="s">
-        <v>778</v>
-      </c>
-      <c r="L139" s="1" t="s">
-        <v>1134</v>
-      </c>
-      <c r="M139" s="1" t="s">
-        <v>1097</v>
-      </c>
-      <c r="N139" s="1" t="s">
-        <v>1124</v>
-      </c>
-      <c r="O139" s="1" t="s">
-        <v>1142</v>
       </c>
       <c r="P139" s="1" t="s">
         <v>28</v>
@@ -13284,46 +13284,46 @@
         <v>139</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="C140" s="1" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>1140</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>1623</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>1624</v>
+      </c>
+      <c r="G140" s="1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="H140" s="1" t="s">
+        <v>1142</v>
+      </c>
+      <c r="I140" s="1" t="s">
         <v>1143</v>
       </c>
-      <c r="D140" s="1" t="s">
+      <c r="J140" s="1" t="s">
         <v>1144</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>1627</v>
-      </c>
-      <c r="F140" s="1" t="s">
-        <v>1628</v>
-      </c>
-      <c r="G140" s="1" t="s">
-        <v>1145</v>
-      </c>
-      <c r="H140" s="1" t="s">
-        <v>1146</v>
-      </c>
-      <c r="I140" s="1" t="s">
-        <v>1147</v>
-      </c>
-      <c r="J140" s="1" t="s">
-        <v>1148</v>
       </c>
       <c r="K140" s="1" t="s">
         <v>147</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>1149</v>
+        <v>1145</v>
       </c>
       <c r="M140" s="1" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="N140" s="1" t="s">
-        <v>1124</v>
+        <v>1120</v>
       </c>
       <c r="O140" s="1" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="P140" s="1" t="s">
         <v>28</v>
@@ -13334,49 +13334,49 @@
         <v>140</v>
       </c>
       <c r="B141" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>1149</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>1625</v>
+      </c>
+      <c r="G141" s="1" t="s">
+        <v>1150</v>
+      </c>
+      <c r="H141" s="1" t="s">
         <v>1151</v>
       </c>
-      <c r="C141" s="1" t="s">
+      <c r="I141" s="1" t="s">
         <v>1152</v>
       </c>
-      <c r="D141" s="1" t="s">
+      <c r="J141" s="1" t="s">
         <v>1153</v>
       </c>
-      <c r="E141" s="1" t="s">
-        <v>1371</v>
-      </c>
-      <c r="F141" s="1" t="s">
-        <v>1629</v>
-      </c>
-      <c r="G141" s="1" t="s">
+      <c r="K141" s="1" t="s">
+        <v>875</v>
+      </c>
+      <c r="L141" s="1" t="s">
         <v>1154</v>
       </c>
-      <c r="H141" s="1" t="s">
+      <c r="M141" s="1" t="s">
         <v>1155</v>
       </c>
-      <c r="I141" s="1" t="s">
+      <c r="N141" s="1" t="s">
         <v>1156</v>
       </c>
-      <c r="J141" s="1" t="s">
+      <c r="O141" s="1" t="s">
         <v>1157</v>
       </c>
-      <c r="K141" s="1" t="s">
-        <v>879</v>
-      </c>
-      <c r="L141" s="1" t="s">
-        <v>1158</v>
-      </c>
-      <c r="M141" s="1" t="s">
-        <v>1159</v>
-      </c>
-      <c r="N141" s="1" t="s">
-        <v>1160</v>
-      </c>
-      <c r="O141" s="1" t="s">
-        <v>1161</v>
-      </c>
       <c r="P141" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="142" spans="1:16" ht="204.75" x14ac:dyDescent="0.25">
@@ -13384,49 +13384,49 @@
         <v>141</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>1151</v>
+        <v>1147</v>
       </c>
       <c r="C142" s="1" t="s">
+        <v>1158</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>1159</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>1626</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>1627</v>
+      </c>
+      <c r="G142" s="1" t="s">
+        <v>1160</v>
+      </c>
+      <c r="H142" s="1" t="s">
+        <v>1161</v>
+      </c>
+      <c r="I142" s="1" t="s">
         <v>1162</v>
       </c>
-      <c r="D142" s="1" t="s">
+      <c r="J142" s="1" t="s">
         <v>1163</v>
-      </c>
-      <c r="E142" s="1" t="s">
-        <v>1630</v>
-      </c>
-      <c r="F142" s="1" t="s">
-        <v>1631</v>
-      </c>
-      <c r="G142" s="1" t="s">
-        <v>1164</v>
-      </c>
-      <c r="H142" s="1" t="s">
-        <v>1165</v>
-      </c>
-      <c r="I142" s="1" t="s">
-        <v>1166</v>
-      </c>
-      <c r="J142" s="1" t="s">
-        <v>1167</v>
       </c>
       <c r="K142" s="1" t="s">
         <v>186</v>
       </c>
       <c r="L142" s="1" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="M142" s="1" t="s">
-        <v>1159</v>
+        <v>1155</v>
       </c>
       <c r="N142" s="1" t="s">
-        <v>1169</v>
+        <v>1165</v>
       </c>
       <c r="O142" s="1" t="s">
-        <v>1170</v>
+        <v>1166</v>
       </c>
       <c r="P142" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="143" spans="1:16" ht="204.75" x14ac:dyDescent="0.25">
@@ -13434,46 +13434,46 @@
         <v>142</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>1151</v>
+        <v>1147</v>
       </c>
       <c r="C143" s="1" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>1168</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>1628</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>1629</v>
+      </c>
+      <c r="G143" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="H143" s="1" t="s">
+        <v>1170</v>
+      </c>
+      <c r="I143" s="1" t="s">
         <v>1171</v>
       </c>
-      <c r="D143" s="1" t="s">
-        <v>1172</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>1632</v>
-      </c>
-      <c r="F143" s="1" t="s">
-        <v>1633</v>
-      </c>
-      <c r="G143" s="1" t="s">
-        <v>1173</v>
-      </c>
-      <c r="H143" s="1" t="s">
-        <v>1174</v>
-      </c>
-      <c r="I143" s="1" t="s">
-        <v>1175</v>
-      </c>
       <c r="J143" s="1" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="K143" s="1" t="s">
         <v>265</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
       <c r="M143" s="1" t="s">
-        <v>1159</v>
+        <v>1155</v>
       </c>
       <c r="N143" s="1" t="s">
-        <v>1177</v>
+        <v>1173</v>
       </c>
       <c r="O143" s="1" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
       <c r="P143" s="1" t="s">
         <v>28</v>
@@ -13484,46 +13484,46 @@
         <v>143</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>1151</v>
+        <v>1147</v>
       </c>
       <c r="C144" s="1" t="s">
+        <v>1175</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>1176</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>1630</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>1631</v>
+      </c>
+      <c r="G144" s="1" t="s">
+        <v>1177</v>
+      </c>
+      <c r="H144" s="1" t="s">
+        <v>1178</v>
+      </c>
+      <c r="I144" s="1" t="s">
         <v>1179</v>
       </c>
-      <c r="D144" s="1" t="s">
+      <c r="J144" s="1" t="s">
         <v>1180</v>
-      </c>
-      <c r="E144" s="1" t="s">
-        <v>1634</v>
-      </c>
-      <c r="F144" s="1" t="s">
-        <v>1635</v>
-      </c>
-      <c r="G144" s="1" t="s">
-        <v>1181</v>
-      </c>
-      <c r="H144" s="1" t="s">
-        <v>1182</v>
-      </c>
-      <c r="I144" s="1" t="s">
-        <v>1183</v>
-      </c>
-      <c r="J144" s="1" t="s">
-        <v>1184</v>
       </c>
       <c r="K144" s="1" t="s">
         <v>331</v>
       </c>
       <c r="L144" s="1" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="M144" s="1" t="s">
-        <v>1159</v>
+        <v>1155</v>
       </c>
       <c r="N144" s="1" t="s">
-        <v>1186</v>
+        <v>1182</v>
       </c>
       <c r="O144" s="1" t="s">
-        <v>1187</v>
+        <v>1183</v>
       </c>
       <c r="P144" s="1" t="s">
         <v>28</v>
@@ -13534,49 +13534,49 @@
         <v>144</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>1151</v>
+        <v>1147</v>
       </c>
       <c r="C145" s="1" t="s">
+        <v>1184</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>1185</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>1632</v>
+      </c>
+      <c r="G145" s="1" t="s">
+        <v>1186</v>
+      </c>
+      <c r="H145" s="1" t="s">
+        <v>1187</v>
+      </c>
+      <c r="I145" s="1" t="s">
+        <v>1162</v>
+      </c>
+      <c r="J145" s="1" t="s">
         <v>1188</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>1189</v>
-      </c>
-      <c r="E145" s="1" t="s">
-        <v>1372</v>
-      </c>
-      <c r="F145" s="1" t="s">
-        <v>1636</v>
-      </c>
-      <c r="G145" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="H145" s="1" t="s">
-        <v>1191</v>
-      </c>
-      <c r="I145" s="1" t="s">
-        <v>1166</v>
-      </c>
-      <c r="J145" s="1" t="s">
-        <v>1192</v>
       </c>
       <c r="K145" s="1" t="s">
         <v>147</v>
       </c>
       <c r="L145" s="1" t="s">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="M145" s="1" t="s">
-        <v>1159</v>
+        <v>1155</v>
       </c>
       <c r="N145" s="1" t="s">
-        <v>1186</v>
+        <v>1182</v>
       </c>
       <c r="O145" s="1" t="s">
-        <v>1194</v>
+        <v>1190</v>
       </c>
       <c r="P145" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="146" spans="1:16" ht="204.75" x14ac:dyDescent="0.25">
@@ -13584,49 +13584,49 @@
         <v>145</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>1151</v>
+        <v>1147</v>
       </c>
       <c r="C146" s="1" t="s">
+        <v>1191</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>1633</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>1634</v>
+      </c>
+      <c r="G146" s="1" t="s">
+        <v>1193</v>
+      </c>
+      <c r="H146" s="1" t="s">
+        <v>1194</v>
+      </c>
+      <c r="I146" s="1" t="s">
+        <v>1162</v>
+      </c>
+      <c r="J146" s="1" t="s">
+        <v>1188</v>
+      </c>
+      <c r="K146" s="1" t="s">
+        <v>875</v>
+      </c>
+      <c r="L146" s="1" t="s">
         <v>1195</v>
       </c>
-      <c r="D146" s="1" t="s">
+      <c r="M146" s="1" t="s">
+        <v>1155</v>
+      </c>
+      <c r="N146" s="1" t="s">
+        <v>1182</v>
+      </c>
+      <c r="O146" s="1" t="s">
         <v>1196</v>
       </c>
-      <c r="E146" s="1" t="s">
-        <v>1637</v>
-      </c>
-      <c r="F146" s="1" t="s">
-        <v>1638</v>
-      </c>
-      <c r="G146" s="1" t="s">
-        <v>1197</v>
-      </c>
-      <c r="H146" s="1" t="s">
-        <v>1198</v>
-      </c>
-      <c r="I146" s="1" t="s">
-        <v>1166</v>
-      </c>
-      <c r="J146" s="1" t="s">
-        <v>1192</v>
-      </c>
-      <c r="K146" s="1" t="s">
-        <v>879</v>
-      </c>
-      <c r="L146" s="1" t="s">
-        <v>1199</v>
-      </c>
-      <c r="M146" s="1" t="s">
-        <v>1159</v>
-      </c>
-      <c r="N146" s="1" t="s">
-        <v>1186</v>
-      </c>
-      <c r="O146" s="1" t="s">
-        <v>1200</v>
-      </c>
       <c r="P146" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="147" spans="1:16" ht="252" x14ac:dyDescent="0.25">
@@ -13634,49 +13634,49 @@
         <v>146</v>
       </c>
       <c r="B147" s="1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>1198</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>1369</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>1635</v>
+      </c>
+      <c r="G147" s="1" t="s">
+        <v>1200</v>
+      </c>
+      <c r="H147" s="1" t="s">
         <v>1201</v>
       </c>
-      <c r="C147" s="1" t="s">
+      <c r="I147" s="1" t="s">
         <v>1202</v>
       </c>
-      <c r="D147" s="1" t="s">
+      <c r="J147" s="1" t="s">
         <v>1203</v>
       </c>
-      <c r="E147" s="1" t="s">
-        <v>1373</v>
-      </c>
-      <c r="F147" s="1" t="s">
-        <v>1639</v>
-      </c>
-      <c r="G147" s="1" t="s">
+      <c r="K147" s="1" t="s">
         <v>1204</v>
       </c>
-      <c r="H147" s="1" t="s">
+      <c r="L147" s="1" t="s">
         <v>1205</v>
       </c>
-      <c r="I147" s="1" t="s">
+      <c r="M147" s="1" t="s">
         <v>1206</v>
       </c>
-      <c r="J147" s="1" t="s">
+      <c r="N147" s="1" t="s">
         <v>1207</v>
       </c>
-      <c r="K147" s="1" t="s">
+      <c r="O147" s="1" t="s">
         <v>1208</v>
       </c>
-      <c r="L147" s="1" t="s">
-        <v>1209</v>
-      </c>
-      <c r="M147" s="1" t="s">
-        <v>1210</v>
-      </c>
-      <c r="N147" s="1" t="s">
-        <v>1211</v>
-      </c>
-      <c r="O147" s="1" t="s">
-        <v>1212</v>
-      </c>
       <c r="P147" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="148" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -13684,49 +13684,49 @@
         <v>147</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>1201</v>
+        <v>1197</v>
       </c>
       <c r="C148" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>1636</v>
+      </c>
+      <c r="G148" s="1" t="s">
+        <v>1211</v>
+      </c>
+      <c r="H148" s="1" t="s">
+        <v>1212</v>
+      </c>
+      <c r="I148" s="1" t="s">
         <v>1213</v>
       </c>
-      <c r="D148" s="1" t="s">
+      <c r="J148" s="1" t="s">
+        <v>1203</v>
+      </c>
+      <c r="K148" s="1" t="s">
         <v>1214</v>
       </c>
-      <c r="E148" s="1" t="s">
-        <v>1374</v>
-      </c>
-      <c r="F148" s="1" t="s">
-        <v>1640</v>
-      </c>
-      <c r="G148" s="1" t="s">
+      <c r="L148" s="1" t="s">
         <v>1215</v>
       </c>
-      <c r="H148" s="1" t="s">
+      <c r="M148" s="1" t="s">
+        <v>1206</v>
+      </c>
+      <c r="N148" s="1" t="s">
         <v>1216</v>
       </c>
-      <c r="I148" s="1" t="s">
+      <c r="O148" s="1" t="s">
         <v>1217</v>
       </c>
-      <c r="J148" s="1" t="s">
-        <v>1207</v>
-      </c>
-      <c r="K148" s="1" t="s">
-        <v>1218</v>
-      </c>
-      <c r="L148" s="1" t="s">
-        <v>1219</v>
-      </c>
-      <c r="M148" s="1" t="s">
-        <v>1210</v>
-      </c>
-      <c r="N148" s="1" t="s">
-        <v>1220</v>
-      </c>
-      <c r="O148" s="1" t="s">
-        <v>1221</v>
-      </c>
       <c r="P148" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="149" spans="1:16" ht="409.5" x14ac:dyDescent="0.25">
@@ -13734,49 +13734,49 @@
         <v>148</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>1201</v>
+        <v>1197</v>
       </c>
       <c r="C149" s="1" t="s">
+        <v>1218</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>1371</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>1372</v>
+      </c>
+      <c r="G149" s="1" t="s">
+        <v>1220</v>
+      </c>
+      <c r="H149" s="1" t="s">
+        <v>1221</v>
+      </c>
+      <c r="I149" s="1" t="s">
         <v>1222</v>
       </c>
-      <c r="D149" s="1" t="s">
+      <c r="J149" s="1" t="s">
         <v>1223</v>
       </c>
-      <c r="E149" s="1" t="s">
-        <v>1375</v>
-      </c>
-      <c r="F149" s="1" t="s">
-        <v>1376</v>
-      </c>
-      <c r="G149" s="1" t="s">
+      <c r="K149" s="1" t="s">
+        <v>986</v>
+      </c>
+      <c r="L149" s="1" t="s">
         <v>1224</v>
       </c>
-      <c r="H149" s="1" t="s">
+      <c r="M149" s="1" t="s">
+        <v>1206</v>
+      </c>
+      <c r="N149" s="1" t="s">
         <v>1225</v>
       </c>
-      <c r="I149" s="1" t="s">
+      <c r="O149" s="1" t="s">
         <v>1226</v>
       </c>
-      <c r="J149" s="1" t="s">
-        <v>1227</v>
-      </c>
-      <c r="K149" s="1" t="s">
-        <v>990</v>
-      </c>
-      <c r="L149" s="1" t="s">
-        <v>1228</v>
-      </c>
-      <c r="M149" s="1" t="s">
-        <v>1210</v>
-      </c>
-      <c r="N149" s="1" t="s">
-        <v>1229</v>
-      </c>
-      <c r="O149" s="1" t="s">
-        <v>1230</v>
-      </c>
       <c r="P149" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="150" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -13784,46 +13784,46 @@
         <v>149</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>1201</v>
+        <v>1197</v>
       </c>
       <c r="C150" s="1" t="s">
+        <v>1227</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>1228</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>1229</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>1637</v>
+      </c>
+      <c r="G150" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="H150" s="1" t="s">
         <v>1231</v>
       </c>
-      <c r="D150" s="1" t="s">
+      <c r="I150" s="1" t="s">
         <v>1232</v>
       </c>
-      <c r="E150" s="1" t="s">
+      <c r="J150" s="1" t="s">
+        <v>994</v>
+      </c>
+      <c r="K150" s="1" t="s">
+        <v>986</v>
+      </c>
+      <c r="L150" s="1" t="s">
         <v>1233</v>
       </c>
-      <c r="F150" s="1" t="s">
-        <v>1641</v>
-      </c>
-      <c r="G150" s="1" t="s">
+      <c r="M150" s="1" t="s">
+        <v>1206</v>
+      </c>
+      <c r="N150" s="1" t="s">
         <v>1234</v>
       </c>
-      <c r="H150" s="1" t="s">
+      <c r="O150" s="1" t="s">
         <v>1235</v>
-      </c>
-      <c r="I150" s="1" t="s">
-        <v>1236</v>
-      </c>
-      <c r="J150" s="1" t="s">
-        <v>998</v>
-      </c>
-      <c r="K150" s="1" t="s">
-        <v>990</v>
-      </c>
-      <c r="L150" s="1" t="s">
-        <v>1237</v>
-      </c>
-      <c r="M150" s="1" t="s">
-        <v>1210</v>
-      </c>
-      <c r="N150" s="1" t="s">
-        <v>1238</v>
-      </c>
-      <c r="O150" s="1" t="s">
-        <v>1239</v>
       </c>
       <c r="P150" s="1" t="s">
         <v>28</v>
@@ -13834,46 +13834,46 @@
         <v>150</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>1201</v>
+        <v>1197</v>
       </c>
       <c r="C151" s="1" t="s">
+        <v>1236</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>1237</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>1638</v>
+      </c>
+      <c r="G151" s="1" t="s">
+        <v>1239</v>
+      </c>
+      <c r="H151" s="1" t="s">
         <v>1240</v>
       </c>
-      <c r="D151" s="1" t="s">
+      <c r="I151" s="1" t="s">
         <v>1241</v>
       </c>
-      <c r="E151" s="1" t="s">
+      <c r="J151" s="1" t="s">
         <v>1242</v>
       </c>
-      <c r="F151" s="1" t="s">
-        <v>1642</v>
-      </c>
-      <c r="G151" s="1" t="s">
+      <c r="K151" s="1" t="s">
         <v>1243</v>
       </c>
-      <c r="H151" s="1" t="s">
+      <c r="L151" s="1" t="s">
         <v>1244</v>
       </c>
-      <c r="I151" s="1" t="s">
+      <c r="M151" s="1" t="s">
+        <v>1206</v>
+      </c>
+      <c r="N151" s="1" t="s">
+        <v>1234</v>
+      </c>
+      <c r="O151" s="1" t="s">
         <v>1245</v>
-      </c>
-      <c r="J151" s="1" t="s">
-        <v>1246</v>
-      </c>
-      <c r="K151" s="1" t="s">
-        <v>1247</v>
-      </c>
-      <c r="L151" s="1" t="s">
-        <v>1248</v>
-      </c>
-      <c r="M151" s="1" t="s">
-        <v>1210</v>
-      </c>
-      <c r="N151" s="1" t="s">
-        <v>1238</v>
-      </c>
-      <c r="O151" s="1" t="s">
-        <v>1249</v>
       </c>
       <c r="P151" s="1" t="s">
         <v>28</v>
@@ -13884,46 +13884,46 @@
         <v>151</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>1201</v>
+        <v>1197</v>
       </c>
       <c r="C152" s="1" t="s">
+        <v>1246</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>1247</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>1639</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>1640</v>
+      </c>
+      <c r="G152" s="1" t="s">
+        <v>1248</v>
+      </c>
+      <c r="H152" s="1" t="s">
+        <v>1249</v>
+      </c>
+      <c r="I152" s="1" t="s">
         <v>1250</v>
       </c>
-      <c r="D152" s="1" t="s">
+      <c r="J152" s="1" t="s">
         <v>1251</v>
       </c>
-      <c r="E152" s="1" t="s">
-        <v>1643</v>
-      </c>
-      <c r="F152" s="1" t="s">
-        <v>1644</v>
-      </c>
-      <c r="G152" s="1" t="s">
+      <c r="K152" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="L152" s="1" t="s">
         <v>1252</v>
       </c>
-      <c r="H152" s="1" t="s">
+      <c r="M152" s="1" t="s">
+        <v>1206</v>
+      </c>
+      <c r="N152" s="1" t="s">
+        <v>1234</v>
+      </c>
+      <c r="O152" s="1" t="s">
         <v>1253</v>
-      </c>
-      <c r="I152" s="1" t="s">
-        <v>1254</v>
-      </c>
-      <c r="J152" s="1" t="s">
-        <v>1255</v>
-      </c>
-      <c r="K152" s="1" t="s">
-        <v>634</v>
-      </c>
-      <c r="L152" s="1" t="s">
-        <v>1256</v>
-      </c>
-      <c r="M152" s="1" t="s">
-        <v>1210</v>
-      </c>
-      <c r="N152" s="1" t="s">
-        <v>1238</v>
-      </c>
-      <c r="O152" s="1" t="s">
-        <v>1257</v>
       </c>
       <c r="P152" s="1" t="s">
         <v>28</v>
@@ -13934,49 +13934,49 @@
         <v>152</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>1201</v>
+        <v>1197</v>
       </c>
       <c r="C153" s="1" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>1340</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>1641</v>
+      </c>
+      <c r="G153" s="1" t="s">
+        <v>1341</v>
+      </c>
+      <c r="H153" s="1" t="s">
+        <v>1256</v>
+      </c>
+      <c r="I153" s="1" t="s">
+        <v>1335</v>
+      </c>
+      <c r="J153" s="1" t="s">
+        <v>1334</v>
+      </c>
+      <c r="K153" s="1" t="s">
+        <v>1204</v>
+      </c>
+      <c r="L153" s="1" t="s">
+        <v>1257</v>
+      </c>
+      <c r="M153" s="1" t="s">
+        <v>1206</v>
+      </c>
+      <c r="N153" s="1" t="s">
+        <v>1234</v>
+      </c>
+      <c r="O153" s="1" t="s">
         <v>1258</v>
       </c>
-      <c r="D153" s="1" t="s">
-        <v>1259</v>
-      </c>
-      <c r="E153" s="1" t="s">
-        <v>1344</v>
-      </c>
-      <c r="F153" s="1" t="s">
-        <v>1645</v>
-      </c>
-      <c r="G153" s="1" t="s">
-        <v>1345</v>
-      </c>
-      <c r="H153" s="1" t="s">
-        <v>1260</v>
-      </c>
-      <c r="I153" s="1" t="s">
-        <v>1339</v>
-      </c>
-      <c r="J153" s="1" t="s">
-        <v>1338</v>
-      </c>
-      <c r="K153" s="1" t="s">
-        <v>1208</v>
-      </c>
-      <c r="L153" s="1" t="s">
-        <v>1261</v>
-      </c>
-      <c r="M153" s="1" t="s">
-        <v>1210</v>
-      </c>
-      <c r="N153" s="1" t="s">
-        <v>1238</v>
-      </c>
-      <c r="O153" s="1" t="s">
-        <v>1262</v>
-      </c>
       <c r="P153" s="1" t="s">
-        <v>1330</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="154" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -13984,46 +13984,46 @@
         <v>153</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>1201</v>
+        <v>1197</v>
       </c>
       <c r="C154" s="1" t="s">
+        <v>1259</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>1260</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>1642</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>1643</v>
+      </c>
+      <c r="G154" s="1" t="s">
+        <v>1261</v>
+      </c>
+      <c r="H154" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="I154" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="D154" s="1" t="s">
+      <c r="J154" s="1" t="s">
         <v>1264</v>
       </c>
-      <c r="E154" s="1" t="s">
-        <v>1646</v>
-      </c>
-      <c r="F154" s="1" t="s">
-        <v>1647</v>
-      </c>
-      <c r="G154" s="1" t="s">
+      <c r="K154" s="1" t="s">
         <v>1265</v>
       </c>
-      <c r="H154" s="1" t="s">
+      <c r="L154" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M154" s="1" t="s">
+        <v>1206</v>
+      </c>
+      <c r="N154" s="1" t="s">
+        <v>1234</v>
+      </c>
+      <c r="O154" s="1" t="s">
         <v>1266</v>
-      </c>
-      <c r="I154" s="1" t="s">
-        <v>1267</v>
-      </c>
-      <c r="J154" s="1" t="s">
-        <v>1268</v>
-      </c>
-      <c r="K154" s="1" t="s">
-        <v>1269</v>
-      </c>
-      <c r="L154" s="1" t="s">
-        <v>1039</v>
-      </c>
-      <c r="M154" s="1" t="s">
-        <v>1210</v>
-      </c>
-      <c r="N154" s="1" t="s">
-        <v>1238</v>
-      </c>
-      <c r="O154" s="1" t="s">
-        <v>1270</v>
       </c>
       <c r="P154" s="1" t="s">
         <v>28</v>
@@ -14034,46 +14034,46 @@
         <v>154</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>1201</v>
+        <v>1197</v>
       </c>
       <c r="C155" s="1" t="s">
+        <v>1267</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>1644</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>1645</v>
+      </c>
+      <c r="G155" s="1" t="s">
+        <v>1269</v>
+      </c>
+      <c r="H155" s="1" t="s">
+        <v>1270</v>
+      </c>
+      <c r="I155" s="1" t="s">
         <v>1271</v>
       </c>
-      <c r="D155" s="1" t="s">
+      <c r="J155" s="1" t="s">
         <v>1272</v>
       </c>
-      <c r="E155" s="1" t="s">
-        <v>1648</v>
-      </c>
-      <c r="F155" s="1" t="s">
-        <v>1649</v>
-      </c>
-      <c r="G155" s="1" t="s">
+      <c r="K155" s="1" t="s">
         <v>1273</v>
       </c>
-      <c r="H155" s="1" t="s">
+      <c r="L155" s="1" t="s">
+        <v>1043</v>
+      </c>
+      <c r="M155" s="1" t="s">
+        <v>1206</v>
+      </c>
+      <c r="N155" s="1" t="s">
+        <v>1234</v>
+      </c>
+      <c r="O155" s="1" t="s">
         <v>1274</v>
-      </c>
-      <c r="I155" s="1" t="s">
-        <v>1275</v>
-      </c>
-      <c r="J155" s="1" t="s">
-        <v>1276</v>
-      </c>
-      <c r="K155" s="1" t="s">
-        <v>1277</v>
-      </c>
-      <c r="L155" s="1" t="s">
-        <v>1047</v>
-      </c>
-      <c r="M155" s="1" t="s">
-        <v>1210</v>
-      </c>
-      <c r="N155" s="1" t="s">
-        <v>1238</v>
-      </c>
-      <c r="O155" s="1" t="s">
-        <v>1278</v>
       </c>
       <c r="P155" s="1" t="s">
         <v>28</v>
@@ -14084,49 +14084,49 @@
         <v>155</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>1201</v>
+        <v>1197</v>
       </c>
       <c r="C156" s="1" t="s">
+        <v>1275</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>1276</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>1277</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>1646</v>
+      </c>
+      <c r="G156" s="1" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H156" s="1" t="s">
         <v>1279</v>
       </c>
-      <c r="D156" s="1" t="s">
+      <c r="I156" s="1" t="s">
         <v>1280</v>
       </c>
-      <c r="E156" s="1" t="s">
+      <c r="J156" s="1" t="s">
         <v>1281</v>
       </c>
-      <c r="F156" s="1" t="s">
-        <v>1650</v>
-      </c>
-      <c r="G156" s="1" t="s">
+      <c r="K156" s="1" t="s">
         <v>1282</v>
       </c>
-      <c r="H156" s="1" t="s">
+      <c r="L156" s="1" t="s">
         <v>1283</v>
       </c>
-      <c r="I156" s="1" t="s">
+      <c r="M156" s="1" t="s">
+        <v>1206</v>
+      </c>
+      <c r="N156" s="1" t="s">
+        <v>1234</v>
+      </c>
+      <c r="O156" s="1" t="s">
         <v>1284</v>
       </c>
-      <c r="J156" s="1" t="s">
-        <v>1285</v>
-      </c>
-      <c r="K156" s="1" t="s">
-        <v>1286</v>
-      </c>
-      <c r="L156" s="1" t="s">
-        <v>1287</v>
-      </c>
-      <c r="M156" s="1" t="s">
-        <v>1210</v>
-      </c>
-      <c r="N156" s="1" t="s">
-        <v>1238</v>
-      </c>
-      <c r="O156" s="1" t="s">
-        <v>1288</v>
-      </c>
       <c r="P156" s="1" t="s">
-        <v>1342</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="157" spans="1:16" ht="252" x14ac:dyDescent="0.25">
@@ -14134,46 +14134,46 @@
         <v>156</v>
       </c>
       <c r="B157" s="1" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>1286</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>1647</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>1648</v>
+      </c>
+      <c r="G157" s="1" t="s">
+        <v>1288</v>
+      </c>
+      <c r="H157" s="1" t="s">
         <v>1289</v>
       </c>
-      <c r="C157" s="1" t="s">
+      <c r="I157" s="1" t="s">
         <v>1290</v>
       </c>
-      <c r="D157" s="1" t="s">
+      <c r="J157" s="1" t="s">
         <v>1291</v>
-      </c>
-      <c r="E157" s="1" t="s">
-        <v>1651</v>
-      </c>
-      <c r="F157" s="1" t="s">
-        <v>1652</v>
-      </c>
-      <c r="G157" s="1" t="s">
-        <v>1292</v>
-      </c>
-      <c r="H157" s="1" t="s">
-        <v>1293</v>
-      </c>
-      <c r="I157" s="1" t="s">
-        <v>1294</v>
-      </c>
-      <c r="J157" s="1" t="s">
-        <v>1295</v>
       </c>
       <c r="K157" s="1" t="s">
         <v>53</v>
       </c>
       <c r="L157" s="1" t="s">
-        <v>1296</v>
+        <v>1292</v>
       </c>
       <c r="M157" s="1" t="s">
-        <v>1297</v>
+        <v>1293</v>
       </c>
       <c r="N157" s="1" t="s">
-        <v>1298</v>
+        <v>1294</v>
       </c>
       <c r="O157" s="1" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="P157" s="1" t="s">
         <v>28</v>
@@ -14184,49 +14184,49 @@
         <v>157</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>1289</v>
+        <v>1285</v>
       </c>
       <c r="C158" s="1" t="s">
+        <v>1296</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>1297</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>1336</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>1649</v>
+      </c>
+      <c r="G158" s="1" t="s">
+        <v>1337</v>
+      </c>
+      <c r="H158" s="1" t="s">
+        <v>1344</v>
+      </c>
+      <c r="I158" s="1" t="s">
+        <v>1343</v>
+      </c>
+      <c r="J158" s="1" t="s">
+        <v>1342</v>
+      </c>
+      <c r="K158" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="L158" s="1" t="s">
+        <v>1298</v>
+      </c>
+      <c r="M158" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="N158" s="1" t="s">
+        <v>1299</v>
+      </c>
+      <c r="O158" s="1" t="s">
         <v>1300</v>
       </c>
-      <c r="D158" s="1" t="s">
-        <v>1301</v>
-      </c>
-      <c r="E158" s="1" t="s">
-        <v>1340</v>
-      </c>
-      <c r="F158" s="1" t="s">
-        <v>1653</v>
-      </c>
-      <c r="G158" s="1" t="s">
-        <v>1341</v>
-      </c>
-      <c r="H158" s="1" t="s">
-        <v>1348</v>
-      </c>
-      <c r="I158" s="1" t="s">
-        <v>1347</v>
-      </c>
-      <c r="J158" s="1" t="s">
-        <v>1346</v>
-      </c>
-      <c r="K158" s="1" t="s">
-        <v>816</v>
-      </c>
-      <c r="L158" s="1" t="s">
-        <v>1302</v>
-      </c>
-      <c r="M158" s="1" t="s">
-        <v>1297</v>
-      </c>
-      <c r="N158" s="1" t="s">
-        <v>1303</v>
-      </c>
-      <c r="O158" s="1" t="s">
-        <v>1304</v>
-      </c>
       <c r="P158" s="1" t="s">
-        <v>1330</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="159" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -14234,46 +14234,46 @@
         <v>158</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>1289</v>
+        <v>1285</v>
       </c>
       <c r="C159" s="1" t="s">
+        <v>1301</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>1302</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>1650</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>1651</v>
+      </c>
+      <c r="G159" s="1" t="s">
+        <v>1303</v>
+      </c>
+      <c r="H159" s="1" t="s">
+        <v>1304</v>
+      </c>
+      <c r="I159" s="1" t="s">
         <v>1305</v>
       </c>
-      <c r="D159" s="1" t="s">
-        <v>1306</v>
-      </c>
-      <c r="E159" s="1" t="s">
-        <v>1654</v>
-      </c>
-      <c r="F159" s="1" t="s">
-        <v>1655</v>
-      </c>
-      <c r="G159" s="1" t="s">
-        <v>1307</v>
-      </c>
-      <c r="H159" s="1" t="s">
-        <v>1308</v>
-      </c>
-      <c r="I159" s="1" t="s">
-        <v>1309</v>
-      </c>
       <c r="J159" s="1" t="s">
-        <v>1295</v>
+        <v>1291</v>
       </c>
       <c r="K159" s="1" t="s">
         <v>158</v>
       </c>
       <c r="L159" s="1" t="s">
-        <v>1296</v>
+        <v>1292</v>
       </c>
       <c r="M159" s="1" t="s">
-        <v>1297</v>
+        <v>1293</v>
       </c>
       <c r="N159" s="1" t="s">
-        <v>1310</v>
+        <v>1306</v>
       </c>
       <c r="O159" s="1" t="s">
-        <v>1311</v>
+        <v>1307</v>
       </c>
       <c r="P159" s="1" t="s">
         <v>28</v>
@@ -14284,49 +14284,49 @@
         <v>159</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>1289</v>
+        <v>1285</v>
       </c>
       <c r="C160" s="1" t="s">
+        <v>1308</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>1309</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>1652</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>1653</v>
+      </c>
+      <c r="G160" s="1" t="s">
+        <v>1310</v>
+      </c>
+      <c r="H160" s="1" t="s">
+        <v>1311</v>
+      </c>
+      <c r="I160" s="1" t="s">
         <v>1312</v>
       </c>
-      <c r="D160" s="1" t="s">
+      <c r="J160" s="1" t="s">
+        <v>1291</v>
+      </c>
+      <c r="K160" s="1" t="s">
         <v>1313</v>
       </c>
-      <c r="E160" s="1" t="s">
-        <v>1656</v>
-      </c>
-      <c r="F160" s="1" t="s">
-        <v>1657</v>
-      </c>
-      <c r="G160" s="1" t="s">
+      <c r="L160" s="1" t="s">
         <v>1314</v>
       </c>
-      <c r="H160" s="1" t="s">
+      <c r="M160" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="N160" s="1" t="s">
         <v>1315</v>
       </c>
-      <c r="I160" s="1" t="s">
+      <c r="O160" s="1" t="s">
         <v>1316</v>
       </c>
-      <c r="J160" s="1" t="s">
-        <v>1295</v>
-      </c>
-      <c r="K160" s="1" t="s">
-        <v>1317</v>
-      </c>
-      <c r="L160" s="1" t="s">
-        <v>1318</v>
-      </c>
-      <c r="M160" s="1" t="s">
-        <v>1297</v>
-      </c>
-      <c r="N160" s="1" t="s">
-        <v>1319</v>
-      </c>
-      <c r="O160" s="1" t="s">
-        <v>1320</v>
-      </c>
       <c r="P160" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="161" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -14334,56 +14334,56 @@
         <v>160</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>1289</v>
+        <v>1285</v>
       </c>
       <c r="C161" s="1" t="s">
+        <v>1317</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>1318</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>1654</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>1655</v>
+      </c>
+      <c r="G161" s="1" t="s">
+        <v>1319</v>
+      </c>
+      <c r="H161" s="1" t="s">
+        <v>1320</v>
+      </c>
+      <c r="I161" s="1" t="s">
         <v>1321</v>
       </c>
-      <c r="D161" s="1" t="s">
+      <c r="J161" s="1" t="s">
         <v>1322</v>
       </c>
-      <c r="E161" s="1" t="s">
-        <v>1658</v>
-      </c>
-      <c r="F161" s="1" t="s">
-        <v>1659</v>
-      </c>
-      <c r="G161" s="1" t="s">
+      <c r="K161" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="L161" s="1" t="s">
         <v>1323</v>
       </c>
-      <c r="H161" s="1" t="s">
+      <c r="M161" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="N161" s="1" t="s">
+        <v>1315</v>
+      </c>
+      <c r="O161" s="1" t="s">
         <v>1324</v>
       </c>
-      <c r="I161" s="1" t="s">
-        <v>1325</v>
-      </c>
-      <c r="J161" s="1" t="s">
-        <v>1326</v>
-      </c>
-      <c r="K161" s="1" t="s">
-        <v>651</v>
-      </c>
-      <c r="L161" s="1" t="s">
-        <v>1327</v>
-      </c>
-      <c r="M161" s="1" t="s">
-        <v>1297</v>
-      </c>
-      <c r="N161" s="1" t="s">
-        <v>1319</v>
-      </c>
-      <c r="O161" s="1" t="s">
-        <v>1328</v>
-      </c>
       <c r="P161" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:P161" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:P1 A93:D93 A89:D89 H89:K89 M89:O89 A95:D95 A94:D94 H94:K94 M94:O94 A118:D118 A117:D117 I117:O117 A155:D155 A153:D153 K153:O153 A159:D159 A158:D158 A74:D74 A31:D31 A106:D106 A104:D104 A105:D105 A129:D129 A128:D128 A135:D135 A130:D130 A131:D131 A132:D132 A133:D133 A157:D157 A156:D156 H153 K158:O158 A8:D8 A5:D5 H5 K5 M5:O5 A6:D6 H6 K6 M6:O6 A7:D7 H7 K7 M7:O7 A30:D30 A16:D16 H16 K16 M16:O16 A81:D81 A78:D78 H78 K78 M78:O78 A79:D79 H79 K79 M79:O79 A80:D80 H80 K80 M80:O80 A84:D84 A82:D82 H82 K82 M82:O82 A83:D83 H83 K83 M83:O83 A88:D88 A85:D85 H85 K85 M85:O85 A86:D86 H86 K86 M86:O86 A87:D87 H87 K87 M87:O87 H88 K88 M88:O88 A90:D90 H90 K90 M90:O90 A91:D91 H91 K91 M91:O91 A100:D100 A96:D96 H96 K96 M96:O96 A97:D97 H97 K97 M97:O97 A98:D98 H98 K98 M98:O98 A103:D103 A101:D101 H101 K101 M101:O101 A102:D102 H102 K102 M102:O102 A109:D109 A107:D107 H107 K107 M107:O107 A108:D108 H108 K108 M108:O108 A116:D116 A110:D110 H110 K110 M110:O110 A111:D111 H111 K111 M111:O111 A112:D112 H112 K112 M112:O112 A113:D113 H113 K113 M113:O113 A114:D114 H114 K114 M114:O114 A115:D115 H115 K115 M115:O115 A124:D124 A119:D119 H119 K119 M119:O119 A120:D120 H120 K120 M120:O120 A121:D121 H121 K121 M121:O121 A122:D122 H122 K122 M122:O122 A123:D123 H123 K123 M123:O123 A126:D126 A125:D125 H125 K125 M125:O125 A127:D127 H127 K127 M127:O127 H129 K129 M129:O129 A140:D140 A136:D136 H136 K136 M136:O136 A144:D144 A141:D141 H141 K141 M141:O141 A142:D142 H142 K142 M142:O142 A152:D152 A145:D145 H145 K145 M145:O145 A146:D146 H146 K146 M146:O146 A147:D147 H147 K147 M147:O147 A148:D148 H148 K148 M148:O148 A149:D149 H149 K149 M149:O149 A161:D161 A160:D160 H160 K160 M160:O160 H161 K161 M161:O161 A77:D77 A75:D75 H75 K75 M75:O75 H81 K81 M81:O81 A15:D15 A9:D9 H9 K9 M9:O9 A4:D4 A2:D2 G2:P2 A3:D3 G3:P3 G4:P4 G8:P8 A10:D10 G10:P10 A11:D11 G11:P11 A12:D12 G12:P12 A13:D13 G13:P13 A14:D14 G14:P14 G15:P15 A17:D17 G17:P17 A18:D18 G18:P18 A19:D19 G19:P19 A20:D20 G20:P20 A21:D21 G21:P21 A22:D22 G22:P22 A23:D23 G23:P23 A24:D24 G24:P24 A25:D25 G25:P25 A26:D26 G26:P26 A27:D27 G27:P27 A28:D28 G28:P28 A29:D29 G29:P29 G30:P30 G31:O31 A32:D32 G32:P32 A33:D33 G33:P33 A34:D34 G34:P34 A35:D35 G35:P35 A36:D36 G36:P36 A37:D37 G37:P37 A38:D38 G38:P38 A39:D39 G39:P39 A40:D40 G40:P40 A41:D41 G41:P41 A42:D42 G42:P42 A43:D43 G43:P43 A44:D44 G44:P44 A45:D45 G45:P45 A46:D46 G46:P46 A47:D47 G47:P47 A48:D48 G48:P48 A49:D49 G49:P49 A50:D50 G50:P50 A51:D51 G51:P51 A52:D52 G52:P52 A53:D53 G53:P53 A54:D54 G54:P54 A55:D55 G55:P55 A56:D56 G56:P56 A57:D57 G57:P57 A58:D58 G58:P58 A59:D59 G59:P59 A60:D60 G60:P60 A61:D61 G61:P61 A62:D62 G62:P62 A63:D63 G63:P63 A64:D64 G64:P64 A65:D65 G65:P65 A66:D66 G66:P66 A67:D67 G67:P67 A68:D68 G68:P68 A69:D69 G69:P69 A70:D70 G70:P70 A71:D71 G71:P71 A72:D72 G72:P72 A73:D73 G73:P73 G74:P74 A76:D76 G76:P76 G77:P77 G84:P84 A92:D92 G92:P92 G93:P93 G95:P95 A99:D99 G99:P99 G100:P100 G103:P103 G104:O104 G105:O105 G106:P106 G109:P109 G116:P116 G118:P118 G124:P124 G126:P126 G128:O128 G130:O130 G131:O131 G132:O132 G133:O133 A134:D134 G134:P134 G135:P135 A137:D137 G137:P137 A138:D138 G138:P138 A139:D139 G139:P139 G140:P140 A143:D143 G143:P143 G144:P144 A150:D150 G150:P150 A151:D151 G151:P151 G152:P152 A154:D154 G154:P154 G155:P155 G156:O156 G157:P157 G159:P159" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:P1 A93:D93 A89:D89 H89:K89 M89:O89 A95:D95 A94:D94 H94:K94 M94:O94 A118:D118 A117:D117 I117:O117 A155:D155 A153:D153 K153:O153 A159:D159 A158:D158 A74:D74 A31:D31 A106:D106 A104:D104 A105:D105 A129:D129 A128:D128 A135:D135 A130:D130 A131:D131 A132:D132 A133:D133 A157:D157 A156:D156 H153 K158:O158 A8:D8 A5:D5 H5 K5 M5:O5 A6:D6 H6 K6 M6:O6 A7:D7 H7 K7 M7:O7 A30:D30 A16:D16 H16 K16 M16:O16 A81:D81 A78:D78 H78 K78 M78:O78 A79:D79 H79 K79 M79:O79 A80:D80 H80 K80 M80:O80 A84:D84 A82:D82 H82 K82 M82:O82 A83:D83 H83 K83 M83:O83 A88:D88 A85:D85 H85 K85 M85:O85 A86:D86 H86 K86 M86:O86 A87:D87 H87 K87 M87:O87 H88 K88 M88:O88 A90:D90 H90 K90 M90:O90 A91:D91 H91 K91 M91:O91 A100:D100 A96:D96 H96 K96 M96:O96 A97:D97 H97 K97 M97:O97 A98:D98 H98 K98 M98:O98 A103:D103 A101:D101 H101 K101 M101:O101 A102:D102 H102 K102 M102:O102 A109:D109 A107:D107 H107 K107 M107:O107 A108:D108 H108 K108 M108:O108 A116:D116 A110:D110 H110 K110 M110:O110 A111:D111 H111 K111 M111:O111 A112:D112 H112 K112 M112:O112 A113:D113 H113 K113 M113:O113 A114:D114 H114 K114 M114:O114 A115:D115 H115 K115 M115:O115 A124:D124 A119:D119 H119 K119 M119:O119 A120:D120 H120 K120 M120:O120 A121:D121 H121 K121 M121:O121 A122:D122 H122 K122 M122:O122 A123:D123 H123 K123 M123:O123 A126:D126 A125:D125 H125 K125 M125:O125 A127:D127 H127 K127 M127:O127 H129 K129 M129:O129 A140:D140 A136:D136 H136 K136 M136:O136 A144:D144 A141:D141 H141 K141 M141:O141 A142:D142 H142 K142 M142:O142 A152:D152 A145:D145 H145 K145 M145:O145 A146:D146 H146 K146 M146:O146 A147:D147 H147 K147 M147:O147 A148:D148 H148 K148 M148:O148 A149:D149 H149 K149 M149:O149 A161:D161 A160:D160 H160 K160 M160:O160 H161 K161 M161:O161 A77:D77 A75:D75 H75 K75 M75:O75 H81 K81 M81:O81 A15:D15 A9:D9 H9 K9 M9:O9 A4:D4 A2:D2 G2:P2 A3:D3 G3:P3 G4:P4 G8:P8 A10:D10 G10:P10 A11:D11 G11:P11 A12:D12 G12:P12 A13:D13 G13:P13 A14:D14 G14:P14 G15:P15 A17:D17 G17:P17 A18:D18 G18:P18 A19:D19 G19:P19 A20:D20 G20:P20 A21:D21 G21:P21 A22:D22 G22:P22 A23:D23 G23:P23 A24:D24 G24:P24 A25:D25 G25:P25 A26:D26 G26:P26 A27:D27 G27:P27 A28:D28 G28:P28 A29:D29 G29:P29 G30:P30 G31:O31 A32:D32 G32:P32 A33:D33 G33:P33 A34:D34 G34:P34 A35:D35 G35:P35 A36:D36 G36:P36 A37:D37 G37:P37 A38:D38 G38:P38 A39:D39 G39:P39 A40:D40 G40:P40 A41:D41 G41:P41 A42:D42 G42:P42 A43:D43 G43:P43 A44:B44 G44:N44 A45:D45 G45:P45 A46:B46 G46:N46 A47:D47 G47:P47 A48:D48 G48:P48 A49:D49 G49:P49 A50:D50 G50:P50 A51:D51 G51:P51 A52:D52 G52:P52 A53:D53 G53:P53 A54:D54 G54:P54 A55:D55 G55:P55 A56:D56 G56:P56 A57:D57 G57:P57 A58:D58 G58:P58 A59:D59 G59:P59 A60:D60 G60:P60 A61:D61 G61:P61 A62:D62 G62:P62 A63:D63 G63:P63 A64:D64 G64:P64 A65:D65 G65:P65 A66:D66 G66:P66 A67:D67 G67:P67 A68:D68 G68:P68 A69:D69 G69:P69 A70:D70 G70:P70 A71:D71 G71:P71 A72:D72 G72:P72 A73:D73 G73:P73 G74:P74 A76:D76 G76:P76 G77:P77 G84:P84 A92:D92 G92:P92 G93:P93 G95:P95 A99:D99 G99:P99 G100:P100 G103:P103 G104:O104 G105:O105 G106:P106 G109:P109 G116:P116 G118:P118 G124:P124 G126:P126 G128:O128 G130:O130 G131:O131 G132:O132 G133:O133 A134:D134 G134:P134 G135:P135 A137:D137 G137:P137 A138:D138 G138:P138 A139:D139 G139:P139 G140:P140 A143:D143 G143:P143 G144:P144 A150:D150 G150:P150 A151:D151 G151:P151 G152:P152 A154:D154 G154:P154 G155:P155 G156:O156 G157:P157 G159:P159 D44 P44 D46 P46" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/02_sources/extracted/design_handoff_professions_catalog/data/professions.xlsx
+++ b/02_sources/extracted/design_handoff_professions_catalog/data/professions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\рс\Desktop\ПРОФТРЕКЕР\ВЭБ СТУДИЯ сайты, графика, бренд\ИИ\сайт 160 карт\02_sources\extracted\design_handoff_professions_catalog\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79772DD5-35A0-4041-B1CC-2B6891D795CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F535A163-E949-4BDF-B262-63BF0B46BB6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4189,15 +4189,9 @@
     <t>Органы внутренних дел и ГИБДД, МЧС и пожарные части, прокуратура и суды, частные охранные организации, лесничества и заповедники.</t>
   </si>
   <si>
-    <t>Автоиспектор; Охранник; Пожарный</t>
-  </si>
-  <si>
     <t>Полицейский.jpg</t>
   </si>
   <si>
-    <t>Автоиспектор</t>
-  </si>
-  <si>
     <t>Следит за порядком на дорогах.</t>
   </si>
   <si>
@@ -4213,9 +4207,6 @@
     <t>Полицейский; Охранник; Пожарный</t>
   </si>
   <si>
-    <t>Автоиспектор.jpg</t>
-  </si>
-  <si>
     <t>Охранник</t>
   </si>
   <si>
@@ -4237,9 +4228,6 @@
     <t>35–60 тыс ₽</t>
   </si>
   <si>
-    <t>Полицейский; Автоиспектор; Пожарный</t>
-  </si>
-  <si>
     <t>Охранник.jpg</t>
   </si>
   <si>
@@ -4265,9 +4253,6 @@
   </si>
   <si>
     <t>20.01.01 Пожарный, 20.02.04 Пожарная безопасность</t>
-  </si>
-  <si>
-    <t>Полицейский; Автоиспектор; Охранник</t>
   </si>
   <si>
     <t>Пожарный.jpg</t>
@@ -5927,6 +5912,21 @@
   </si>
   <si>
     <t>специалист-в-области-учета-и-контроля-ядерных-материалов-в-области-атомной-энергетики.png</t>
+  </si>
+  <si>
+    <t>Автоинспектор</t>
+  </si>
+  <si>
+    <t>автоинспектор.png</t>
+  </si>
+  <si>
+    <t>Автоинспектор; Охранник; Пожарный</t>
+  </si>
+  <si>
+    <t>Полицейский; Автоинспектор; Пожарный</t>
+  </si>
+  <si>
+    <t>Полицейский; Автоинспектор; Охранник</t>
   </si>
 </sst>
 </file>
@@ -6393,10 +6393,10 @@
         <v>18</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>1381</v>
+        <v>1376</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>1382</v>
+        <v>1377</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>19</v>
@@ -6443,10 +6443,10 @@
         <v>30</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>1383</v>
+        <v>1378</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>1384</v>
+        <v>1379</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>31</v>
@@ -6493,10 +6493,10 @@
         <v>40</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>1385</v>
+        <v>1380</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>1386</v>
+        <v>1381</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>41</v>
@@ -6543,10 +6543,10 @@
         <v>48</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>1345</v>
+        <v>1340</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>1387</v>
+        <v>1382</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>49</v>
@@ -6576,7 +6576,7 @@
         <v>56</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="409.5" x14ac:dyDescent="0.25">
@@ -6593,10 +6593,10 @@
         <v>58</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>1347</v>
+        <v>1342</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>1388</v>
+        <v>1383</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>59</v>
@@ -6626,7 +6626,7 @@
         <v>65</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="362.25" x14ac:dyDescent="0.25">
@@ -6643,10 +6643,10 @@
         <v>67</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>1389</v>
+        <v>1384</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>68</v>
@@ -6676,7 +6676,7 @@
         <v>74</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -6693,10 +6693,10 @@
         <v>76</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>1391</v>
+        <v>1386</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>1392</v>
+        <v>1387</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>77</v>
@@ -6743,13 +6743,13 @@
         <v>84</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>1393</v>
+        <v>1388</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>1394</v>
+        <v>1389</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>1379</v>
+        <v>1374</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>85</v>
@@ -6764,7 +6764,7 @@
         <v>88</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>1380</v>
+        <v>1375</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>25</v>
@@ -6776,7 +6776,7 @@
         <v>89</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="409.5" x14ac:dyDescent="0.25">
@@ -6793,10 +6793,10 @@
         <v>91</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>1395</v>
+        <v>1390</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>1396</v>
+        <v>1391</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>92</v>
@@ -6843,10 +6843,10 @@
         <v>98</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>1397</v>
+        <v>1392</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>1398</v>
+        <v>1393</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>99</v>
@@ -6893,10 +6893,10 @@
         <v>107</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>1399</v>
+        <v>1394</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>1400</v>
+        <v>1395</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>108</v>
@@ -6943,10 +6943,10 @@
         <v>115</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>1401</v>
+        <v>1396</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>1402</v>
+        <v>1397</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>116</v>
@@ -6993,10 +6993,10 @@
         <v>123</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>1403</v>
+        <v>1398</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>1404</v>
+        <v>1399</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>124</v>
@@ -7043,10 +7043,10 @@
         <v>132</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>1405</v>
+        <v>1400</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>1406</v>
+        <v>1401</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>133</v>
@@ -7093,10 +7093,10 @@
         <v>142</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>1408</v>
+        <v>1403</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>143</v>
@@ -7126,7 +7126,7 @@
         <v>151</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="409.5" x14ac:dyDescent="0.25">
@@ -7143,10 +7143,10 @@
         <v>153</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>1409</v>
+        <v>1404</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>1410</v>
+        <v>1405</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>154</v>
@@ -7193,10 +7193,10 @@
         <v>163</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>1411</v>
+        <v>1406</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>1412</v>
+        <v>1407</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>164</v>
@@ -7243,10 +7243,10 @@
         <v>172</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>1413</v>
+        <v>1408</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>1414</v>
+        <v>1409</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>173</v>
@@ -7293,10 +7293,10 @@
         <v>181</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>1415</v>
+        <v>1410</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>1416</v>
+        <v>1411</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>182</v>
@@ -7343,10 +7343,10 @@
         <v>191</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>1417</v>
+        <v>1412</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>1418</v>
+        <v>1413</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>192</v>
@@ -7393,10 +7393,10 @@
         <v>201</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>1419</v>
+        <v>1414</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>1420</v>
+        <v>1415</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>202</v>
@@ -7443,10 +7443,10 @@
         <v>210</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>1421</v>
+        <v>1416</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>1422</v>
+        <v>1417</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>211</v>
@@ -7493,10 +7493,10 @@
         <v>219</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>1423</v>
+        <v>1418</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>1424</v>
+        <v>1419</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>220</v>
@@ -7543,10 +7543,10 @@
         <v>228</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>1425</v>
+        <v>1420</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>1426</v>
+        <v>1421</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>229</v>
@@ -7593,10 +7593,10 @@
         <v>235</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>1427</v>
+        <v>1422</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>1428</v>
+        <v>1423</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>236</v>
@@ -7643,10 +7643,10 @@
         <v>244</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>1429</v>
+        <v>1424</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>1430</v>
+        <v>1425</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>245</v>
@@ -7693,10 +7693,10 @@
         <v>252</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>1431</v>
+        <v>1426</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>1432</v>
+        <v>1427</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>253</v>
@@ -7743,10 +7743,10 @@
         <v>261</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>1433</v>
+        <v>1428</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>1434</v>
+        <v>1429</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>262</v>
@@ -7793,10 +7793,10 @@
         <v>269</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>1435</v>
+        <v>1430</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>1436</v>
+        <v>1431</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>270</v>
@@ -7846,7 +7846,7 @@
         <v>279</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>1437</v>
+        <v>1432</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>280</v>
@@ -7876,7 +7876,7 @@
         <v>286</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>1338</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="32" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -7893,10 +7893,10 @@
         <v>289</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>1438</v>
+        <v>1433</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>1439</v>
+        <v>1434</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>290</v>
@@ -7943,10 +7943,10 @@
         <v>298</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>1440</v>
+        <v>1435</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>1441</v>
+        <v>1436</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>299</v>
@@ -7993,10 +7993,10 @@
         <v>308</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>1442</v>
+        <v>1437</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>1443</v>
+        <v>1438</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>309</v>
@@ -8043,10 +8043,10 @@
         <v>317</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>1444</v>
+        <v>1439</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>1445</v>
+        <v>1440</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>318</v>
@@ -8093,10 +8093,10 @@
         <v>326</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>1446</v>
+        <v>1441</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>1447</v>
+        <v>1442</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>327</v>
@@ -8143,10 +8143,10 @@
         <v>336</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>337</v>
@@ -8193,10 +8193,10 @@
         <v>346</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>347</v>
@@ -8243,10 +8243,10 @@
         <v>355</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>356</v>
@@ -8293,10 +8293,10 @@
         <v>361</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>1454</v>
+        <v>1449</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>1455</v>
+        <v>1450</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>362</v>
@@ -8343,10 +8343,10 @@
         <v>370</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>1456</v>
+        <v>1451</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>1457</v>
+        <v>1452</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>371</v>
@@ -8393,10 +8393,10 @@
         <v>379</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>1458</v>
+        <v>1453</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>1459</v>
+        <v>1454</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>380</v>
@@ -8443,10 +8443,10 @@
         <v>385</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>1460</v>
+        <v>1455</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>1461</v>
+        <v>1456</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>386</v>
@@ -8487,16 +8487,16 @@
         <v>334</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>1656</v>
+        <v>1651</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>389</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>1462</v>
+        <v>1457</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>1463</v>
+        <v>1458</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>390</v>
@@ -8523,7 +8523,7 @@
         <v>367</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>1657</v>
+        <v>1652</v>
       </c>
       <c r="P44" s="1" t="s">
         <v>28</v>
@@ -8543,10 +8543,10 @@
         <v>393</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>1464</v>
+        <v>1459</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>1465</v>
+        <v>1460</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>394</v>
@@ -8587,16 +8587,16 @@
         <v>334</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>1658</v>
+        <v>1653</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>399</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>1466</v>
+        <v>1461</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>1467</v>
+        <v>1462</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>400</v>
@@ -8623,7 +8623,7 @@
         <v>367</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>1659</v>
+        <v>1654</v>
       </c>
       <c r="P46" s="1" t="s">
         <v>28</v>
@@ -8643,10 +8643,10 @@
         <v>405</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>1468</v>
+        <v>1463</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>1469</v>
+        <v>1464</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>406</v>
@@ -8693,10 +8693,10 @@
         <v>415</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>1470</v>
+        <v>1465</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>1471</v>
+        <v>1466</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>416</v>
@@ -8743,10 +8743,10 @@
         <v>424</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>1472</v>
+        <v>1467</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>1473</v>
+        <v>1468</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>425</v>
@@ -8793,10 +8793,10 @@
         <v>434</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>1474</v>
+        <v>1469</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>1475</v>
+        <v>1470</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>435</v>
@@ -8843,10 +8843,10 @@
         <v>442</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>1476</v>
+        <v>1471</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>1477</v>
+        <v>1472</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>443</v>
@@ -8893,10 +8893,10 @@
         <v>446</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>1478</v>
+        <v>1473</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>1479</v>
+        <v>1474</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>447</v>
@@ -8943,10 +8943,10 @@
         <v>453</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>1480</v>
+        <v>1475</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>1481</v>
+        <v>1476</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>454</v>
@@ -8996,7 +8996,7 @@
         <v>462</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>1482</v>
+        <v>1477</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>463</v>
@@ -9043,10 +9043,10 @@
         <v>470</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>1483</v>
+        <v>1478</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>1484</v>
+        <v>1479</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>471</v>
@@ -9093,10 +9093,10 @@
         <v>478</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>1485</v>
+        <v>1480</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>1486</v>
+        <v>1481</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>479</v>
@@ -9146,7 +9146,7 @@
         <v>487</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>1487</v>
+        <v>1482</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>488</v>
@@ -9193,10 +9193,10 @@
         <v>497</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>1488</v>
+        <v>1483</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>1489</v>
+        <v>1484</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>498</v>
@@ -9243,10 +9243,10 @@
         <v>505</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>1490</v>
+        <v>1485</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>1491</v>
+        <v>1486</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>506</v>
@@ -9293,10 +9293,10 @@
         <v>514</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>1492</v>
+        <v>1487</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>1493</v>
+        <v>1488</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>515</v>
@@ -9343,10 +9343,10 @@
         <v>520</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>1494</v>
+        <v>1489</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>1495</v>
+        <v>1490</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>521</v>
@@ -9393,10 +9393,10 @@
         <v>527</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>1496</v>
+        <v>1491</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>1497</v>
+        <v>1492</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>528</v>
@@ -9443,10 +9443,10 @@
         <v>533</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>1498</v>
+        <v>1493</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>1499</v>
+        <v>1494</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>534</v>
@@ -9493,10 +9493,10 @@
         <v>541</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>1500</v>
+        <v>1495</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>1501</v>
+        <v>1496</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>542</v>
@@ -9543,10 +9543,10 @@
         <v>549</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>1502</v>
+        <v>1497</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>1503</v>
+        <v>1498</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>550</v>
@@ -9593,10 +9593,10 @@
         <v>557</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>1504</v>
+        <v>1499</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>1505</v>
+        <v>1500</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>558</v>
@@ -9643,10 +9643,10 @@
         <v>566</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>1506</v>
+        <v>1501</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>1507</v>
+        <v>1502</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>567</v>
@@ -9693,10 +9693,10 @@
         <v>576</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>1508</v>
+        <v>1503</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>1509</v>
+        <v>1504</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>577</v>
@@ -9743,10 +9743,10 @@
         <v>585</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>1510</v>
+        <v>1505</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>1511</v>
+        <v>1506</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>586</v>
@@ -9793,10 +9793,10 @@
         <v>594</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>1512</v>
+        <v>1507</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>1513</v>
+        <v>1508</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>595</v>
@@ -9843,10 +9843,10 @@
         <v>603</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>1514</v>
+        <v>1509</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>1515</v>
+        <v>1510</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>604</v>
@@ -9893,10 +9893,10 @@
         <v>611</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>1516</v>
+        <v>1511</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>1517</v>
+        <v>1512</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>612</v>
@@ -9943,10 +9943,10 @@
         <v>618</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>1518</v>
+        <v>1513</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>1519</v>
+        <v>1514</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>619</v>
@@ -9993,10 +9993,10 @@
         <v>626</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>1520</v>
+        <v>1515</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>1521</v>
+        <v>1516</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>627</v>
@@ -10043,28 +10043,28 @@
         <v>634</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>1522</v>
+        <v>1517</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>1523</v>
+        <v>1518</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>1373</v>
+        <v>1368</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>635</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>1374</v>
+        <v>1369</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>1375</v>
+        <v>1370</v>
       </c>
       <c r="K75" s="1" t="s">
         <v>491</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>1376</v>
+        <v>1371</v>
       </c>
       <c r="M75" s="1" t="s">
         <v>572</v>
@@ -10076,7 +10076,7 @@
         <v>638</v>
       </c>
       <c r="P75" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="76" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -10093,10 +10093,10 @@
         <v>640</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>1524</v>
+        <v>1519</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>1525</v>
+        <v>1520</v>
       </c>
       <c r="G76" s="1" t="s">
         <v>641</v>
@@ -10143,10 +10143,10 @@
         <v>645</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>1526</v>
+        <v>1521</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>1527</v>
+        <v>1522</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>646</v>
@@ -10193,10 +10193,10 @@
         <v>652</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>1348</v>
+        <v>1343</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>1528</v>
+        <v>1523</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>653</v>
@@ -10226,7 +10226,7 @@
         <v>660</v>
       </c>
       <c r="P78" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="79" spans="1:16" ht="252" x14ac:dyDescent="0.25">
@@ -10243,10 +10243,10 @@
         <v>662</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>1349</v>
+        <v>1344</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>1529</v>
+        <v>1524</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>663</v>
@@ -10276,7 +10276,7 @@
         <v>669</v>
       </c>
       <c r="P79" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="80" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -10293,10 +10293,10 @@
         <v>671</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>1350</v>
+        <v>1345</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>1530</v>
+        <v>1525</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>672</v>
@@ -10326,7 +10326,7 @@
         <v>678</v>
       </c>
       <c r="P80" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="81" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -10343,10 +10343,10 @@
         <v>680</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>1377</v>
+        <v>1372</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>1531</v>
+        <v>1526</v>
       </c>
       <c r="G81" s="1" t="s">
         <v>681</v>
@@ -10364,7 +10364,7 @@
         <v>53</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>1378</v>
+        <v>1373</v>
       </c>
       <c r="M81" s="1" t="s">
         <v>658</v>
@@ -10376,7 +10376,7 @@
         <v>684</v>
       </c>
       <c r="P81" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="82" spans="1:16" ht="267.75" x14ac:dyDescent="0.25">
@@ -10393,10 +10393,10 @@
         <v>686</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>1532</v>
+        <v>1527</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>1533</v>
+        <v>1528</v>
       </c>
       <c r="G82" s="1" t="s">
         <v>687</v>
@@ -10426,7 +10426,7 @@
         <v>692</v>
       </c>
       <c r="P82" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="83" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -10443,10 +10443,10 @@
         <v>694</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>1534</v>
+        <v>1529</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>1535</v>
+        <v>1530</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>695</v>
@@ -10476,7 +10476,7 @@
         <v>698</v>
       </c>
       <c r="P83" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="84" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -10493,10 +10493,10 @@
         <v>700</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>1536</v>
+        <v>1531</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>1537</v>
+        <v>1532</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>701</v>
@@ -10543,10 +10543,10 @@
         <v>709</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>1538</v>
+        <v>1533</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>1539</v>
+        <v>1534</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>710</v>
@@ -10576,7 +10576,7 @@
         <v>714</v>
       </c>
       <c r="P85" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="86" spans="1:16" ht="409.5" x14ac:dyDescent="0.25">
@@ -10593,10 +10593,10 @@
         <v>716</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>1540</v>
+        <v>1535</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>1541</v>
+        <v>1536</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>717</v>
@@ -10626,7 +10626,7 @@
         <v>721</v>
       </c>
       <c r="P86" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="87" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -10643,10 +10643,10 @@
         <v>723</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>1542</v>
+        <v>1537</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>1543</v>
+        <v>1538</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>724</v>
@@ -10676,7 +10676,7 @@
         <v>728</v>
       </c>
       <c r="P87" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="88" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -10693,13 +10693,13 @@
         <v>731</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>1545</v>
+        <v>1540</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>1351</v>
+        <v>1346</v>
       </c>
       <c r="H88" s="1" t="s">
         <v>732</v>
@@ -10726,7 +10726,7 @@
         <v>739</v>
       </c>
       <c r="P88" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="89" spans="1:16" ht="252" x14ac:dyDescent="0.25">
@@ -10743,13 +10743,13 @@
         <v>741</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>1325</v>
+        <v>1320</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>1328</v>
+        <v>1323</v>
       </c>
       <c r="H89" s="1" t="s">
         <v>732</v>
@@ -10764,7 +10764,7 @@
         <v>743</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>1327</v>
+        <v>1322</v>
       </c>
       <c r="M89" s="1" t="s">
         <v>737</v>
@@ -10776,7 +10776,7 @@
         <v>745</v>
       </c>
       <c r="P89" s="1" t="s">
-        <v>1326</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="90" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -10793,10 +10793,10 @@
         <v>747</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>1547</v>
+        <v>1542</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>1548</v>
+        <v>1543</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>742</v>
@@ -10826,7 +10826,7 @@
         <v>751</v>
       </c>
       <c r="P90" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="91" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -10843,13 +10843,13 @@
         <v>753</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>1549</v>
+        <v>1544</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>1550</v>
+        <v>1545</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>1352</v>
+        <v>1347</v>
       </c>
       <c r="H91" s="1" t="s">
         <v>732</v>
@@ -10876,7 +10876,7 @@
         <v>757</v>
       </c>
       <c r="P91" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="92" spans="1:16" ht="252" x14ac:dyDescent="0.25">
@@ -10893,10 +10893,10 @@
         <v>759</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>1551</v>
+        <v>1546</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>1552</v>
+        <v>1547</v>
       </c>
       <c r="G92" s="1" t="s">
         <v>760</v>
@@ -10943,10 +10943,10 @@
         <v>765</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>1553</v>
+        <v>1548</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>1554</v>
+        <v>1549</v>
       </c>
       <c r="G93" s="1" t="s">
         <v>766</v>
@@ -10993,13 +10993,13 @@
         <v>772</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>1329</v>
+        <v>1324</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>1555</v>
+        <v>1550</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>1331</v>
+        <v>1326</v>
       </c>
       <c r="H94" s="1" t="s">
         <v>773</v>
@@ -11014,7 +11014,7 @@
         <v>774</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>1330</v>
+        <v>1325</v>
       </c>
       <c r="M94" s="1" t="s">
         <v>737</v>
@@ -11026,7 +11026,7 @@
         <v>775</v>
       </c>
       <c r="P94" s="1" t="s">
-        <v>1326</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="95" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -11043,10 +11043,10 @@
         <v>777</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>1556</v>
+        <v>1551</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>1557</v>
+        <v>1552</v>
       </c>
       <c r="G95" s="1" t="s">
         <v>778</v>
@@ -11093,10 +11093,10 @@
         <v>784</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>1353</v>
+        <v>1348</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>1558</v>
+        <v>1553</v>
       </c>
       <c r="G96" s="1" t="s">
         <v>785</v>
@@ -11126,7 +11126,7 @@
         <v>789</v>
       </c>
       <c r="P96" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="97" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -11143,10 +11143,10 @@
         <v>791</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>1354</v>
+        <v>1349</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>1559</v>
+        <v>1554</v>
       </c>
       <c r="G97" s="1" t="s">
         <v>792</v>
@@ -11176,7 +11176,7 @@
         <v>794</v>
       </c>
       <c r="P97" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="98" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -11193,10 +11193,10 @@
         <v>796</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>1355</v>
+        <v>1350</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>1560</v>
+        <v>1555</v>
       </c>
       <c r="G98" s="1" t="s">
         <v>797</v>
@@ -11226,7 +11226,7 @@
         <v>800</v>
       </c>
       <c r="P98" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="99" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -11246,7 +11246,7 @@
         <v>803</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>1561</v>
+        <v>1556</v>
       </c>
       <c r="G99" s="1" t="s">
         <v>804</v>
@@ -11293,10 +11293,10 @@
         <v>809</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>1562</v>
+        <v>1557</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>1563</v>
+        <v>1558</v>
       </c>
       <c r="G100" s="1" t="s">
         <v>810</v>
@@ -11343,10 +11343,10 @@
         <v>817</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>1356</v>
+        <v>1351</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>1564</v>
+        <v>1559</v>
       </c>
       <c r="G101" s="1" t="s">
         <v>818</v>
@@ -11376,7 +11376,7 @@
         <v>825</v>
       </c>
       <c r="P101" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="102" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -11393,10 +11393,10 @@
         <v>827</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>1357</v>
+        <v>1352</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>1565</v>
+        <v>1560</v>
       </c>
       <c r="G102" s="1" t="s">
         <v>828</v>
@@ -11426,7 +11426,7 @@
         <v>834</v>
       </c>
       <c r="P102" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="103" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -11443,10 +11443,10 @@
         <v>836</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>1566</v>
+        <v>1561</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="G103" s="1" t="s">
         <v>837</v>
@@ -11493,10 +11493,10 @@
         <v>842</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>1568</v>
+        <v>1563</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>1569</v>
+        <v>1564</v>
       </c>
       <c r="G104" s="1" t="s">
         <v>843</v>
@@ -11526,7 +11526,7 @@
         <v>849</v>
       </c>
       <c r="P104" s="1" t="s">
-        <v>1338</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="105" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -11543,10 +11543,10 @@
         <v>851</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>1570</v>
+        <v>1565</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>1571</v>
+        <v>1566</v>
       </c>
       <c r="G105" s="1" t="s">
         <v>852</v>
@@ -11576,7 +11576,7 @@
         <v>857</v>
       </c>
       <c r="P105" s="1" t="s">
-        <v>1338</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="106" spans="1:16" ht="204.75" x14ac:dyDescent="0.25">
@@ -11593,10 +11593,10 @@
         <v>860</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>1572</v>
+        <v>1567</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>1573</v>
+        <v>1568</v>
       </c>
       <c r="G106" s="1" t="s">
         <v>861</v>
@@ -11643,10 +11643,10 @@
         <v>870</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>1574</v>
+        <v>1569</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>1575</v>
+        <v>1570</v>
       </c>
       <c r="G107" s="1" t="s">
         <v>871</v>
@@ -11676,7 +11676,7 @@
         <v>878</v>
       </c>
       <c r="P107" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="108" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -11693,10 +11693,10 @@
         <v>880</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>1576</v>
+        <v>1571</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>1577</v>
+        <v>1572</v>
       </c>
       <c r="G108" s="1" t="s">
         <v>881</v>
@@ -11726,7 +11726,7 @@
         <v>885</v>
       </c>
       <c r="P108" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="109" spans="1:16" ht="189" x14ac:dyDescent="0.25">
@@ -11743,10 +11743,10 @@
         <v>887</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>1578</v>
+        <v>1573</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>1579</v>
+        <v>1574</v>
       </c>
       <c r="G109" s="1" t="s">
         <v>888</v>
@@ -11793,10 +11793,10 @@
         <v>893</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>1580</v>
+        <v>1575</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>1581</v>
+        <v>1576</v>
       </c>
       <c r="G110" s="1" t="s">
         <v>894</v>
@@ -11826,7 +11826,7 @@
         <v>900</v>
       </c>
       <c r="P110" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="111" spans="1:16" ht="189" x14ac:dyDescent="0.25">
@@ -11843,10 +11843,10 @@
         <v>902</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>1358</v>
+        <v>1353</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>1582</v>
+        <v>1577</v>
       </c>
       <c r="G111" s="1" t="s">
         <v>903</v>
@@ -11876,7 +11876,7 @@
         <v>907</v>
       </c>
       <c r="P111" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="112" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -11893,10 +11893,10 @@
         <v>909</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>1359</v>
+        <v>1354</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>1583</v>
+        <v>1578</v>
       </c>
       <c r="G112" s="1" t="s">
         <v>910</v>
@@ -11926,7 +11926,7 @@
         <v>914</v>
       </c>
       <c r="P112" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="113" spans="1:16" ht="204.75" x14ac:dyDescent="0.25">
@@ -11943,10 +11943,10 @@
         <v>916</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>1584</v>
+        <v>1579</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>1585</v>
+        <v>1580</v>
       </c>
       <c r="G113" s="1" t="s">
         <v>917</v>
@@ -11976,7 +11976,7 @@
         <v>922</v>
       </c>
       <c r="P113" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="114" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -11993,10 +11993,10 @@
         <v>924</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>1360</v>
+        <v>1355</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>1586</v>
+        <v>1581</v>
       </c>
       <c r="G114" s="1" t="s">
         <v>925</v>
@@ -12026,7 +12026,7 @@
         <v>930</v>
       </c>
       <c r="P114" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="115" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -12043,10 +12043,10 @@
         <v>932</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>1587</v>
+        <v>1582</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>1588</v>
+        <v>1583</v>
       </c>
       <c r="G115" s="1" t="s">
         <v>933</v>
@@ -12076,7 +12076,7 @@
         <v>939</v>
       </c>
       <c r="P115" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="116" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -12093,10 +12093,10 @@
         <v>941</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>1590</v>
+        <v>1585</v>
       </c>
       <c r="G116" s="1" t="s">
         <v>942</v>
@@ -12143,16 +12143,16 @@
         <v>948</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>1332</v>
+        <v>1327</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>1591</v>
+        <v>1586</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>1333</v>
+        <v>1328</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>1339</v>
+        <v>1334</v>
       </c>
       <c r="I117" s="1" t="s">
         <v>949</v>
@@ -12176,7 +12176,7 @@
         <v>953</v>
       </c>
       <c r="P117" s="1" t="s">
-        <v>1326</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="118" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -12193,10 +12193,10 @@
         <v>955</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>1592</v>
+        <v>1587</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>1593</v>
+        <v>1588</v>
       </c>
       <c r="G118" s="1" t="s">
         <v>956</v>
@@ -12243,10 +12243,10 @@
         <v>963</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>1361</v>
+        <v>1356</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>1594</v>
+        <v>1589</v>
       </c>
       <c r="G119" s="1" t="s">
         <v>964</v>
@@ -12276,7 +12276,7 @@
         <v>969</v>
       </c>
       <c r="P119" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="120" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -12293,10 +12293,10 @@
         <v>971</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>1362</v>
+        <v>1357</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>1595</v>
+        <v>1590</v>
       </c>
       <c r="G120" s="1" t="s">
         <v>972</v>
@@ -12326,7 +12326,7 @@
         <v>975</v>
       </c>
       <c r="P120" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="121" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -12343,10 +12343,10 @@
         <v>977</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>1363</v>
+        <v>1358</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>1596</v>
+        <v>1591</v>
       </c>
       <c r="G121" s="1" t="s">
         <v>978</v>
@@ -12376,7 +12376,7 @@
         <v>981</v>
       </c>
       <c r="P121" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="122" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -12393,10 +12393,10 @@
         <v>983</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>1597</v>
+        <v>1592</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>1598</v>
+        <v>1593</v>
       </c>
       <c r="G122" s="1" t="s">
         <v>984</v>
@@ -12426,7 +12426,7 @@
         <v>988</v>
       </c>
       <c r="P122" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="123" spans="1:16" ht="204.75" x14ac:dyDescent="0.25">
@@ -12443,10 +12443,10 @@
         <v>990</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>1599</v>
+        <v>1594</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>1600</v>
+        <v>1595</v>
       </c>
       <c r="G123" s="1" t="s">
         <v>991</v>
@@ -12476,7 +12476,7 @@
         <v>997</v>
       </c>
       <c r="P123" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="124" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -12493,10 +12493,10 @@
         <v>999</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>1601</v>
+        <v>1596</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>1602</v>
+        <v>1597</v>
       </c>
       <c r="G124" s="1" t="s">
         <v>1000</v>
@@ -12543,10 +12543,10 @@
         <v>1007</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>1603</v>
+        <v>1598</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>1604</v>
+        <v>1599</v>
       </c>
       <c r="G125" s="1" t="s">
         <v>1008</v>
@@ -12576,7 +12576,7 @@
         <v>1012</v>
       </c>
       <c r="P125" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="126" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -12596,7 +12596,7 @@
         <v>1015</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>1605</v>
+        <v>1600</v>
       </c>
       <c r="G126" s="1" t="s">
         <v>1016</v>
@@ -12643,10 +12643,10 @@
         <v>1023</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>1364</v>
+        <v>1359</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>1606</v>
+        <v>1601</v>
       </c>
       <c r="G127" s="1" t="s">
         <v>1024</v>
@@ -12664,7 +12664,7 @@
         <v>787</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>1365</v>
+        <v>1360</v>
       </c>
       <c r="M127" s="1" t="s">
         <v>866</v>
@@ -12676,7 +12676,7 @@
         <v>1027</v>
       </c>
       <c r="P127" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="128" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -12696,7 +12696,7 @@
         <v>1030</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>1607</v>
+        <v>1602</v>
       </c>
       <c r="G128" s="1" t="s">
         <v>1031</v>
@@ -12726,7 +12726,7 @@
         <v>1036</v>
       </c>
       <c r="P128" s="1" t="s">
-        <v>1338</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="129" spans="1:16" ht="204.75" x14ac:dyDescent="0.25">
@@ -12743,10 +12743,10 @@
         <v>1039</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>1366</v>
+        <v>1361</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>1608</v>
+        <v>1603</v>
       </c>
       <c r="G129" s="1" t="s">
         <v>1040</v>
@@ -12776,7 +12776,7 @@
         <v>1046</v>
       </c>
       <c r="P129" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="130" spans="1:16" ht="204.75" x14ac:dyDescent="0.25">
@@ -12796,7 +12796,7 @@
         <v>1049</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>1609</v>
+        <v>1604</v>
       </c>
       <c r="G130" s="1" t="s">
         <v>1050</v>
@@ -12826,7 +12826,7 @@
         <v>1056</v>
       </c>
       <c r="P130" s="1" t="s">
-        <v>1338</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="131" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -12846,7 +12846,7 @@
         <v>1059</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>1610</v>
+        <v>1605</v>
       </c>
       <c r="G131" s="1" t="s">
         <v>1060</v>
@@ -12876,7 +12876,7 @@
         <v>1065</v>
       </c>
       <c r="P131" s="1" t="s">
-        <v>1338</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="132" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -12896,7 +12896,7 @@
         <v>1068</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>1611</v>
+        <v>1606</v>
       </c>
       <c r="G132" s="1" t="s">
         <v>1069</v>
@@ -12926,7 +12926,7 @@
         <v>1075</v>
       </c>
       <c r="P132" s="1" t="s">
-        <v>1338</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="133" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -12946,7 +12946,7 @@
         <v>1078</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>1612</v>
+        <v>1607</v>
       </c>
       <c r="G133" s="1" t="s">
         <v>1079</v>
@@ -12976,7 +12976,7 @@
         <v>1084</v>
       </c>
       <c r="P133" s="1" t="s">
-        <v>1338</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="134" spans="1:16" ht="409.5" x14ac:dyDescent="0.25">
@@ -12993,10 +12993,10 @@
         <v>1087</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>1613</v>
+        <v>1608</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>1614</v>
+        <v>1609</v>
       </c>
       <c r="G134" s="1" t="s">
         <v>1088</v>
@@ -13020,10 +13020,10 @@
         <v>1093</v>
       </c>
       <c r="N134" s="1" t="s">
+        <v>1657</v>
+      </c>
+      <c r="O134" s="1" t="s">
         <v>1094</v>
-      </c>
-      <c r="O134" s="1" t="s">
-        <v>1095</v>
       </c>
       <c r="P134" s="1" t="s">
         <v>28</v>
@@ -13037,25 +13037,25 @@
         <v>1085</v>
       </c>
       <c r="C135" s="1" t="s">
+        <v>1655</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>1610</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>1611</v>
+      </c>
+      <c r="G135" s="1" t="s">
         <v>1096</v>
       </c>
-      <c r="D135" s="1" t="s">
+      <c r="H135" s="1" t="s">
         <v>1097</v>
       </c>
-      <c r="E135" s="1" t="s">
-        <v>1615</v>
-      </c>
-      <c r="F135" s="1" t="s">
-        <v>1616</v>
-      </c>
-      <c r="G135" s="1" t="s">
+      <c r="I135" s="1" t="s">
         <v>1098</v>
-      </c>
-      <c r="H135" s="1" t="s">
-        <v>1099</v>
-      </c>
-      <c r="I135" s="1" t="s">
-        <v>1100</v>
       </c>
       <c r="J135" s="1" t="s">
         <v>1091</v>
@@ -13070,10 +13070,10 @@
         <v>1093</v>
       </c>
       <c r="N135" s="1" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="O135" s="1" t="s">
-        <v>1102</v>
+        <v>1656</v>
       </c>
       <c r="P135" s="1" t="s">
         <v>28</v>
@@ -13087,31 +13087,31 @@
         <v>1085</v>
       </c>
       <c r="C136" s="1" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>1101</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>1612</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="G136" s="1" t="s">
+        <v>1102</v>
+      </c>
+      <c r="H136" s="1" t="s">
         <v>1103</v>
       </c>
-      <c r="D136" s="1" t="s">
+      <c r="I136" s="1" t="s">
         <v>1104</v>
       </c>
-      <c r="E136" s="1" t="s">
-        <v>1617</v>
-      </c>
-      <c r="F136" s="1" t="s">
-        <v>1618</v>
-      </c>
-      <c r="G136" s="1" t="s">
+      <c r="J136" s="1" t="s">
         <v>1105</v>
       </c>
-      <c r="H136" s="1" t="s">
+      <c r="K136" s="1" t="s">
         <v>1106</v>
-      </c>
-      <c r="I136" s="1" t="s">
-        <v>1107</v>
-      </c>
-      <c r="J136" s="1" t="s">
-        <v>1108</v>
-      </c>
-      <c r="K136" s="1" t="s">
-        <v>1109</v>
       </c>
       <c r="L136" s="1" t="s">
         <v>1092</v>
@@ -13120,13 +13120,13 @@
         <v>1093</v>
       </c>
       <c r="N136" s="1" t="s">
-        <v>1110</v>
+        <v>1658</v>
       </c>
       <c r="O136" s="1" t="s">
-        <v>1111</v>
+        <v>1107</v>
       </c>
       <c r="P136" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="137" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -13137,43 +13137,43 @@
         <v>1085</v>
       </c>
       <c r="C137" s="1" t="s">
+        <v>1108</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>1110</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>1614</v>
+      </c>
+      <c r="G137" s="1" t="s">
+        <v>1111</v>
+      </c>
+      <c r="H137" s="1" t="s">
         <v>1112</v>
       </c>
-      <c r="D137" s="1" t="s">
+      <c r="I137" s="1" t="s">
         <v>1113</v>
       </c>
-      <c r="E137" s="1" t="s">
+      <c r="J137" s="1" t="s">
         <v>1114</v>
-      </c>
-      <c r="F137" s="1" t="s">
-        <v>1619</v>
-      </c>
-      <c r="G137" s="1" t="s">
-        <v>1115</v>
-      </c>
-      <c r="H137" s="1" t="s">
-        <v>1116</v>
-      </c>
-      <c r="I137" s="1" t="s">
-        <v>1117</v>
-      </c>
-      <c r="J137" s="1" t="s">
-        <v>1118</v>
       </c>
       <c r="K137" s="1" t="s">
         <v>875</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>1119</v>
+        <v>1115</v>
       </c>
       <c r="M137" s="1" t="s">
         <v>1093</v>
       </c>
       <c r="N137" s="1" t="s">
-        <v>1120</v>
+        <v>1659</v>
       </c>
       <c r="O137" s="1" t="s">
-        <v>1121</v>
+        <v>1116</v>
       </c>
       <c r="P137" s="1" t="s">
         <v>28</v>
@@ -13187,43 +13187,43 @@
         <v>1085</v>
       </c>
       <c r="C138" s="1" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>1119</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="G138" s="1" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H138" s="1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="I138" s="1" t="s">
         <v>1122</v>
       </c>
-      <c r="D138" s="1" t="s">
+      <c r="J138" s="1" t="s">
         <v>1123</v>
       </c>
-      <c r="E138" s="1" t="s">
+      <c r="K138" s="1" t="s">
         <v>1124</v>
       </c>
-      <c r="F138" s="1" t="s">
-        <v>1620</v>
-      </c>
-      <c r="G138" s="1" t="s">
+      <c r="L138" s="1" t="s">
         <v>1125</v>
-      </c>
-      <c r="H138" s="1" t="s">
-        <v>1126</v>
-      </c>
-      <c r="I138" s="1" t="s">
-        <v>1127</v>
-      </c>
-      <c r="J138" s="1" t="s">
-        <v>1128</v>
-      </c>
-      <c r="K138" s="1" t="s">
-        <v>1129</v>
-      </c>
-      <c r="L138" s="1" t="s">
-        <v>1130</v>
       </c>
       <c r="M138" s="1" t="s">
         <v>1093</v>
       </c>
       <c r="N138" s="1" t="s">
-        <v>1120</v>
+        <v>1659</v>
       </c>
       <c r="O138" s="1" t="s">
-        <v>1131</v>
+        <v>1126</v>
       </c>
       <c r="P138" s="1" t="s">
         <v>28</v>
@@ -13237,43 +13237,43 @@
         <v>1085</v>
       </c>
       <c r="C139" s="1" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>1616</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>1617</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>1129</v>
+      </c>
+      <c r="H139" s="1" t="s">
+        <v>1130</v>
+      </c>
+      <c r="I139" s="1" t="s">
+        <v>1131</v>
+      </c>
+      <c r="J139" s="1" t="s">
         <v>1132</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>1133</v>
-      </c>
-      <c r="E139" s="1" t="s">
-        <v>1621</v>
-      </c>
-      <c r="F139" s="1" t="s">
-        <v>1622</v>
-      </c>
-      <c r="G139" s="1" t="s">
-        <v>1134</v>
-      </c>
-      <c r="H139" s="1" t="s">
-        <v>1135</v>
-      </c>
-      <c r="I139" s="1" t="s">
-        <v>1136</v>
-      </c>
-      <c r="J139" s="1" t="s">
-        <v>1137</v>
       </c>
       <c r="K139" s="1" t="s">
         <v>774</v>
       </c>
       <c r="L139" s="1" t="s">
-        <v>1130</v>
+        <v>1125</v>
       </c>
       <c r="M139" s="1" t="s">
         <v>1093</v>
       </c>
       <c r="N139" s="1" t="s">
-        <v>1120</v>
+        <v>1659</v>
       </c>
       <c r="O139" s="1" t="s">
-        <v>1138</v>
+        <v>1133</v>
       </c>
       <c r="P139" s="1" t="s">
         <v>28</v>
@@ -13287,43 +13287,43 @@
         <v>1085</v>
       </c>
       <c r="C140" s="1" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>1135</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>1618</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>1619</v>
+      </c>
+      <c r="G140" s="1" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H140" s="1" t="s">
+        <v>1137</v>
+      </c>
+      <c r="I140" s="1" t="s">
+        <v>1138</v>
+      </c>
+      <c r="J140" s="1" t="s">
         <v>1139</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>1140</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>1623</v>
-      </c>
-      <c r="F140" s="1" t="s">
-        <v>1624</v>
-      </c>
-      <c r="G140" s="1" t="s">
-        <v>1141</v>
-      </c>
-      <c r="H140" s="1" t="s">
-        <v>1142</v>
-      </c>
-      <c r="I140" s="1" t="s">
-        <v>1143</v>
-      </c>
-      <c r="J140" s="1" t="s">
-        <v>1144</v>
       </c>
       <c r="K140" s="1" t="s">
         <v>147</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>1145</v>
+        <v>1140</v>
       </c>
       <c r="M140" s="1" t="s">
         <v>1093</v>
       </c>
       <c r="N140" s="1" t="s">
-        <v>1120</v>
+        <v>1659</v>
       </c>
       <c r="O140" s="1" t="s">
-        <v>1146</v>
+        <v>1141</v>
       </c>
       <c r="P140" s="1" t="s">
         <v>28</v>
@@ -13334,49 +13334,49 @@
         <v>140</v>
       </c>
       <c r="B141" s="1" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>1362</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>1620</v>
+      </c>
+      <c r="G141" s="1" t="s">
+        <v>1145</v>
+      </c>
+      <c r="H141" s="1" t="s">
+        <v>1146</v>
+      </c>
+      <c r="I141" s="1" t="s">
         <v>1147</v>
       </c>
-      <c r="C141" s="1" t="s">
+      <c r="J141" s="1" t="s">
         <v>1148</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>1149</v>
-      </c>
-      <c r="E141" s="1" t="s">
-        <v>1367</v>
-      </c>
-      <c r="F141" s="1" t="s">
-        <v>1625</v>
-      </c>
-      <c r="G141" s="1" t="s">
-        <v>1150</v>
-      </c>
-      <c r="H141" s="1" t="s">
-        <v>1151</v>
-      </c>
-      <c r="I141" s="1" t="s">
-        <v>1152</v>
-      </c>
-      <c r="J141" s="1" t="s">
-        <v>1153</v>
       </c>
       <c r="K141" s="1" t="s">
         <v>875</v>
       </c>
       <c r="L141" s="1" t="s">
-        <v>1154</v>
+        <v>1149</v>
       </c>
       <c r="M141" s="1" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
       <c r="N141" s="1" t="s">
-        <v>1156</v>
+        <v>1151</v>
       </c>
       <c r="O141" s="1" t="s">
-        <v>1157</v>
+        <v>1152</v>
       </c>
       <c r="P141" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="142" spans="1:16" ht="204.75" x14ac:dyDescent="0.25">
@@ -13384,49 +13384,49 @@
         <v>141</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
       <c r="C142" s="1" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>1622</v>
+      </c>
+      <c r="G142" s="1" t="s">
+        <v>1155</v>
+      </c>
+      <c r="H142" s="1" t="s">
+        <v>1156</v>
+      </c>
+      <c r="I142" s="1" t="s">
+        <v>1157</v>
+      </c>
+      <c r="J142" s="1" t="s">
         <v>1158</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>1159</v>
-      </c>
-      <c r="E142" s="1" t="s">
-        <v>1626</v>
-      </c>
-      <c r="F142" s="1" t="s">
-        <v>1627</v>
-      </c>
-      <c r="G142" s="1" t="s">
-        <v>1160</v>
-      </c>
-      <c r="H142" s="1" t="s">
-        <v>1161</v>
-      </c>
-      <c r="I142" s="1" t="s">
-        <v>1162</v>
-      </c>
-      <c r="J142" s="1" t="s">
-        <v>1163</v>
       </c>
       <c r="K142" s="1" t="s">
         <v>186</v>
       </c>
       <c r="L142" s="1" t="s">
-        <v>1164</v>
+        <v>1159</v>
       </c>
       <c r="M142" s="1" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
       <c r="N142" s="1" t="s">
-        <v>1165</v>
+        <v>1160</v>
       </c>
       <c r="O142" s="1" t="s">
-        <v>1166</v>
+        <v>1161</v>
       </c>
       <c r="P142" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="143" spans="1:16" ht="204.75" x14ac:dyDescent="0.25">
@@ -13434,28 +13434,28 @@
         <v>142</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>1167</v>
+        <v>1162</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>1168</v>
+        <v>1163</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>1628</v>
+        <v>1623</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>1629</v>
+        <v>1624</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>1169</v>
+        <v>1164</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>1170</v>
+        <v>1165</v>
       </c>
       <c r="I143" s="1" t="s">
-        <v>1171</v>
+        <v>1166</v>
       </c>
       <c r="J143" s="1" t="s">
         <v>897</v>
@@ -13464,16 +13464,16 @@
         <v>265</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>1172</v>
+        <v>1167</v>
       </c>
       <c r="M143" s="1" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
       <c r="N143" s="1" t="s">
-        <v>1173</v>
+        <v>1168</v>
       </c>
       <c r="O143" s="1" t="s">
-        <v>1174</v>
+        <v>1169</v>
       </c>
       <c r="P143" s="1" t="s">
         <v>28</v>
@@ -13484,46 +13484,46 @@
         <v>143</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
       <c r="C144" s="1" t="s">
+        <v>1170</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>1171</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>1625</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>1626</v>
+      </c>
+      <c r="G144" s="1" t="s">
+        <v>1172</v>
+      </c>
+      <c r="H144" s="1" t="s">
+        <v>1173</v>
+      </c>
+      <c r="I144" s="1" t="s">
+        <v>1174</v>
+      </c>
+      <c r="J144" s="1" t="s">
         <v>1175</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>1176</v>
-      </c>
-      <c r="E144" s="1" t="s">
-        <v>1630</v>
-      </c>
-      <c r="F144" s="1" t="s">
-        <v>1631</v>
-      </c>
-      <c r="G144" s="1" t="s">
-        <v>1177</v>
-      </c>
-      <c r="H144" s="1" t="s">
-        <v>1178</v>
-      </c>
-      <c r="I144" s="1" t="s">
-        <v>1179</v>
-      </c>
-      <c r="J144" s="1" t="s">
-        <v>1180</v>
       </c>
       <c r="K144" s="1" t="s">
         <v>331</v>
       </c>
       <c r="L144" s="1" t="s">
-        <v>1181</v>
+        <v>1176</v>
       </c>
       <c r="M144" s="1" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
       <c r="N144" s="1" t="s">
-        <v>1182</v>
+        <v>1177</v>
       </c>
       <c r="O144" s="1" t="s">
-        <v>1183</v>
+        <v>1178</v>
       </c>
       <c r="P144" s="1" t="s">
         <v>28</v>
@@ -13534,49 +13534,49 @@
         <v>144</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>1184</v>
+        <v>1179</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>1185</v>
+        <v>1180</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>1368</v>
+        <v>1363</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>1632</v>
+        <v>1627</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>1186</v>
+        <v>1181</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>1187</v>
+        <v>1182</v>
       </c>
       <c r="I145" s="1" t="s">
-        <v>1162</v>
+        <v>1157</v>
       </c>
       <c r="J145" s="1" t="s">
-        <v>1188</v>
+        <v>1183</v>
       </c>
       <c r="K145" s="1" t="s">
         <v>147</v>
       </c>
       <c r="L145" s="1" t="s">
-        <v>1189</v>
+        <v>1184</v>
       </c>
       <c r="M145" s="1" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
       <c r="N145" s="1" t="s">
-        <v>1182</v>
+        <v>1177</v>
       </c>
       <c r="O145" s="1" t="s">
-        <v>1190</v>
+        <v>1185</v>
       </c>
       <c r="P145" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="146" spans="1:16" ht="204.75" x14ac:dyDescent="0.25">
@@ -13584,49 +13584,49 @@
         <v>145</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>1191</v>
+        <v>1186</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>1192</v>
+        <v>1187</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>1633</v>
+        <v>1628</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>1634</v>
+        <v>1629</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>1193</v>
+        <v>1188</v>
       </c>
       <c r="H146" s="1" t="s">
-        <v>1194</v>
+        <v>1189</v>
       </c>
       <c r="I146" s="1" t="s">
-        <v>1162</v>
+        <v>1157</v>
       </c>
       <c r="J146" s="1" t="s">
-        <v>1188</v>
+        <v>1183</v>
       </c>
       <c r="K146" s="1" t="s">
         <v>875</v>
       </c>
       <c r="L146" s="1" t="s">
-        <v>1195</v>
+        <v>1190</v>
       </c>
       <c r="M146" s="1" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
       <c r="N146" s="1" t="s">
-        <v>1182</v>
+        <v>1177</v>
       </c>
       <c r="O146" s="1" t="s">
-        <v>1196</v>
+        <v>1191</v>
       </c>
       <c r="P146" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="147" spans="1:16" ht="252" x14ac:dyDescent="0.25">
@@ -13634,49 +13634,49 @@
         <v>146</v>
       </c>
       <c r="B147" s="1" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>1193</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>1364</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>1630</v>
+      </c>
+      <c r="G147" s="1" t="s">
+        <v>1195</v>
+      </c>
+      <c r="H147" s="1" t="s">
+        <v>1196</v>
+      </c>
+      <c r="I147" s="1" t="s">
         <v>1197</v>
       </c>
-      <c r="C147" s="1" t="s">
+      <c r="J147" s="1" t="s">
         <v>1198</v>
       </c>
-      <c r="D147" s="1" t="s">
+      <c r="K147" s="1" t="s">
         <v>1199</v>
       </c>
-      <c r="E147" s="1" t="s">
-        <v>1369</v>
-      </c>
-      <c r="F147" s="1" t="s">
-        <v>1635</v>
-      </c>
-      <c r="G147" s="1" t="s">
+      <c r="L147" s="1" t="s">
         <v>1200</v>
       </c>
-      <c r="H147" s="1" t="s">
+      <c r="M147" s="1" t="s">
         <v>1201</v>
       </c>
-      <c r="I147" s="1" t="s">
+      <c r="N147" s="1" t="s">
         <v>1202</v>
       </c>
-      <c r="J147" s="1" t="s">
+      <c r="O147" s="1" t="s">
         <v>1203</v>
       </c>
-      <c r="K147" s="1" t="s">
-        <v>1204</v>
-      </c>
-      <c r="L147" s="1" t="s">
-        <v>1205</v>
-      </c>
-      <c r="M147" s="1" t="s">
-        <v>1206</v>
-      </c>
-      <c r="N147" s="1" t="s">
-        <v>1207</v>
-      </c>
-      <c r="O147" s="1" t="s">
-        <v>1208</v>
-      </c>
       <c r="P147" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="148" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -13684,49 +13684,49 @@
         <v>147</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
       <c r="C148" s="1" t="s">
+        <v>1204</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>1205</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>1365</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>1631</v>
+      </c>
+      <c r="G148" s="1" t="s">
+        <v>1206</v>
+      </c>
+      <c r="H148" s="1" t="s">
+        <v>1207</v>
+      </c>
+      <c r="I148" s="1" t="s">
+        <v>1208</v>
+      </c>
+      <c r="J148" s="1" t="s">
+        <v>1198</v>
+      </c>
+      <c r="K148" s="1" t="s">
         <v>1209</v>
       </c>
-      <c r="D148" s="1" t="s">
+      <c r="L148" s="1" t="s">
         <v>1210</v>
       </c>
-      <c r="E148" s="1" t="s">
-        <v>1370</v>
-      </c>
-      <c r="F148" s="1" t="s">
-        <v>1636</v>
-      </c>
-      <c r="G148" s="1" t="s">
+      <c r="M148" s="1" t="s">
+        <v>1201</v>
+      </c>
+      <c r="N148" s="1" t="s">
         <v>1211</v>
       </c>
-      <c r="H148" s="1" t="s">
+      <c r="O148" s="1" t="s">
         <v>1212</v>
       </c>
-      <c r="I148" s="1" t="s">
-        <v>1213</v>
-      </c>
-      <c r="J148" s="1" t="s">
-        <v>1203</v>
-      </c>
-      <c r="K148" s="1" t="s">
-        <v>1214</v>
-      </c>
-      <c r="L148" s="1" t="s">
-        <v>1215</v>
-      </c>
-      <c r="M148" s="1" t="s">
-        <v>1206</v>
-      </c>
-      <c r="N148" s="1" t="s">
-        <v>1216</v>
-      </c>
-      <c r="O148" s="1" t="s">
-        <v>1217</v>
-      </c>
       <c r="P148" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="149" spans="1:16" ht="409.5" x14ac:dyDescent="0.25">
@@ -13734,49 +13734,49 @@
         <v>148</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
       <c r="C149" s="1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>1214</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>1366</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>1367</v>
+      </c>
+      <c r="G149" s="1" t="s">
+        <v>1215</v>
+      </c>
+      <c r="H149" s="1" t="s">
+        <v>1216</v>
+      </c>
+      <c r="I149" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="J149" s="1" t="s">
         <v>1218</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>1219</v>
-      </c>
-      <c r="E149" s="1" t="s">
-        <v>1371</v>
-      </c>
-      <c r="F149" s="1" t="s">
-        <v>1372</v>
-      </c>
-      <c r="G149" s="1" t="s">
-        <v>1220</v>
-      </c>
-      <c r="H149" s="1" t="s">
-        <v>1221</v>
-      </c>
-      <c r="I149" s="1" t="s">
-        <v>1222</v>
-      </c>
-      <c r="J149" s="1" t="s">
-        <v>1223</v>
       </c>
       <c r="K149" s="1" t="s">
         <v>986</v>
       </c>
       <c r="L149" s="1" t="s">
-        <v>1224</v>
+        <v>1219</v>
       </c>
       <c r="M149" s="1" t="s">
-        <v>1206</v>
+        <v>1201</v>
       </c>
       <c r="N149" s="1" t="s">
-        <v>1225</v>
+        <v>1220</v>
       </c>
       <c r="O149" s="1" t="s">
-        <v>1226</v>
+        <v>1221</v>
       </c>
       <c r="P149" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="150" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -13784,28 +13784,28 @@
         <v>149</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
       <c r="C150" s="1" t="s">
+        <v>1222</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>1223</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>1224</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>1632</v>
+      </c>
+      <c r="G150" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="H150" s="1" t="s">
+        <v>1226</v>
+      </c>
+      <c r="I150" s="1" t="s">
         <v>1227</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>1228</v>
-      </c>
-      <c r="E150" s="1" t="s">
-        <v>1229</v>
-      </c>
-      <c r="F150" s="1" t="s">
-        <v>1637</v>
-      </c>
-      <c r="G150" s="1" t="s">
-        <v>1230</v>
-      </c>
-      <c r="H150" s="1" t="s">
-        <v>1231</v>
-      </c>
-      <c r="I150" s="1" t="s">
-        <v>1232</v>
       </c>
       <c r="J150" s="1" t="s">
         <v>994</v>
@@ -13814,16 +13814,16 @@
         <v>986</v>
       </c>
       <c r="L150" s="1" t="s">
-        <v>1233</v>
+        <v>1228</v>
       </c>
       <c r="M150" s="1" t="s">
-        <v>1206</v>
+        <v>1201</v>
       </c>
       <c r="N150" s="1" t="s">
-        <v>1234</v>
+        <v>1229</v>
       </c>
       <c r="O150" s="1" t="s">
-        <v>1235</v>
+        <v>1230</v>
       </c>
       <c r="P150" s="1" t="s">
         <v>28</v>
@@ -13834,46 +13834,46 @@
         <v>150</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
       <c r="C151" s="1" t="s">
+        <v>1231</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>1232</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>1233</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>1633</v>
+      </c>
+      <c r="G151" s="1" t="s">
+        <v>1234</v>
+      </c>
+      <c r="H151" s="1" t="s">
+        <v>1235</v>
+      </c>
+      <c r="I151" s="1" t="s">
         <v>1236</v>
       </c>
-      <c r="D151" s="1" t="s">
+      <c r="J151" s="1" t="s">
         <v>1237</v>
       </c>
-      <c r="E151" s="1" t="s">
+      <c r="K151" s="1" t="s">
         <v>1238</v>
       </c>
-      <c r="F151" s="1" t="s">
-        <v>1638</v>
-      </c>
-      <c r="G151" s="1" t="s">
+      <c r="L151" s="1" t="s">
         <v>1239</v>
       </c>
-      <c r="H151" s="1" t="s">
+      <c r="M151" s="1" t="s">
+        <v>1201</v>
+      </c>
+      <c r="N151" s="1" t="s">
+        <v>1229</v>
+      </c>
+      <c r="O151" s="1" t="s">
         <v>1240</v>
-      </c>
-      <c r="I151" s="1" t="s">
-        <v>1241</v>
-      </c>
-      <c r="J151" s="1" t="s">
-        <v>1242</v>
-      </c>
-      <c r="K151" s="1" t="s">
-        <v>1243</v>
-      </c>
-      <c r="L151" s="1" t="s">
-        <v>1244</v>
-      </c>
-      <c r="M151" s="1" t="s">
-        <v>1206</v>
-      </c>
-      <c r="N151" s="1" t="s">
-        <v>1234</v>
-      </c>
-      <c r="O151" s="1" t="s">
-        <v>1245</v>
       </c>
       <c r="P151" s="1" t="s">
         <v>28</v>
@@ -13884,46 +13884,46 @@
         <v>151</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
       <c r="C152" s="1" t="s">
+        <v>1241</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>1634</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>1635</v>
+      </c>
+      <c r="G152" s="1" t="s">
+        <v>1243</v>
+      </c>
+      <c r="H152" s="1" t="s">
+        <v>1244</v>
+      </c>
+      <c r="I152" s="1" t="s">
+        <v>1245</v>
+      </c>
+      <c r="J152" s="1" t="s">
         <v>1246</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>1247</v>
-      </c>
-      <c r="E152" s="1" t="s">
-        <v>1639</v>
-      </c>
-      <c r="F152" s="1" t="s">
-        <v>1640</v>
-      </c>
-      <c r="G152" s="1" t="s">
-        <v>1248</v>
-      </c>
-      <c r="H152" s="1" t="s">
-        <v>1249</v>
-      </c>
-      <c r="I152" s="1" t="s">
-        <v>1250</v>
-      </c>
-      <c r="J152" s="1" t="s">
-        <v>1251</v>
       </c>
       <c r="K152" s="1" t="s">
         <v>630</v>
       </c>
       <c r="L152" s="1" t="s">
-        <v>1252</v>
+        <v>1247</v>
       </c>
       <c r="M152" s="1" t="s">
-        <v>1206</v>
+        <v>1201</v>
       </c>
       <c r="N152" s="1" t="s">
-        <v>1234</v>
+        <v>1229</v>
       </c>
       <c r="O152" s="1" t="s">
-        <v>1253</v>
+        <v>1248</v>
       </c>
       <c r="P152" s="1" t="s">
         <v>28</v>
@@ -13934,49 +13934,49 @@
         <v>152</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>1254</v>
+        <v>1249</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>1255</v>
+        <v>1250</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>1340</v>
+        <v>1335</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>1641</v>
+        <v>1636</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>1341</v>
+        <v>1336</v>
       </c>
       <c r="H153" s="1" t="s">
-        <v>1256</v>
+        <v>1251</v>
       </c>
       <c r="I153" s="1" t="s">
-        <v>1335</v>
+        <v>1330</v>
       </c>
       <c r="J153" s="1" t="s">
-        <v>1334</v>
+        <v>1329</v>
       </c>
       <c r="K153" s="1" t="s">
-        <v>1204</v>
+        <v>1199</v>
       </c>
       <c r="L153" s="1" t="s">
-        <v>1257</v>
+        <v>1252</v>
       </c>
       <c r="M153" s="1" t="s">
-        <v>1206</v>
+        <v>1201</v>
       </c>
       <c r="N153" s="1" t="s">
-        <v>1234</v>
+        <v>1229</v>
       </c>
       <c r="O153" s="1" t="s">
-        <v>1258</v>
+        <v>1253</v>
       </c>
       <c r="P153" s="1" t="s">
-        <v>1326</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="154" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -13984,46 +13984,46 @@
         <v>153</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
       <c r="C154" s="1" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>1637</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>1638</v>
+      </c>
+      <c r="G154" s="1" t="s">
+        <v>1256</v>
+      </c>
+      <c r="H154" s="1" t="s">
+        <v>1257</v>
+      </c>
+      <c r="I154" s="1" t="s">
+        <v>1258</v>
+      </c>
+      <c r="J154" s="1" t="s">
         <v>1259</v>
       </c>
-      <c r="D154" s="1" t="s">
+      <c r="K154" s="1" t="s">
         <v>1260</v>
-      </c>
-      <c r="E154" s="1" t="s">
-        <v>1642</v>
-      </c>
-      <c r="F154" s="1" t="s">
-        <v>1643</v>
-      </c>
-      <c r="G154" s="1" t="s">
-        <v>1261</v>
-      </c>
-      <c r="H154" s="1" t="s">
-        <v>1262</v>
-      </c>
-      <c r="I154" s="1" t="s">
-        <v>1263</v>
-      </c>
-      <c r="J154" s="1" t="s">
-        <v>1264</v>
-      </c>
-      <c r="K154" s="1" t="s">
-        <v>1265</v>
       </c>
       <c r="L154" s="1" t="s">
         <v>1035</v>
       </c>
       <c r="M154" s="1" t="s">
-        <v>1206</v>
+        <v>1201</v>
       </c>
       <c r="N154" s="1" t="s">
-        <v>1234</v>
+        <v>1229</v>
       </c>
       <c r="O154" s="1" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
       <c r="P154" s="1" t="s">
         <v>28</v>
@@ -14034,46 +14034,46 @@
         <v>154</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
       <c r="C155" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>1263</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>1639</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>1640</v>
+      </c>
+      <c r="G155" s="1" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H155" s="1" t="s">
+        <v>1265</v>
+      </c>
+      <c r="I155" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="J155" s="1" t="s">
         <v>1267</v>
       </c>
-      <c r="D155" s="1" t="s">
+      <c r="K155" s="1" t="s">
         <v>1268</v>
-      </c>
-      <c r="E155" s="1" t="s">
-        <v>1644</v>
-      </c>
-      <c r="F155" s="1" t="s">
-        <v>1645</v>
-      </c>
-      <c r="G155" s="1" t="s">
-        <v>1269</v>
-      </c>
-      <c r="H155" s="1" t="s">
-        <v>1270</v>
-      </c>
-      <c r="I155" s="1" t="s">
-        <v>1271</v>
-      </c>
-      <c r="J155" s="1" t="s">
-        <v>1272</v>
-      </c>
-      <c r="K155" s="1" t="s">
-        <v>1273</v>
       </c>
       <c r="L155" s="1" t="s">
         <v>1043</v>
       </c>
       <c r="M155" s="1" t="s">
-        <v>1206</v>
+        <v>1201</v>
       </c>
       <c r="N155" s="1" t="s">
-        <v>1234</v>
+        <v>1229</v>
       </c>
       <c r="O155" s="1" t="s">
-        <v>1274</v>
+        <v>1269</v>
       </c>
       <c r="P155" s="1" t="s">
         <v>28</v>
@@ -14084,49 +14084,49 @@
         <v>155</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
       <c r="C156" s="1" t="s">
+        <v>1270</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>1271</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>1641</v>
+      </c>
+      <c r="G156" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="H156" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="I156" s="1" t="s">
         <v>1275</v>
       </c>
-      <c r="D156" s="1" t="s">
+      <c r="J156" s="1" t="s">
         <v>1276</v>
       </c>
-      <c r="E156" s="1" t="s">
+      <c r="K156" s="1" t="s">
         <v>1277</v>
       </c>
-      <c r="F156" s="1" t="s">
-        <v>1646</v>
-      </c>
-      <c r="G156" s="1" t="s">
+      <c r="L156" s="1" t="s">
         <v>1278</v>
       </c>
-      <c r="H156" s="1" t="s">
+      <c r="M156" s="1" t="s">
+        <v>1201</v>
+      </c>
+      <c r="N156" s="1" t="s">
+        <v>1229</v>
+      </c>
+      <c r="O156" s="1" t="s">
         <v>1279</v>
       </c>
-      <c r="I156" s="1" t="s">
-        <v>1280</v>
-      </c>
-      <c r="J156" s="1" t="s">
-        <v>1281</v>
-      </c>
-      <c r="K156" s="1" t="s">
-        <v>1282</v>
-      </c>
-      <c r="L156" s="1" t="s">
-        <v>1283</v>
-      </c>
-      <c r="M156" s="1" t="s">
-        <v>1206</v>
-      </c>
-      <c r="N156" s="1" t="s">
-        <v>1234</v>
-      </c>
-      <c r="O156" s="1" t="s">
-        <v>1284</v>
-      </c>
       <c r="P156" s="1" t="s">
-        <v>1338</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="157" spans="1:16" ht="252" x14ac:dyDescent="0.25">
@@ -14134,46 +14134,46 @@
         <v>156</v>
       </c>
       <c r="B157" s="1" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>1281</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>1282</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>1642</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>1643</v>
+      </c>
+      <c r="G157" s="1" t="s">
+        <v>1283</v>
+      </c>
+      <c r="H157" s="1" t="s">
+        <v>1284</v>
+      </c>
+      <c r="I157" s="1" t="s">
         <v>1285</v>
       </c>
-      <c r="C157" s="1" t="s">
+      <c r="J157" s="1" t="s">
         <v>1286</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>1287</v>
-      </c>
-      <c r="E157" s="1" t="s">
-        <v>1647</v>
-      </c>
-      <c r="F157" s="1" t="s">
-        <v>1648</v>
-      </c>
-      <c r="G157" s="1" t="s">
-        <v>1288</v>
-      </c>
-      <c r="H157" s="1" t="s">
-        <v>1289</v>
-      </c>
-      <c r="I157" s="1" t="s">
-        <v>1290</v>
-      </c>
-      <c r="J157" s="1" t="s">
-        <v>1291</v>
       </c>
       <c r="K157" s="1" t="s">
         <v>53</v>
       </c>
       <c r="L157" s="1" t="s">
-        <v>1292</v>
+        <v>1287</v>
       </c>
       <c r="M157" s="1" t="s">
-        <v>1293</v>
+        <v>1288</v>
       </c>
       <c r="N157" s="1" t="s">
-        <v>1294</v>
+        <v>1289</v>
       </c>
       <c r="O157" s="1" t="s">
-        <v>1295</v>
+        <v>1290</v>
       </c>
       <c r="P157" s="1" t="s">
         <v>28</v>
@@ -14184,49 +14184,49 @@
         <v>157</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>1285</v>
+        <v>1280</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>1296</v>
+        <v>1291</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>1297</v>
+        <v>1292</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>1336</v>
+        <v>1331</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>1649</v>
+        <v>1644</v>
       </c>
       <c r="G158" s="1" t="s">
+        <v>1332</v>
+      </c>
+      <c r="H158" s="1" t="s">
+        <v>1339</v>
+      </c>
+      <c r="I158" s="1" t="s">
+        <v>1338</v>
+      </c>
+      <c r="J158" s="1" t="s">
         <v>1337</v>
-      </c>
-      <c r="H158" s="1" t="s">
-        <v>1344</v>
-      </c>
-      <c r="I158" s="1" t="s">
-        <v>1343</v>
-      </c>
-      <c r="J158" s="1" t="s">
-        <v>1342</v>
       </c>
       <c r="K158" s="1" t="s">
         <v>812</v>
       </c>
       <c r="L158" s="1" t="s">
-        <v>1298</v>
+        <v>1293</v>
       </c>
       <c r="M158" s="1" t="s">
-        <v>1293</v>
+        <v>1288</v>
       </c>
       <c r="N158" s="1" t="s">
-        <v>1299</v>
+        <v>1294</v>
       </c>
       <c r="O158" s="1" t="s">
-        <v>1300</v>
+        <v>1295</v>
       </c>
       <c r="P158" s="1" t="s">
-        <v>1326</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="159" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -14234,46 +14234,46 @@
         <v>158</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>1285</v>
+        <v>1280</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>1301</v>
+        <v>1296</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>1302</v>
+        <v>1297</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>1650</v>
+        <v>1645</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>1651</v>
+        <v>1646</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>1303</v>
+        <v>1298</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>1304</v>
+        <v>1299</v>
       </c>
       <c r="I159" s="1" t="s">
-        <v>1305</v>
+        <v>1300</v>
       </c>
       <c r="J159" s="1" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
       <c r="K159" s="1" t="s">
         <v>158</v>
       </c>
       <c r="L159" s="1" t="s">
-        <v>1292</v>
+        <v>1287</v>
       </c>
       <c r="M159" s="1" t="s">
-        <v>1293</v>
+        <v>1288</v>
       </c>
       <c r="N159" s="1" t="s">
-        <v>1306</v>
+        <v>1301</v>
       </c>
       <c r="O159" s="1" t="s">
-        <v>1307</v>
+        <v>1302</v>
       </c>
       <c r="P159" s="1" t="s">
         <v>28</v>
@@ -14284,49 +14284,49 @@
         <v>159</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>1285</v>
+        <v>1280</v>
       </c>
       <c r="C160" s="1" t="s">
+        <v>1303</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>1304</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>1647</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>1648</v>
+      </c>
+      <c r="G160" s="1" t="s">
+        <v>1305</v>
+      </c>
+      <c r="H160" s="1" t="s">
+        <v>1306</v>
+      </c>
+      <c r="I160" s="1" t="s">
+        <v>1307</v>
+      </c>
+      <c r="J160" s="1" t="s">
+        <v>1286</v>
+      </c>
+      <c r="K160" s="1" t="s">
         <v>1308</v>
       </c>
-      <c r="D160" s="1" t="s">
+      <c r="L160" s="1" t="s">
         <v>1309</v>
       </c>
-      <c r="E160" s="1" t="s">
-        <v>1652</v>
-      </c>
-      <c r="F160" s="1" t="s">
-        <v>1653</v>
-      </c>
-      <c r="G160" s="1" t="s">
+      <c r="M160" s="1" t="s">
+        <v>1288</v>
+      </c>
+      <c r="N160" s="1" t="s">
         <v>1310</v>
       </c>
-      <c r="H160" s="1" t="s">
+      <c r="O160" s="1" t="s">
         <v>1311</v>
       </c>
-      <c r="I160" s="1" t="s">
-        <v>1312</v>
-      </c>
-      <c r="J160" s="1" t="s">
-        <v>1291</v>
-      </c>
-      <c r="K160" s="1" t="s">
-        <v>1313</v>
-      </c>
-      <c r="L160" s="1" t="s">
-        <v>1314</v>
-      </c>
-      <c r="M160" s="1" t="s">
-        <v>1293</v>
-      </c>
-      <c r="N160" s="1" t="s">
-        <v>1315</v>
-      </c>
-      <c r="O160" s="1" t="s">
-        <v>1316</v>
-      </c>
       <c r="P160" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="161" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -14334,56 +14334,56 @@
         <v>160</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>1285</v>
+        <v>1280</v>
       </c>
       <c r="C161" s="1" t="s">
+        <v>1312</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>1649</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>1650</v>
+      </c>
+      <c r="G161" s="1" t="s">
+        <v>1314</v>
+      </c>
+      <c r="H161" s="1" t="s">
+        <v>1315</v>
+      </c>
+      <c r="I161" s="1" t="s">
+        <v>1316</v>
+      </c>
+      <c r="J161" s="1" t="s">
         <v>1317</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>1318</v>
-      </c>
-      <c r="E161" s="1" t="s">
-        <v>1654</v>
-      </c>
-      <c r="F161" s="1" t="s">
-        <v>1655</v>
-      </c>
-      <c r="G161" s="1" t="s">
-        <v>1319</v>
-      </c>
-      <c r="H161" s="1" t="s">
-        <v>1320</v>
-      </c>
-      <c r="I161" s="1" t="s">
-        <v>1321</v>
-      </c>
-      <c r="J161" s="1" t="s">
-        <v>1322</v>
       </c>
       <c r="K161" s="1" t="s">
         <v>647</v>
       </c>
       <c r="L161" s="1" t="s">
-        <v>1323</v>
+        <v>1318</v>
       </c>
       <c r="M161" s="1" t="s">
-        <v>1293</v>
+        <v>1288</v>
       </c>
       <c r="N161" s="1" t="s">
-        <v>1315</v>
+        <v>1310</v>
       </c>
       <c r="O161" s="1" t="s">
-        <v>1324</v>
+        <v>1319</v>
       </c>
       <c r="P161" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:P161" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:P1 A93:D93 A89:D89 H89:K89 M89:O89 A95:D95 A94:D94 H94:K94 M94:O94 A118:D118 A117:D117 I117:O117 A155:D155 A153:D153 K153:O153 A159:D159 A158:D158 A74:D74 A31:D31 A106:D106 A104:D104 A105:D105 A129:D129 A128:D128 A135:D135 A130:D130 A131:D131 A132:D132 A133:D133 A157:D157 A156:D156 H153 K158:O158 A8:D8 A5:D5 H5 K5 M5:O5 A6:D6 H6 K6 M6:O6 A7:D7 H7 K7 M7:O7 A30:D30 A16:D16 H16 K16 M16:O16 A81:D81 A78:D78 H78 K78 M78:O78 A79:D79 H79 K79 M79:O79 A80:D80 H80 K80 M80:O80 A84:D84 A82:D82 H82 K82 M82:O82 A83:D83 H83 K83 M83:O83 A88:D88 A85:D85 H85 K85 M85:O85 A86:D86 H86 K86 M86:O86 A87:D87 H87 K87 M87:O87 H88 K88 M88:O88 A90:D90 H90 K90 M90:O90 A91:D91 H91 K91 M91:O91 A100:D100 A96:D96 H96 K96 M96:O96 A97:D97 H97 K97 M97:O97 A98:D98 H98 K98 M98:O98 A103:D103 A101:D101 H101 K101 M101:O101 A102:D102 H102 K102 M102:O102 A109:D109 A107:D107 H107 K107 M107:O107 A108:D108 H108 K108 M108:O108 A116:D116 A110:D110 H110 K110 M110:O110 A111:D111 H111 K111 M111:O111 A112:D112 H112 K112 M112:O112 A113:D113 H113 K113 M113:O113 A114:D114 H114 K114 M114:O114 A115:D115 H115 K115 M115:O115 A124:D124 A119:D119 H119 K119 M119:O119 A120:D120 H120 K120 M120:O120 A121:D121 H121 K121 M121:O121 A122:D122 H122 K122 M122:O122 A123:D123 H123 K123 M123:O123 A126:D126 A125:D125 H125 K125 M125:O125 A127:D127 H127 K127 M127:O127 H129 K129 M129:O129 A140:D140 A136:D136 H136 K136 M136:O136 A144:D144 A141:D141 H141 K141 M141:O141 A142:D142 H142 K142 M142:O142 A152:D152 A145:D145 H145 K145 M145:O145 A146:D146 H146 K146 M146:O146 A147:D147 H147 K147 M147:O147 A148:D148 H148 K148 M148:O148 A149:D149 H149 K149 M149:O149 A161:D161 A160:D160 H160 K160 M160:O160 H161 K161 M161:O161 A77:D77 A75:D75 H75 K75 M75:O75 H81 K81 M81:O81 A15:D15 A9:D9 H9 K9 M9:O9 A4:D4 A2:D2 G2:P2 A3:D3 G3:P3 G4:P4 G8:P8 A10:D10 G10:P10 A11:D11 G11:P11 A12:D12 G12:P12 A13:D13 G13:P13 A14:D14 G14:P14 G15:P15 A17:D17 G17:P17 A18:D18 G18:P18 A19:D19 G19:P19 A20:D20 G20:P20 A21:D21 G21:P21 A22:D22 G22:P22 A23:D23 G23:P23 A24:D24 G24:P24 A25:D25 G25:P25 A26:D26 G26:P26 A27:D27 G27:P27 A28:D28 G28:P28 A29:D29 G29:P29 G30:P30 G31:O31 A32:D32 G32:P32 A33:D33 G33:P33 A34:D34 G34:P34 A35:D35 G35:P35 A36:D36 G36:P36 A37:D37 G37:P37 A38:D38 G38:P38 A39:D39 G39:P39 A40:D40 G40:P40 A41:D41 G41:P41 A42:D42 G42:P42 A43:D43 G43:P43 A44:B44 G44:N44 A45:D45 G45:P45 A46:B46 G46:N46 A47:D47 G47:P47 A48:D48 G48:P48 A49:D49 G49:P49 A50:D50 G50:P50 A51:D51 G51:P51 A52:D52 G52:P52 A53:D53 G53:P53 A54:D54 G54:P54 A55:D55 G55:P55 A56:D56 G56:P56 A57:D57 G57:P57 A58:D58 G58:P58 A59:D59 G59:P59 A60:D60 G60:P60 A61:D61 G61:P61 A62:D62 G62:P62 A63:D63 G63:P63 A64:D64 G64:P64 A65:D65 G65:P65 A66:D66 G66:P66 A67:D67 G67:P67 A68:D68 G68:P68 A69:D69 G69:P69 A70:D70 G70:P70 A71:D71 G71:P71 A72:D72 G72:P72 A73:D73 G73:P73 G74:P74 A76:D76 G76:P76 G77:P77 G84:P84 A92:D92 G92:P92 G93:P93 G95:P95 A99:D99 G99:P99 G100:P100 G103:P103 G104:O104 G105:O105 G106:P106 G109:P109 G116:P116 G118:P118 G124:P124 G126:P126 G128:O128 G130:O130 G131:O131 G132:O132 G133:O133 A134:D134 G134:P134 G135:P135 A137:D137 G137:P137 A138:D138 G138:P138 A139:D139 G139:P139 G140:P140 A143:D143 G143:P143 G144:P144 A150:D150 G150:P150 A151:D151 G151:P151 G152:P152 A154:D154 G154:P154 G155:P155 G156:O156 G157:P157 G159:P159 D44 P44 D46 P46" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:P1 A93:D93 A89:D89 H89:K89 M89:O89 A95:D95 A94:D94 H94:K94 M94:O94 A118:D118 A117:D117 I117:O117 A155:D155 A153:D153 K153:O153 A159:D159 A158:D158 A74:D74 A31:D31 A106:D106 A104:D104 A105:D105 A129:D129 A128:D128 A135:B135 A130:D130 A131:D131 A132:D132 A133:D133 A157:D157 A156:D156 H153 K158:O158 A8:D8 A5:D5 H5 K5 M5:O5 A6:D6 H6 K6 M6:O6 A7:D7 H7 K7 M7:O7 A30:D30 A16:D16 H16 K16 M16:O16 A81:D81 A78:D78 H78 K78 M78:O78 A79:D79 H79 K79 M79:O79 A80:D80 H80 K80 M80:O80 A84:D84 A82:D82 H82 K82 M82:O82 A83:D83 H83 K83 M83:O83 A88:D88 A85:D85 H85 K85 M85:O85 A86:D86 H86 K86 M86:O86 A87:D87 H87 K87 M87:O87 H88 K88 M88:O88 A90:D90 H90 K90 M90:O90 A91:D91 H91 K91 M91:O91 A100:D100 A96:D96 H96 K96 M96:O96 A97:D97 H97 K97 M97:O97 A98:D98 H98 K98 M98:O98 A103:D103 A101:D101 H101 K101 M101:O101 A102:D102 H102 K102 M102:O102 A109:D109 A107:D107 H107 K107 M107:O107 A108:D108 H108 K108 M108:O108 A116:D116 A110:D110 H110 K110 M110:O110 A111:D111 H111 K111 M111:O111 A112:D112 H112 K112 M112:O112 A113:D113 H113 K113 M113:O113 A114:D114 H114 K114 M114:O114 A115:D115 H115 K115 M115:O115 A124:D124 A119:D119 H119 K119 M119:O119 A120:D120 H120 K120 M120:O120 A121:D121 H121 K121 M121:O121 A122:D122 H122 K122 M122:O122 A123:D123 H123 K123 M123:O123 A126:D126 A125:D125 H125 K125 M125:O125 A127:D127 H127 K127 M127:O127 H129 K129 M129:O129 A140:D140 A136:D136 H136 K136 M136 A144:D144 A141:D141 H141 K141 M141:O141 A142:D142 H142 K142 M142:O142 A152:D152 A145:D145 H145 K145 M145:O145 A146:D146 H146 K146 M146:O146 A147:D147 H147 K147 M147:O147 A148:D148 H148 K148 M148:O148 A149:D149 H149 K149 M149:O149 A161:D161 A160:D160 H160 K160 M160:O160 H161 K161 M161:O161 A77:D77 A75:D75 H75 K75 M75:O75 H81 K81 M81:O81 A15:D15 A9:D9 H9 K9 M9:O9 A4:D4 A2:D2 G2:P2 A3:D3 G3:P3 G4:P4 G8:P8 A10:D10 G10:P10 A11:D11 G11:P11 A12:D12 G12:P12 A13:D13 G13:P13 A14:D14 G14:P14 G15:P15 A17:D17 G17:P17 A18:D18 G18:P18 A19:D19 G19:P19 A20:D20 G20:P20 A21:D21 G21:P21 A22:D22 G22:P22 A23:D23 G23:P23 A24:D24 G24:P24 A25:D25 G25:P25 A26:D26 G26:P26 A27:D27 G27:P27 A28:D28 G28:P28 A29:D29 G29:P29 G30:P30 G31:O31 A32:D32 G32:P32 A33:D33 G33:P33 A34:D34 G34:P34 A35:D35 G35:P35 A36:D36 G36:P36 A37:D37 G37:P37 A38:D38 G38:P38 A39:D39 G39:P39 A40:D40 G40:P40 A41:D41 G41:P41 A42:D42 G42:P42 A43:D43 G43:P43 A44:B44 G44:N44 A45:D45 G45:P45 A46:B46 G46:N46 A47:D47 G47:P47 A48:D48 G48:P48 A49:D49 G49:P49 A50:D50 G50:P50 A51:D51 G51:P51 A52:D52 G52:P52 A53:D53 G53:P53 A54:D54 G54:P54 A55:D55 G55:P55 A56:D56 G56:P56 A57:D57 G57:P57 A58:D58 G58:P58 A59:D59 G59:P59 A60:D60 G60:P60 A61:D61 G61:P61 A62:D62 G62:P62 A63:D63 G63:P63 A64:D64 G64:P64 A65:D65 G65:P65 A66:D66 G66:P66 A67:D67 G67:P67 A68:D68 G68:P68 A69:D69 G69:P69 A70:D70 G70:P70 A71:D71 G71:P71 A72:D72 G72:P72 A73:D73 G73:P73 G74:P74 A76:D76 G76:P76 G77:P77 G84:P84 A92:D92 G92:P92 G93:P93 G95:P95 A99:D99 G99:P99 G100:P100 G103:P103 G104:O104 G105:O105 G106:P106 G109:P109 G116:P116 G118:P118 G124:P124 G126:P126 G128:O128 G130:O130 G131:O131 G132:O132 G133:O133 A134:D134 G134:M134 G135:N135 A137:D137 G137:M137 A138:D138 G138:M138 A139:D139 G139:M139 G140:M140 A143:D143 G143:P143 G144:P144 A150:D150 G150:P150 A151:D151 G151:P151 G152:P152 A154:D154 G154:P154 G155:P155 G156:O156 G157:P157 G159:P159 D44 P44 D46 P46 D135 P135 O134:P134 O136 O137:P137 O138:P138 O139:P139 O140:P140" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/02_sources/extracted/design_handoff_professions_catalog/data/professions.xlsx
+++ b/02_sources/extracted/design_handoff_professions_catalog/data/professions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\рс\Desktop\ПРОФТРЕКЕР\ВЭБ СТУДИЯ сайты, графика, бренд\ИИ\сайт 160 карт\02_sources\extracted\design_handoff_professions_catalog\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F535A163-E949-4BDF-B262-63BF0B46BB6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F61F4D8C-D3A7-42D8-9E89-2DE0052B0BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2416" uniqueCount="1660">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2416" uniqueCount="1661">
   <si>
     <t>№</t>
   </si>
@@ -4039,42 +4039,12 @@
     <t>Телеканалы и радиостанции, интернет-издания и редакции, продакшн-студии, пресс-службы предприятий, рекламные агентства.</t>
   </si>
   <si>
-    <t>Диктор телевидения; Радиоведущий; Медиа-продюсер</t>
-  </si>
-  <si>
     <t>Журналист.jpg</t>
   </si>
   <si>
-    <t>Диктор телевидения</t>
-  </si>
-  <si>
-    <t>Читает новости в кадре.</t>
-  </si>
-  <si>
-    <t>Читает новостные и информационные тексты в прямом эфире и в записи.</t>
-  </si>
-  <si>
-    <t>Выпуск новостей или информационная программа, вышедшая в эфир.</t>
-  </si>
-  <si>
-    <t>Телесуфлёр, петличный микрофон, «ухо» с командами режиссёра, студийные камеры и свет, монитор вёрстки выпуска, редакторская система.</t>
-  </si>
-  <si>
-    <t>Студийный деловой костюм или платье однотонных оттенков — без мелкой клетки и полоски (рябят в кадре), эфирный грим, минимум блестящих украшений.</t>
-  </si>
-  <si>
-    <t>Классическая обувь — в кадре чаще всего не видна, поэтому главное удобство при долгой смене.</t>
-  </si>
-  <si>
     <t>42.02.01 Реклама (СПО); профильное направление — журналистика / телерадиовещание</t>
   </si>
   <si>
-    <t>Журналист; Радиоведущий; Медиа-продюсер</t>
-  </si>
-  <si>
-    <t>Диктор телевидения.jpg</t>
-  </si>
-  <si>
     <t>Радиоведущий</t>
   </si>
   <si>
@@ -4096,9 +4066,6 @@
     <t>Любая удобная обувь, чаще кроссовки.</t>
   </si>
   <si>
-    <t>Журналист; Диктор телевидения; Медиа-продюсер</t>
-  </si>
-  <si>
     <t>Радиоведущий.jpg</t>
   </si>
   <si>
@@ -4124,9 +4091,6 @@
   </si>
   <si>
     <t>55.02.01 Театральная и аудиовизуальная техника (по видам); 42.02.01 Реклама</t>
-  </si>
-  <si>
-    <t>Журналист; Диктор телевидения; Радиоведущий</t>
   </si>
   <si>
     <t>Медиа-продюсер.jpg</t>
@@ -5761,9 +5725,6 @@
     <t>Журналист находит информационный повод — событие, проблему, интересного человека — и собирает материал для будущего текста или сюжета: берёт интервью, изучает документы, выезжает на место события. Пишет тексты в текстовом редакторе или готовит аудио- и видеоматериал, используя цифровой диктофон, камеру и микрофон, если работает на радио или телевидении. Проверяет факты и источники информации, прежде чем публиковать материал, — ошибка в фактах подрывает доверие и к самому журналисту, и к изданию. Работает в разных жанрах — от короткой новости до большого репортажа или интервью, — и под каждый жанр выстраивает материал по-своему. Иногда работает с чувствительной информацией и защищает свои источники, используя инструменты шифрования и защиты данных. Работает в редакции или в разъездах на местах событий, в опрятной деловой одежде, которая уместна и на официальном мероприятии, и в поле.</t>
   </si>
   <si>
-    <t>Диктор телевидения готовится к выпуску заранее — разбирает текст, проверяет сложные имена и ударения, чтобы не ошибиться в прямом эфире, где исправить оговорку уже нельзя. В студии считывает текст с телесуфлёра, одновременно слушая в наушнике-«ухе» команды режиссёра о переходе на следующий сюжет или смене темы. Держит ровный темп речи и нужную интонацию на протяжении всего выпуска, даже если в эфире произошла техническая заминка или изменилась вёрстка. Работает с монитором вёрстки выпуска, где видит порядок сюжетов, и должен уметь на ходу перестроиться, если один из материалов сняли с эфира. Перед камерой находится под ярким студийным светом, поэтому проходит через грим, который делает лицо ровным и не бликующим в кадре. Носит однотонный костюм или платье без мелкого рисунка — клетка и полоска «рябят» на экране и мешают зрителю сосредоточиться на новостях.</t>
-  </si>
-  <si>
     <t>Радиоведущий готовит темы и подводки к музыкальным блокам заранее, а в эфире объявляет треки, читает новости и рекламу, стараясь звучать живо и естественно, а не по бумажке. Работает с эфирным пультом и программой-плейлистом, регулируя звук и переключаясь между музыкой, рекламными вставками и собственной речью в эфире. Через телефонный гибрид общается со слушателями, которые дозваниваются в прямой эфир, — быстро реагирует на реплики и удерживает разговор в рамках формата станции. Следит за таймингом эфира по секундам, чтобы уложиться в сетку вещания и не пропустить время следующего блока новостей или рекламы. Записывает и подкаст-выпуски отдельно от прямого эфира, монтируя их в звукозаписывающей программе для последующей публикации. Работает в студии в свободной повседневной одежде — слушателям не видно ведущего, а вот шуршащая ткань в микрофоне слышна отчётливо, поэтому от синтетики и украшений на записи отказываются.</t>
   </si>
   <si>
@@ -5927,6 +5888,48 @@
   </si>
   <si>
     <t>Полицейский; Автоинспектор; Охранник</t>
+  </si>
+  <si>
+    <t>Главный редактор</t>
+  </si>
+  <si>
+    <t>Стоит во главе редакции и отвечает за то, что выходит в эфир или в печать.</t>
+  </si>
+  <si>
+    <t>Руководит редакцией СМИ — определяет содержание выпусков и отвечает за итоговый результат работы всей команды.</t>
+  </si>
+  <si>
+    <t>Главный редактор стоит во главе редакции газеты, журнала, радиостанции, телеканала или интернет-издания и отвечает за то, что в итоге выходит к аудитории. Формирует план выпуска: решает, какие темы и материалы попадут в номер или эфир, а какие отложат или снимут. Распределяет задания между журналистами, редакторами и корреспондентами, следит за сроками и проверяет готовые материалы перед публикацией — вплоть до финальной подписи в печать или выпуска в эфир. Отвечает за фактическую точность и юридическую чистоту публикуемых материалов: ошибка или недостоверные сведения в его редакции — репутационный, а иногда и судебный риск. Согласовывает редакционную политику с руководством издания и коммерческими службами, балансируя интересы аудитории и бизнеса. Работает в основном в редакции, много общается с командой и часто задерживается допоздна перед сдачей номера или выпуска.</t>
+  </si>
+  <si>
+    <t>Итоговый номер издания или вышедший в эфир выпуск — то, за содержание и качество чего он отвечает лично.</t>
+  </si>
+  <si>
+    <t>Компьютер, редакционная информационная система, монитор вёрстки выпуска, телефон и мессенджеры для связи с командой.</t>
+  </si>
+  <si>
+    <t>Деловой стиль одежды — костюм, рубашка, платье; специальной одежды профессия не требует.</t>
+  </si>
+  <si>
+    <t>Удобная закрытая обувь — большую часть дня проводит в редакции на ногах и за столом.</t>
+  </si>
+  <si>
+    <t>42.02.01 Реклама (СПО) — стартовый уровень; для должности главного редактора обычно требуется высшее образование по направлению «Журналистика».</t>
+  </si>
+  <si>
+    <t>Журналист; Медиа-продюсер; Режиссер эфира</t>
+  </si>
+  <si>
+    <t>главный-редактор.png</t>
+  </si>
+  <si>
+    <t>Главный редактор; Радиоведущий; Медиа-продюсер</t>
+  </si>
+  <si>
+    <t>Журналист; Главный редактор; Медиа-продюсер</t>
+  </si>
+  <si>
+    <t>Журналист; Главный редактор; Радиоведущий</t>
   </si>
 </sst>
 </file>
@@ -6393,10 +6396,10 @@
         <v>18</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>1376</v>
+        <v>1364</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>1377</v>
+        <v>1365</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>19</v>
@@ -6443,10 +6446,10 @@
         <v>30</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>1378</v>
+        <v>1366</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>1379</v>
+        <v>1367</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>31</v>
@@ -6493,10 +6496,10 @@
         <v>40</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>1380</v>
+        <v>1368</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>1381</v>
+        <v>1369</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>41</v>
@@ -6543,10 +6546,10 @@
         <v>48</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>1340</v>
+        <v>1328</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>1382</v>
+        <v>1370</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>49</v>
@@ -6576,7 +6579,7 @@
         <v>56</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="409.5" x14ac:dyDescent="0.25">
@@ -6593,10 +6596,10 @@
         <v>58</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>1342</v>
+        <v>1330</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>1383</v>
+        <v>1371</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>59</v>
@@ -6626,7 +6629,7 @@
         <v>65</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="362.25" x14ac:dyDescent="0.25">
@@ -6643,10 +6646,10 @@
         <v>67</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>1384</v>
+        <v>1372</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>1385</v>
+        <v>1373</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>68</v>
@@ -6676,7 +6679,7 @@
         <v>74</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -6693,10 +6696,10 @@
         <v>76</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>1386</v>
+        <v>1374</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>1387</v>
+        <v>1375</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>77</v>
@@ -6743,13 +6746,13 @@
         <v>84</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>1388</v>
+        <v>1376</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>1389</v>
+        <v>1377</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>1374</v>
+        <v>1362</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>85</v>
@@ -6764,7 +6767,7 @@
         <v>88</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>1375</v>
+        <v>1363</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>25</v>
@@ -6776,7 +6779,7 @@
         <v>89</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="409.5" x14ac:dyDescent="0.25">
@@ -6793,10 +6796,10 @@
         <v>91</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>1390</v>
+        <v>1378</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>1391</v>
+        <v>1379</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>92</v>
@@ -6843,10 +6846,10 @@
         <v>98</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>1392</v>
+        <v>1380</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>1393</v>
+        <v>1381</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>99</v>
@@ -6893,10 +6896,10 @@
         <v>107</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>1394</v>
+        <v>1382</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>1395</v>
+        <v>1383</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>108</v>
@@ -6943,10 +6946,10 @@
         <v>115</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>1396</v>
+        <v>1384</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>1397</v>
+        <v>1385</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>116</v>
@@ -6993,10 +6996,10 @@
         <v>123</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>1398</v>
+        <v>1386</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>1399</v>
+        <v>1387</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>124</v>
@@ -7043,10 +7046,10 @@
         <v>132</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>1400</v>
+        <v>1388</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>1401</v>
+        <v>1389</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>133</v>
@@ -7093,10 +7096,10 @@
         <v>142</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>1402</v>
+        <v>1390</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>1403</v>
+        <v>1391</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>143</v>
@@ -7126,7 +7129,7 @@
         <v>151</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="409.5" x14ac:dyDescent="0.25">
@@ -7143,10 +7146,10 @@
         <v>153</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>1404</v>
+        <v>1392</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>1405</v>
+        <v>1393</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>154</v>
@@ -7193,10 +7196,10 @@
         <v>163</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>1406</v>
+        <v>1394</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>1407</v>
+        <v>1395</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>164</v>
@@ -7243,10 +7246,10 @@
         <v>172</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>1408</v>
+        <v>1396</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>1409</v>
+        <v>1397</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>173</v>
@@ -7293,10 +7296,10 @@
         <v>181</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>1410</v>
+        <v>1398</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>1411</v>
+        <v>1399</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>182</v>
@@ -7343,10 +7346,10 @@
         <v>191</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>1412</v>
+        <v>1400</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>1413</v>
+        <v>1401</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>192</v>
@@ -7393,10 +7396,10 @@
         <v>201</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>1414</v>
+        <v>1402</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>1415</v>
+        <v>1403</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>202</v>
@@ -7443,10 +7446,10 @@
         <v>210</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>1416</v>
+        <v>1404</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>1417</v>
+        <v>1405</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>211</v>
@@ -7493,10 +7496,10 @@
         <v>219</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>1418</v>
+        <v>1406</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>1419</v>
+        <v>1407</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>220</v>
@@ -7543,10 +7546,10 @@
         <v>228</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>1420</v>
+        <v>1408</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>1421</v>
+        <v>1409</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>229</v>
@@ -7593,10 +7596,10 @@
         <v>235</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>1422</v>
+        <v>1410</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>1423</v>
+        <v>1411</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>236</v>
@@ -7643,10 +7646,10 @@
         <v>244</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>1424</v>
+        <v>1412</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>1425</v>
+        <v>1413</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>245</v>
@@ -7693,10 +7696,10 @@
         <v>252</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>1426</v>
+        <v>1414</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>1427</v>
+        <v>1415</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>253</v>
@@ -7743,10 +7746,10 @@
         <v>261</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>1428</v>
+        <v>1416</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>1429</v>
+        <v>1417</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>262</v>
@@ -7793,10 +7796,10 @@
         <v>269</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>1430</v>
+        <v>1418</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>1431</v>
+        <v>1419</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>270</v>
@@ -7846,7 +7849,7 @@
         <v>279</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>1432</v>
+        <v>1420</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>280</v>
@@ -7876,7 +7879,7 @@
         <v>286</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>1333</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="32" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -7893,10 +7896,10 @@
         <v>289</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>1433</v>
+        <v>1421</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>1434</v>
+        <v>1422</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>290</v>
@@ -7943,10 +7946,10 @@
         <v>298</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>1435</v>
+        <v>1423</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>1436</v>
+        <v>1424</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>299</v>
@@ -7993,10 +7996,10 @@
         <v>308</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>1437</v>
+        <v>1425</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>1438</v>
+        <v>1426</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>309</v>
@@ -8043,10 +8046,10 @@
         <v>317</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>1439</v>
+        <v>1427</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>1440</v>
+        <v>1428</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>318</v>
@@ -8093,10 +8096,10 @@
         <v>326</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>1441</v>
+        <v>1429</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>1442</v>
+        <v>1430</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>327</v>
@@ -8143,10 +8146,10 @@
         <v>336</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>1443</v>
+        <v>1431</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>1444</v>
+        <v>1432</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>337</v>
@@ -8193,10 +8196,10 @@
         <v>346</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>1445</v>
+        <v>1433</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>1446</v>
+        <v>1434</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>347</v>
@@ -8243,10 +8246,10 @@
         <v>355</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>1447</v>
+        <v>1435</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>1448</v>
+        <v>1436</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>356</v>
@@ -8293,10 +8296,10 @@
         <v>361</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>1449</v>
+        <v>1437</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>1450</v>
+        <v>1438</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>362</v>
@@ -8343,10 +8346,10 @@
         <v>370</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>1451</v>
+        <v>1439</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>1452</v>
+        <v>1440</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>371</v>
@@ -8393,10 +8396,10 @@
         <v>379</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>1453</v>
+        <v>1441</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>1454</v>
+        <v>1442</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>380</v>
@@ -8443,10 +8446,10 @@
         <v>385</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>1455</v>
+        <v>1443</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>1456</v>
+        <v>1444</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>386</v>
@@ -8487,16 +8490,16 @@
         <v>334</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>1651</v>
+        <v>1638</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>389</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>1457</v>
+        <v>1445</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>1458</v>
+        <v>1446</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>390</v>
@@ -8523,7 +8526,7 @@
         <v>367</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>1652</v>
+        <v>1639</v>
       </c>
       <c r="P44" s="1" t="s">
         <v>28</v>
@@ -8543,10 +8546,10 @@
         <v>393</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>1459</v>
+        <v>1447</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>1460</v>
+        <v>1448</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>394</v>
@@ -8587,16 +8590,16 @@
         <v>334</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>1653</v>
+        <v>1640</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>399</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>1461</v>
+        <v>1449</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>1462</v>
+        <v>1450</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>400</v>
@@ -8623,7 +8626,7 @@
         <v>367</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>1654</v>
+        <v>1641</v>
       </c>
       <c r="P46" s="1" t="s">
         <v>28</v>
@@ -8643,10 +8646,10 @@
         <v>405</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>1463</v>
+        <v>1451</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>1464</v>
+        <v>1452</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>406</v>
@@ -8693,10 +8696,10 @@
         <v>415</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>1465</v>
+        <v>1453</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>1466</v>
+        <v>1454</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>416</v>
@@ -8743,10 +8746,10 @@
         <v>424</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>1467</v>
+        <v>1455</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>1468</v>
+        <v>1456</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>425</v>
@@ -8793,10 +8796,10 @@
         <v>434</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>1469</v>
+        <v>1457</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>1470</v>
+        <v>1458</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>435</v>
@@ -8843,10 +8846,10 @@
         <v>442</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>1471</v>
+        <v>1459</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>1472</v>
+        <v>1460</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>443</v>
@@ -8893,10 +8896,10 @@
         <v>446</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>1473</v>
+        <v>1461</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>1474</v>
+        <v>1462</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>447</v>
@@ -8943,10 +8946,10 @@
         <v>453</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>1475</v>
+        <v>1463</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>1476</v>
+        <v>1464</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>454</v>
@@ -8996,7 +8999,7 @@
         <v>462</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>1477</v>
+        <v>1465</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>463</v>
@@ -9043,10 +9046,10 @@
         <v>470</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>1478</v>
+        <v>1466</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>1479</v>
+        <v>1467</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>471</v>
@@ -9093,10 +9096,10 @@
         <v>478</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>1480</v>
+        <v>1468</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>1481</v>
+        <v>1469</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>479</v>
@@ -9146,7 +9149,7 @@
         <v>487</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>1482</v>
+        <v>1470</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>488</v>
@@ -9193,10 +9196,10 @@
         <v>497</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>1483</v>
+        <v>1471</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>1484</v>
+        <v>1472</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>498</v>
@@ -9243,10 +9246,10 @@
         <v>505</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>1485</v>
+        <v>1473</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>1486</v>
+        <v>1474</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>506</v>
@@ -9293,10 +9296,10 @@
         <v>514</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>1487</v>
+        <v>1475</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>1488</v>
+        <v>1476</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>515</v>
@@ -9343,10 +9346,10 @@
         <v>520</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>1489</v>
+        <v>1477</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>1490</v>
+        <v>1478</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>521</v>
@@ -9393,10 +9396,10 @@
         <v>527</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>1491</v>
+        <v>1479</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>1492</v>
+        <v>1480</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>528</v>
@@ -9443,10 +9446,10 @@
         <v>533</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>1493</v>
+        <v>1481</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>1494</v>
+        <v>1482</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>534</v>
@@ -9493,10 +9496,10 @@
         <v>541</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>1495</v>
+        <v>1483</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>1496</v>
+        <v>1484</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>542</v>
@@ -9543,10 +9546,10 @@
         <v>549</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>1497</v>
+        <v>1485</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>550</v>
@@ -9593,10 +9596,10 @@
         <v>557</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>1500</v>
+        <v>1488</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>558</v>
@@ -9643,10 +9646,10 @@
         <v>566</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>1501</v>
+        <v>1489</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>1502</v>
+        <v>1490</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>567</v>
@@ -9693,10 +9696,10 @@
         <v>576</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>1503</v>
+        <v>1491</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>1504</v>
+        <v>1492</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>577</v>
@@ -9743,10 +9746,10 @@
         <v>585</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>1505</v>
+        <v>1493</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>1506</v>
+        <v>1494</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>586</v>
@@ -9793,10 +9796,10 @@
         <v>594</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>1507</v>
+        <v>1495</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>1508</v>
+        <v>1496</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>595</v>
@@ -9843,10 +9846,10 @@
         <v>603</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>1509</v>
+        <v>1497</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>1510</v>
+        <v>1498</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>604</v>
@@ -9893,10 +9896,10 @@
         <v>611</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>1511</v>
+        <v>1499</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>1512</v>
+        <v>1500</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>612</v>
@@ -9943,10 +9946,10 @@
         <v>618</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>1513</v>
+        <v>1501</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>1514</v>
+        <v>1502</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>619</v>
@@ -9993,10 +9996,10 @@
         <v>626</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>1515</v>
+        <v>1503</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>1516</v>
+        <v>1504</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>627</v>
@@ -10043,28 +10046,28 @@
         <v>634</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>1517</v>
+        <v>1505</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>1518</v>
+        <v>1506</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>1368</v>
+        <v>1356</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>635</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>1369</v>
+        <v>1357</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>1370</v>
+        <v>1358</v>
       </c>
       <c r="K75" s="1" t="s">
         <v>491</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>1371</v>
+        <v>1359</v>
       </c>
       <c r="M75" s="1" t="s">
         <v>572</v>
@@ -10076,7 +10079,7 @@
         <v>638</v>
       </c>
       <c r="P75" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="76" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -10093,10 +10096,10 @@
         <v>640</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>1519</v>
+        <v>1507</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>1520</v>
+        <v>1508</v>
       </c>
       <c r="G76" s="1" t="s">
         <v>641</v>
@@ -10143,10 +10146,10 @@
         <v>645</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>1521</v>
+        <v>1509</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>1522</v>
+        <v>1510</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>646</v>
@@ -10193,10 +10196,10 @@
         <v>652</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>1343</v>
+        <v>1331</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>1523</v>
+        <v>1511</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>653</v>
@@ -10226,7 +10229,7 @@
         <v>660</v>
       </c>
       <c r="P78" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="79" spans="1:16" ht="252" x14ac:dyDescent="0.25">
@@ -10243,10 +10246,10 @@
         <v>662</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>1344</v>
+        <v>1332</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>1524</v>
+        <v>1512</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>663</v>
@@ -10276,7 +10279,7 @@
         <v>669</v>
       </c>
       <c r="P79" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="80" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -10293,10 +10296,10 @@
         <v>671</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>1345</v>
+        <v>1333</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>1525</v>
+        <v>1513</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>672</v>
@@ -10326,7 +10329,7 @@
         <v>678</v>
       </c>
       <c r="P80" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="81" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -10343,10 +10346,10 @@
         <v>680</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>1372</v>
+        <v>1360</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>1526</v>
+        <v>1514</v>
       </c>
       <c r="G81" s="1" t="s">
         <v>681</v>
@@ -10364,7 +10367,7 @@
         <v>53</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>1373</v>
+        <v>1361</v>
       </c>
       <c r="M81" s="1" t="s">
         <v>658</v>
@@ -10376,7 +10379,7 @@
         <v>684</v>
       </c>
       <c r="P81" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="82" spans="1:16" ht="267.75" x14ac:dyDescent="0.25">
@@ -10393,10 +10396,10 @@
         <v>686</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>1527</v>
+        <v>1515</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>1528</v>
+        <v>1516</v>
       </c>
       <c r="G82" s="1" t="s">
         <v>687</v>
@@ -10426,7 +10429,7 @@
         <v>692</v>
       </c>
       <c r="P82" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="83" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -10443,10 +10446,10 @@
         <v>694</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>1529</v>
+        <v>1517</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>1530</v>
+        <v>1518</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>695</v>
@@ -10476,7 +10479,7 @@
         <v>698</v>
       </c>
       <c r="P83" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="84" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -10493,10 +10496,10 @@
         <v>700</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>1531</v>
+        <v>1519</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>1532</v>
+        <v>1520</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>701</v>
@@ -10543,10 +10546,10 @@
         <v>709</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>1533</v>
+        <v>1521</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>1534</v>
+        <v>1522</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>710</v>
@@ -10576,7 +10579,7 @@
         <v>714</v>
       </c>
       <c r="P85" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="86" spans="1:16" ht="409.5" x14ac:dyDescent="0.25">
@@ -10593,10 +10596,10 @@
         <v>716</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>1535</v>
+        <v>1523</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>1536</v>
+        <v>1524</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>717</v>
@@ -10626,7 +10629,7 @@
         <v>721</v>
       </c>
       <c r="P86" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="87" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -10643,10 +10646,10 @@
         <v>723</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>1537</v>
+        <v>1525</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>1538</v>
+        <v>1526</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>724</v>
@@ -10676,7 +10679,7 @@
         <v>728</v>
       </c>
       <c r="P87" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="88" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -10693,13 +10696,13 @@
         <v>731</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>1539</v>
+        <v>1527</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>1540</v>
+        <v>1528</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>1346</v>
+        <v>1334</v>
       </c>
       <c r="H88" s="1" t="s">
         <v>732</v>
@@ -10726,7 +10729,7 @@
         <v>739</v>
       </c>
       <c r="P88" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="89" spans="1:16" ht="252" x14ac:dyDescent="0.25">
@@ -10743,13 +10746,13 @@
         <v>741</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>1320</v>
+        <v>1308</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>1541</v>
+        <v>1529</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>1323</v>
+        <v>1311</v>
       </c>
       <c r="H89" s="1" t="s">
         <v>732</v>
@@ -10764,7 +10767,7 @@
         <v>743</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>1322</v>
+        <v>1310</v>
       </c>
       <c r="M89" s="1" t="s">
         <v>737</v>
@@ -10776,7 +10779,7 @@
         <v>745</v>
       </c>
       <c r="P89" s="1" t="s">
-        <v>1321</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="90" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -10793,10 +10796,10 @@
         <v>747</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>1542</v>
+        <v>1530</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>1543</v>
+        <v>1531</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>742</v>
@@ -10826,7 +10829,7 @@
         <v>751</v>
       </c>
       <c r="P90" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="91" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -10843,13 +10846,13 @@
         <v>753</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>1544</v>
+        <v>1532</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>1545</v>
+        <v>1533</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>1347</v>
+        <v>1335</v>
       </c>
       <c r="H91" s="1" t="s">
         <v>732</v>
@@ -10876,7 +10879,7 @@
         <v>757</v>
       </c>
       <c r="P91" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="92" spans="1:16" ht="252" x14ac:dyDescent="0.25">
@@ -10893,10 +10896,10 @@
         <v>759</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>1546</v>
+        <v>1534</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>1547</v>
+        <v>1535</v>
       </c>
       <c r="G92" s="1" t="s">
         <v>760</v>
@@ -10943,10 +10946,10 @@
         <v>765</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>1548</v>
+        <v>1536</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>1549</v>
+        <v>1537</v>
       </c>
       <c r="G93" s="1" t="s">
         <v>766</v>
@@ -10993,13 +10996,13 @@
         <v>772</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>1324</v>
+        <v>1312</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>1550</v>
+        <v>1538</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>1326</v>
+        <v>1314</v>
       </c>
       <c r="H94" s="1" t="s">
         <v>773</v>
@@ -11014,7 +11017,7 @@
         <v>774</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>1325</v>
+        <v>1313</v>
       </c>
       <c r="M94" s="1" t="s">
         <v>737</v>
@@ -11026,7 +11029,7 @@
         <v>775</v>
       </c>
       <c r="P94" s="1" t="s">
-        <v>1321</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="95" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -11043,10 +11046,10 @@
         <v>777</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>1551</v>
+        <v>1539</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>1552</v>
+        <v>1540</v>
       </c>
       <c r="G95" s="1" t="s">
         <v>778</v>
@@ -11093,10 +11096,10 @@
         <v>784</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>1348</v>
+        <v>1336</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>1553</v>
+        <v>1541</v>
       </c>
       <c r="G96" s="1" t="s">
         <v>785</v>
@@ -11126,7 +11129,7 @@
         <v>789</v>
       </c>
       <c r="P96" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="97" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -11143,10 +11146,10 @@
         <v>791</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>1349</v>
+        <v>1337</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>1554</v>
+        <v>1542</v>
       </c>
       <c r="G97" s="1" t="s">
         <v>792</v>
@@ -11176,7 +11179,7 @@
         <v>794</v>
       </c>
       <c r="P97" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="98" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -11193,10 +11196,10 @@
         <v>796</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>1350</v>
+        <v>1338</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>1555</v>
+        <v>1543</v>
       </c>
       <c r="G98" s="1" t="s">
         <v>797</v>
@@ -11226,7 +11229,7 @@
         <v>800</v>
       </c>
       <c r="P98" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="99" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -11246,7 +11249,7 @@
         <v>803</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>1556</v>
+        <v>1544</v>
       </c>
       <c r="G99" s="1" t="s">
         <v>804</v>
@@ -11293,10 +11296,10 @@
         <v>809</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>1557</v>
+        <v>1545</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>1558</v>
+        <v>1546</v>
       </c>
       <c r="G100" s="1" t="s">
         <v>810</v>
@@ -11343,10 +11346,10 @@
         <v>817</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>1351</v>
+        <v>1339</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>1559</v>
+        <v>1547</v>
       </c>
       <c r="G101" s="1" t="s">
         <v>818</v>
@@ -11376,7 +11379,7 @@
         <v>825</v>
       </c>
       <c r="P101" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="102" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -11393,10 +11396,10 @@
         <v>827</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>1352</v>
+        <v>1340</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>1560</v>
+        <v>1548</v>
       </c>
       <c r="G102" s="1" t="s">
         <v>828</v>
@@ -11426,7 +11429,7 @@
         <v>834</v>
       </c>
       <c r="P102" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="103" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -11443,10 +11446,10 @@
         <v>836</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>1561</v>
+        <v>1549</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>1562</v>
+        <v>1550</v>
       </c>
       <c r="G103" s="1" t="s">
         <v>837</v>
@@ -11493,10 +11496,10 @@
         <v>842</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>1563</v>
+        <v>1551</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>1564</v>
+        <v>1552</v>
       </c>
       <c r="G104" s="1" t="s">
         <v>843</v>
@@ -11526,7 +11529,7 @@
         <v>849</v>
       </c>
       <c r="P104" s="1" t="s">
-        <v>1333</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="105" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -11543,10 +11546,10 @@
         <v>851</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>1565</v>
+        <v>1553</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>1566</v>
+        <v>1554</v>
       </c>
       <c r="G105" s="1" t="s">
         <v>852</v>
@@ -11576,7 +11579,7 @@
         <v>857</v>
       </c>
       <c r="P105" s="1" t="s">
-        <v>1333</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="106" spans="1:16" ht="204.75" x14ac:dyDescent="0.25">
@@ -11593,10 +11596,10 @@
         <v>860</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>1567</v>
+        <v>1555</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>1568</v>
+        <v>1556</v>
       </c>
       <c r="G106" s="1" t="s">
         <v>861</v>
@@ -11643,10 +11646,10 @@
         <v>870</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>1569</v>
+        <v>1557</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>1570</v>
+        <v>1558</v>
       </c>
       <c r="G107" s="1" t="s">
         <v>871</v>
@@ -11676,7 +11679,7 @@
         <v>878</v>
       </c>
       <c r="P107" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="108" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -11693,10 +11696,10 @@
         <v>880</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>1571</v>
+        <v>1559</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>1572</v>
+        <v>1560</v>
       </c>
       <c r="G108" s="1" t="s">
         <v>881</v>
@@ -11726,7 +11729,7 @@
         <v>885</v>
       </c>
       <c r="P108" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="109" spans="1:16" ht="189" x14ac:dyDescent="0.25">
@@ -11743,10 +11746,10 @@
         <v>887</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>1573</v>
+        <v>1561</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>1574</v>
+        <v>1562</v>
       </c>
       <c r="G109" s="1" t="s">
         <v>888</v>
@@ -11793,10 +11796,10 @@
         <v>893</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>1575</v>
+        <v>1563</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>1576</v>
+        <v>1564</v>
       </c>
       <c r="G110" s="1" t="s">
         <v>894</v>
@@ -11826,7 +11829,7 @@
         <v>900</v>
       </c>
       <c r="P110" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="111" spans="1:16" ht="189" x14ac:dyDescent="0.25">
@@ -11843,10 +11846,10 @@
         <v>902</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>1353</v>
+        <v>1341</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>1577</v>
+        <v>1565</v>
       </c>
       <c r="G111" s="1" t="s">
         <v>903</v>
@@ -11876,7 +11879,7 @@
         <v>907</v>
       </c>
       <c r="P111" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="112" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -11893,10 +11896,10 @@
         <v>909</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>1354</v>
+        <v>1342</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>1578</v>
+        <v>1566</v>
       </c>
       <c r="G112" s="1" t="s">
         <v>910</v>
@@ -11926,7 +11929,7 @@
         <v>914</v>
       </c>
       <c r="P112" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="113" spans="1:16" ht="204.75" x14ac:dyDescent="0.25">
@@ -11943,10 +11946,10 @@
         <v>916</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>1579</v>
+        <v>1567</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>1580</v>
+        <v>1568</v>
       </c>
       <c r="G113" s="1" t="s">
         <v>917</v>
@@ -11976,7 +11979,7 @@
         <v>922</v>
       </c>
       <c r="P113" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="114" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -11993,10 +11996,10 @@
         <v>924</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>1355</v>
+        <v>1343</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>1581</v>
+        <v>1569</v>
       </c>
       <c r="G114" s="1" t="s">
         <v>925</v>
@@ -12026,7 +12029,7 @@
         <v>930</v>
       </c>
       <c r="P114" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="115" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -12043,10 +12046,10 @@
         <v>932</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>1582</v>
+        <v>1570</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>1583</v>
+        <v>1571</v>
       </c>
       <c r="G115" s="1" t="s">
         <v>933</v>
@@ -12076,7 +12079,7 @@
         <v>939</v>
       </c>
       <c r="P115" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="116" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -12093,10 +12096,10 @@
         <v>941</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>1584</v>
+        <v>1572</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>1585</v>
+        <v>1573</v>
       </c>
       <c r="G116" s="1" t="s">
         <v>942</v>
@@ -12143,16 +12146,16 @@
         <v>948</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>1327</v>
+        <v>1315</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>1586</v>
+        <v>1574</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>1328</v>
+        <v>1316</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>1334</v>
+        <v>1322</v>
       </c>
       <c r="I117" s="1" t="s">
         <v>949</v>
@@ -12176,7 +12179,7 @@
         <v>953</v>
       </c>
       <c r="P117" s="1" t="s">
-        <v>1321</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="118" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -12193,10 +12196,10 @@
         <v>955</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>1587</v>
+        <v>1575</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>1588</v>
+        <v>1576</v>
       </c>
       <c r="G118" s="1" t="s">
         <v>956</v>
@@ -12243,10 +12246,10 @@
         <v>963</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>1356</v>
+        <v>1344</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>1589</v>
+        <v>1577</v>
       </c>
       <c r="G119" s="1" t="s">
         <v>964</v>
@@ -12276,7 +12279,7 @@
         <v>969</v>
       </c>
       <c r="P119" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="120" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -12293,10 +12296,10 @@
         <v>971</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>1357</v>
+        <v>1345</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>1590</v>
+        <v>1578</v>
       </c>
       <c r="G120" s="1" t="s">
         <v>972</v>
@@ -12326,7 +12329,7 @@
         <v>975</v>
       </c>
       <c r="P120" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="121" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -12343,10 +12346,10 @@
         <v>977</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>1358</v>
+        <v>1346</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>1591</v>
+        <v>1579</v>
       </c>
       <c r="G121" s="1" t="s">
         <v>978</v>
@@ -12376,7 +12379,7 @@
         <v>981</v>
       </c>
       <c r="P121" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="122" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -12393,10 +12396,10 @@
         <v>983</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>1592</v>
+        <v>1580</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>1593</v>
+        <v>1581</v>
       </c>
       <c r="G122" s="1" t="s">
         <v>984</v>
@@ -12426,7 +12429,7 @@
         <v>988</v>
       </c>
       <c r="P122" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="123" spans="1:16" ht="204.75" x14ac:dyDescent="0.25">
@@ -12443,10 +12446,10 @@
         <v>990</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>1594</v>
+        <v>1582</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>1595</v>
+        <v>1583</v>
       </c>
       <c r="G123" s="1" t="s">
         <v>991</v>
@@ -12476,7 +12479,7 @@
         <v>997</v>
       </c>
       <c r="P123" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="124" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -12493,10 +12496,10 @@
         <v>999</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>1596</v>
+        <v>1584</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>1597</v>
+        <v>1585</v>
       </c>
       <c r="G124" s="1" t="s">
         <v>1000</v>
@@ -12543,10 +12546,10 @@
         <v>1007</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>1598</v>
+        <v>1586</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>1599</v>
+        <v>1587</v>
       </c>
       <c r="G125" s="1" t="s">
         <v>1008</v>
@@ -12576,7 +12579,7 @@
         <v>1012</v>
       </c>
       <c r="P125" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="126" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -12596,7 +12599,7 @@
         <v>1015</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>1600</v>
+        <v>1588</v>
       </c>
       <c r="G126" s="1" t="s">
         <v>1016</v>
@@ -12643,10 +12646,10 @@
         <v>1023</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>1359</v>
+        <v>1347</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>1601</v>
+        <v>1589</v>
       </c>
       <c r="G127" s="1" t="s">
         <v>1024</v>
@@ -12664,7 +12667,7 @@
         <v>787</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>1360</v>
+        <v>1348</v>
       </c>
       <c r="M127" s="1" t="s">
         <v>866</v>
@@ -12676,7 +12679,7 @@
         <v>1027</v>
       </c>
       <c r="P127" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="128" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -12696,7 +12699,7 @@
         <v>1030</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>1602</v>
+        <v>1590</v>
       </c>
       <c r="G128" s="1" t="s">
         <v>1031</v>
@@ -12726,7 +12729,7 @@
         <v>1036</v>
       </c>
       <c r="P128" s="1" t="s">
-        <v>1333</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="129" spans="1:16" ht="204.75" x14ac:dyDescent="0.25">
@@ -12743,10 +12746,10 @@
         <v>1039</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>1361</v>
+        <v>1349</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>1603</v>
+        <v>1591</v>
       </c>
       <c r="G129" s="1" t="s">
         <v>1040</v>
@@ -12770,13 +12773,13 @@
         <v>1044</v>
       </c>
       <c r="N129" s="1" t="s">
+        <v>1658</v>
+      </c>
+      <c r="O129" s="1" t="s">
         <v>1045</v>
       </c>
-      <c r="O129" s="1" t="s">
-        <v>1046</v>
-      </c>
       <c r="P129" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="130" spans="1:16" ht="204.75" x14ac:dyDescent="0.25">
@@ -12787,46 +12790,46 @@
         <v>1037</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>1047</v>
+        <v>1647</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>1048</v>
+        <v>1648</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>1049</v>
+        <v>1649</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>1604</v>
+        <v>1650</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>1050</v>
+        <v>1651</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>1051</v>
+        <v>1652</v>
       </c>
       <c r="I130" s="1" t="s">
-        <v>1052</v>
+        <v>1653</v>
       </c>
       <c r="J130" s="1" t="s">
-        <v>1053</v>
+        <v>1654</v>
       </c>
       <c r="K130" s="1" t="s">
-        <v>630</v>
+        <v>748</v>
       </c>
       <c r="L130" s="1" t="s">
-        <v>1054</v>
+        <v>1655</v>
       </c>
       <c r="M130" s="1" t="s">
         <v>1044</v>
       </c>
       <c r="N130" s="1" t="s">
-        <v>1055</v>
+        <v>1656</v>
       </c>
       <c r="O130" s="1" t="s">
-        <v>1056</v>
+        <v>1657</v>
       </c>
       <c r="P130" s="1" t="s">
-        <v>1333</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="131" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -12837,46 +12840,46 @@
         <v>1037</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>1057</v>
+        <v>1047</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>1058</v>
+        <v>1048</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>1605</v>
+        <v>1592</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>1060</v>
+        <v>1050</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>1061</v>
+        <v>1051</v>
       </c>
       <c r="I131" s="1" t="s">
-        <v>1062</v>
+        <v>1052</v>
       </c>
       <c r="J131" s="1" t="s">
-        <v>1063</v>
+        <v>1053</v>
       </c>
       <c r="K131" s="1" t="s">
         <v>647</v>
       </c>
       <c r="L131" s="1" t="s">
-        <v>1054</v>
+        <v>1046</v>
       </c>
       <c r="M131" s="1" t="s">
         <v>1044</v>
       </c>
       <c r="N131" s="1" t="s">
-        <v>1064</v>
+        <v>1659</v>
       </c>
       <c r="O131" s="1" t="s">
-        <v>1065</v>
+        <v>1054</v>
       </c>
       <c r="P131" s="1" t="s">
-        <v>1333</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="132" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -12887,46 +12890,46 @@
         <v>1037</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>1066</v>
+        <v>1055</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>1067</v>
+        <v>1056</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>1068</v>
+        <v>1057</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>1606</v>
+        <v>1593</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>1069</v>
+        <v>1058</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>1070</v>
+        <v>1059</v>
       </c>
       <c r="I132" s="1" t="s">
-        <v>1071</v>
+        <v>1060</v>
       </c>
       <c r="J132" s="1" t="s">
-        <v>1072</v>
+        <v>1061</v>
       </c>
       <c r="K132" s="1" t="s">
         <v>754</v>
       </c>
       <c r="L132" s="1" t="s">
-        <v>1073</v>
+        <v>1062</v>
       </c>
       <c r="M132" s="1" t="s">
         <v>1044</v>
       </c>
       <c r="N132" s="1" t="s">
-        <v>1074</v>
+        <v>1660</v>
       </c>
       <c r="O132" s="1" t="s">
-        <v>1075</v>
+        <v>1063</v>
       </c>
       <c r="P132" s="1" t="s">
-        <v>1333</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="133" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -12937,46 +12940,46 @@
         <v>1037</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>1076</v>
+        <v>1064</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>1077</v>
+        <v>1065</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>1078</v>
+        <v>1066</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>1607</v>
+        <v>1594</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>1079</v>
+        <v>1067</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>1080</v>
+        <v>1068</v>
       </c>
       <c r="I133" s="1" t="s">
-        <v>1081</v>
+        <v>1069</v>
       </c>
       <c r="J133" s="1" t="s">
-        <v>1082</v>
+        <v>1070</v>
       </c>
       <c r="K133" s="1" t="s">
         <v>284</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>1083</v>
+        <v>1071</v>
       </c>
       <c r="M133" s="1" t="s">
         <v>1044</v>
       </c>
       <c r="N133" s="1" t="s">
-        <v>1074</v>
+        <v>1660</v>
       </c>
       <c r="O133" s="1" t="s">
-        <v>1084</v>
+        <v>1072</v>
       </c>
       <c r="P133" s="1" t="s">
-        <v>1333</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="134" spans="1:16" ht="409.5" x14ac:dyDescent="0.25">
@@ -12984,46 +12987,46 @@
         <v>133</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>1085</v>
+        <v>1073</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>1086</v>
+        <v>1074</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>1087</v>
+        <v>1075</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>1608</v>
+        <v>1595</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>1609</v>
+        <v>1596</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>1088</v>
+        <v>1076</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>1089</v>
+        <v>1077</v>
       </c>
       <c r="I134" s="1" t="s">
-        <v>1090</v>
+        <v>1078</v>
       </c>
       <c r="J134" s="1" t="s">
-        <v>1091</v>
+        <v>1079</v>
       </c>
       <c r="K134" s="1" t="s">
         <v>53</v>
       </c>
       <c r="L134" s="1" t="s">
-        <v>1092</v>
+        <v>1080</v>
       </c>
       <c r="M134" s="1" t="s">
-        <v>1093</v>
+        <v>1081</v>
       </c>
       <c r="N134" s="1" t="s">
-        <v>1657</v>
+        <v>1644</v>
       </c>
       <c r="O134" s="1" t="s">
-        <v>1094</v>
+        <v>1082</v>
       </c>
       <c r="P134" s="1" t="s">
         <v>28</v>
@@ -13034,46 +13037,46 @@
         <v>134</v>
       </c>
       <c r="B135" s="1" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>1642</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>1597</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>1598</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>1084</v>
+      </c>
+      <c r="H135" s="1" t="s">
         <v>1085</v>
       </c>
-      <c r="C135" s="1" t="s">
-        <v>1655</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>1095</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>1610</v>
-      </c>
-      <c r="F135" s="1" t="s">
-        <v>1611</v>
-      </c>
-      <c r="G135" s="1" t="s">
-        <v>1096</v>
-      </c>
-      <c r="H135" s="1" t="s">
-        <v>1097</v>
-      </c>
       <c r="I135" s="1" t="s">
-        <v>1098</v>
+        <v>1086</v>
       </c>
       <c r="J135" s="1" t="s">
-        <v>1091</v>
+        <v>1079</v>
       </c>
       <c r="K135" s="1" t="s">
         <v>53</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>1092</v>
+        <v>1080</v>
       </c>
       <c r="M135" s="1" t="s">
-        <v>1093</v>
+        <v>1081</v>
       </c>
       <c r="N135" s="1" t="s">
-        <v>1099</v>
+        <v>1087</v>
       </c>
       <c r="O135" s="1" t="s">
-        <v>1656</v>
+        <v>1643</v>
       </c>
       <c r="P135" s="1" t="s">
         <v>28</v>
@@ -13084,49 +13087,49 @@
         <v>135</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>1085</v>
+        <v>1073</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>1100</v>
+        <v>1088</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>1101</v>
+        <v>1089</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>1612</v>
+        <v>1599</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>1613</v>
+        <v>1600</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>1102</v>
+        <v>1090</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>1103</v>
+        <v>1091</v>
       </c>
       <c r="I136" s="1" t="s">
-        <v>1104</v>
+        <v>1092</v>
       </c>
       <c r="J136" s="1" t="s">
-        <v>1105</v>
+        <v>1093</v>
       </c>
       <c r="K136" s="1" t="s">
-        <v>1106</v>
+        <v>1094</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>1092</v>
+        <v>1080</v>
       </c>
       <c r="M136" s="1" t="s">
-        <v>1093</v>
+        <v>1081</v>
       </c>
       <c r="N136" s="1" t="s">
-        <v>1658</v>
+        <v>1645</v>
       </c>
       <c r="O136" s="1" t="s">
-        <v>1107</v>
+        <v>1095</v>
       </c>
       <c r="P136" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="137" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -13134,46 +13137,46 @@
         <v>136</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>1085</v>
+        <v>1073</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>1108</v>
+        <v>1096</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>1109</v>
+        <v>1097</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>1110</v>
+        <v>1098</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>1614</v>
+        <v>1601</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>1111</v>
+        <v>1099</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>1112</v>
+        <v>1100</v>
       </c>
       <c r="I137" s="1" t="s">
-        <v>1113</v>
+        <v>1101</v>
       </c>
       <c r="J137" s="1" t="s">
-        <v>1114</v>
+        <v>1102</v>
       </c>
       <c r="K137" s="1" t="s">
         <v>875</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>1115</v>
+        <v>1103</v>
       </c>
       <c r="M137" s="1" t="s">
-        <v>1093</v>
+        <v>1081</v>
       </c>
       <c r="N137" s="1" t="s">
-        <v>1659</v>
+        <v>1646</v>
       </c>
       <c r="O137" s="1" t="s">
-        <v>1116</v>
+        <v>1104</v>
       </c>
       <c r="P137" s="1" t="s">
         <v>28</v>
@@ -13184,46 +13187,46 @@
         <v>137</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>1085</v>
+        <v>1073</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>1117</v>
+        <v>1105</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>1118</v>
+        <v>1106</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>1119</v>
+        <v>1107</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>1615</v>
+        <v>1602</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>1120</v>
+        <v>1108</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>1121</v>
+        <v>1109</v>
       </c>
       <c r="I138" s="1" t="s">
-        <v>1122</v>
+        <v>1110</v>
       </c>
       <c r="J138" s="1" t="s">
-        <v>1123</v>
+        <v>1111</v>
       </c>
       <c r="K138" s="1" t="s">
-        <v>1124</v>
+        <v>1112</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>1125</v>
+        <v>1113</v>
       </c>
       <c r="M138" s="1" t="s">
-        <v>1093</v>
+        <v>1081</v>
       </c>
       <c r="N138" s="1" t="s">
-        <v>1659</v>
+        <v>1646</v>
       </c>
       <c r="O138" s="1" t="s">
-        <v>1126</v>
+        <v>1114</v>
       </c>
       <c r="P138" s="1" t="s">
         <v>28</v>
@@ -13234,46 +13237,46 @@
         <v>138</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>1085</v>
+        <v>1073</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>1127</v>
+        <v>1115</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>1128</v>
+        <v>1116</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>1616</v>
+        <v>1603</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>1617</v>
+        <v>1604</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>1129</v>
+        <v>1117</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>1130</v>
+        <v>1118</v>
       </c>
       <c r="I139" s="1" t="s">
-        <v>1131</v>
+        <v>1119</v>
       </c>
       <c r="J139" s="1" t="s">
-        <v>1132</v>
+        <v>1120</v>
       </c>
       <c r="K139" s="1" t="s">
         <v>774</v>
       </c>
       <c r="L139" s="1" t="s">
-        <v>1125</v>
+        <v>1113</v>
       </c>
       <c r="M139" s="1" t="s">
-        <v>1093</v>
+        <v>1081</v>
       </c>
       <c r="N139" s="1" t="s">
-        <v>1659</v>
+        <v>1646</v>
       </c>
       <c r="O139" s="1" t="s">
-        <v>1133</v>
+        <v>1121</v>
       </c>
       <c r="P139" s="1" t="s">
         <v>28</v>
@@ -13284,46 +13287,46 @@
         <v>139</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>1085</v>
+        <v>1073</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>1134</v>
+        <v>1122</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>1135</v>
+        <v>1123</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>1618</v>
+        <v>1605</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>1619</v>
+        <v>1606</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>1136</v>
+        <v>1124</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>1137</v>
+        <v>1125</v>
       </c>
       <c r="I140" s="1" t="s">
-        <v>1138</v>
+        <v>1126</v>
       </c>
       <c r="J140" s="1" t="s">
-        <v>1139</v>
+        <v>1127</v>
       </c>
       <c r="K140" s="1" t="s">
         <v>147</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>1140</v>
+        <v>1128</v>
       </c>
       <c r="M140" s="1" t="s">
-        <v>1093</v>
+        <v>1081</v>
       </c>
       <c r="N140" s="1" t="s">
-        <v>1659</v>
+        <v>1646</v>
       </c>
       <c r="O140" s="1" t="s">
-        <v>1141</v>
+        <v>1129</v>
       </c>
       <c r="P140" s="1" t="s">
         <v>28</v>
@@ -13334,49 +13337,49 @@
         <v>140</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>1142</v>
+        <v>1130</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>1143</v>
+        <v>1131</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>1144</v>
+        <v>1132</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>1362</v>
+        <v>1350</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>1620</v>
+        <v>1607</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>1145</v>
+        <v>1133</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>1146</v>
+        <v>1134</v>
       </c>
       <c r="I141" s="1" t="s">
-        <v>1147</v>
+        <v>1135</v>
       </c>
       <c r="J141" s="1" t="s">
-        <v>1148</v>
+        <v>1136</v>
       </c>
       <c r="K141" s="1" t="s">
         <v>875</v>
       </c>
       <c r="L141" s="1" t="s">
-        <v>1149</v>
+        <v>1137</v>
       </c>
       <c r="M141" s="1" t="s">
-        <v>1150</v>
+        <v>1138</v>
       </c>
       <c r="N141" s="1" t="s">
-        <v>1151</v>
+        <v>1139</v>
       </c>
       <c r="O141" s="1" t="s">
-        <v>1152</v>
+        <v>1140</v>
       </c>
       <c r="P141" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="142" spans="1:16" ht="204.75" x14ac:dyDescent="0.25">
@@ -13384,49 +13387,49 @@
         <v>141</v>
       </c>
       <c r="B142" s="1" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D142" s="1" t="s">
         <v>1142</v>
       </c>
-      <c r="C142" s="1" t="s">
-        <v>1153</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>1154</v>
-      </c>
       <c r="E142" s="1" t="s">
-        <v>1621</v>
+        <v>1608</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>1622</v>
+        <v>1609</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>1155</v>
+        <v>1143</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>1156</v>
+        <v>1144</v>
       </c>
       <c r="I142" s="1" t="s">
-        <v>1157</v>
+        <v>1145</v>
       </c>
       <c r="J142" s="1" t="s">
-        <v>1158</v>
+        <v>1146</v>
       </c>
       <c r="K142" s="1" t="s">
         <v>186</v>
       </c>
       <c r="L142" s="1" t="s">
-        <v>1159</v>
+        <v>1147</v>
       </c>
       <c r="M142" s="1" t="s">
-        <v>1150</v>
+        <v>1138</v>
       </c>
       <c r="N142" s="1" t="s">
-        <v>1160</v>
+        <v>1148</v>
       </c>
       <c r="O142" s="1" t="s">
-        <v>1161</v>
+        <v>1149</v>
       </c>
       <c r="P142" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="143" spans="1:16" ht="204.75" x14ac:dyDescent="0.25">
@@ -13434,28 +13437,28 @@
         <v>142</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>1142</v>
+        <v>1130</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>1162</v>
+        <v>1150</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>1163</v>
+        <v>1151</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>1623</v>
+        <v>1610</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>1624</v>
+        <v>1611</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>1164</v>
+        <v>1152</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>1165</v>
+        <v>1153</v>
       </c>
       <c r="I143" s="1" t="s">
-        <v>1166</v>
+        <v>1154</v>
       </c>
       <c r="J143" s="1" t="s">
         <v>897</v>
@@ -13464,16 +13467,16 @@
         <v>265</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>1167</v>
+        <v>1155</v>
       </c>
       <c r="M143" s="1" t="s">
-        <v>1150</v>
+        <v>1138</v>
       </c>
       <c r="N143" s="1" t="s">
-        <v>1168</v>
+        <v>1156</v>
       </c>
       <c r="O143" s="1" t="s">
-        <v>1169</v>
+        <v>1157</v>
       </c>
       <c r="P143" s="1" t="s">
         <v>28</v>
@@ -13484,46 +13487,46 @@
         <v>143</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>1142</v>
+        <v>1130</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>1170</v>
+        <v>1158</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>1171</v>
+        <v>1159</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>1625</v>
+        <v>1612</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>1626</v>
+        <v>1613</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>1172</v>
+        <v>1160</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>1173</v>
+        <v>1161</v>
       </c>
       <c r="I144" s="1" t="s">
-        <v>1174</v>
+        <v>1162</v>
       </c>
       <c r="J144" s="1" t="s">
-        <v>1175</v>
+        <v>1163</v>
       </c>
       <c r="K144" s="1" t="s">
         <v>331</v>
       </c>
       <c r="L144" s="1" t="s">
-        <v>1176</v>
+        <v>1164</v>
       </c>
       <c r="M144" s="1" t="s">
-        <v>1150</v>
+        <v>1138</v>
       </c>
       <c r="N144" s="1" t="s">
-        <v>1177</v>
+        <v>1165</v>
       </c>
       <c r="O144" s="1" t="s">
-        <v>1178</v>
+        <v>1166</v>
       </c>
       <c r="P144" s="1" t="s">
         <v>28</v>
@@ -13534,49 +13537,49 @@
         <v>144</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>1142</v>
+        <v>1130</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>1179</v>
+        <v>1167</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>1180</v>
+        <v>1168</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>1363</v>
+        <v>1351</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>1627</v>
+        <v>1614</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>1181</v>
+        <v>1169</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>1182</v>
+        <v>1170</v>
       </c>
       <c r="I145" s="1" t="s">
-        <v>1157</v>
+        <v>1145</v>
       </c>
       <c r="J145" s="1" t="s">
-        <v>1183</v>
+        <v>1171</v>
       </c>
       <c r="K145" s="1" t="s">
         <v>147</v>
       </c>
       <c r="L145" s="1" t="s">
-        <v>1184</v>
+        <v>1172</v>
       </c>
       <c r="M145" s="1" t="s">
-        <v>1150</v>
+        <v>1138</v>
       </c>
       <c r="N145" s="1" t="s">
-        <v>1177</v>
+        <v>1165</v>
       </c>
       <c r="O145" s="1" t="s">
-        <v>1185</v>
+        <v>1173</v>
       </c>
       <c r="P145" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="146" spans="1:16" ht="204.75" x14ac:dyDescent="0.25">
@@ -13584,49 +13587,49 @@
         <v>145</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>1142</v>
+        <v>1130</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>1186</v>
+        <v>1174</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>1187</v>
+        <v>1175</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>1628</v>
+        <v>1615</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>1629</v>
+        <v>1616</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>1188</v>
+        <v>1176</v>
       </c>
       <c r="H146" s="1" t="s">
-        <v>1189</v>
+        <v>1177</v>
       </c>
       <c r="I146" s="1" t="s">
-        <v>1157</v>
+        <v>1145</v>
       </c>
       <c r="J146" s="1" t="s">
-        <v>1183</v>
+        <v>1171</v>
       </c>
       <c r="K146" s="1" t="s">
         <v>875</v>
       </c>
       <c r="L146" s="1" t="s">
-        <v>1190</v>
+        <v>1178</v>
       </c>
       <c r="M146" s="1" t="s">
-        <v>1150</v>
+        <v>1138</v>
       </c>
       <c r="N146" s="1" t="s">
-        <v>1177</v>
+        <v>1165</v>
       </c>
       <c r="O146" s="1" t="s">
-        <v>1191</v>
+        <v>1179</v>
       </c>
       <c r="P146" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="147" spans="1:16" ht="252" x14ac:dyDescent="0.25">
@@ -13634,49 +13637,49 @@
         <v>146</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>1192</v>
+        <v>1180</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>1193</v>
+        <v>1181</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>1194</v>
+        <v>1182</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>1364</v>
+        <v>1352</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>1630</v>
+        <v>1617</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>1195</v>
+        <v>1183</v>
       </c>
       <c r="H147" s="1" t="s">
-        <v>1196</v>
+        <v>1184</v>
       </c>
       <c r="I147" s="1" t="s">
-        <v>1197</v>
+        <v>1185</v>
       </c>
       <c r="J147" s="1" t="s">
-        <v>1198</v>
+        <v>1186</v>
       </c>
       <c r="K147" s="1" t="s">
-        <v>1199</v>
+        <v>1187</v>
       </c>
       <c r="L147" s="1" t="s">
-        <v>1200</v>
+        <v>1188</v>
       </c>
       <c r="M147" s="1" t="s">
-        <v>1201</v>
+        <v>1189</v>
       </c>
       <c r="N147" s="1" t="s">
-        <v>1202</v>
+        <v>1190</v>
       </c>
       <c r="O147" s="1" t="s">
-        <v>1203</v>
+        <v>1191</v>
       </c>
       <c r="P147" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="148" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -13684,49 +13687,49 @@
         <v>147</v>
       </c>
       <c r="B148" s="1" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C148" s="1" t="s">
         <v>1192</v>
       </c>
-      <c r="C148" s="1" t="s">
-        <v>1204</v>
-      </c>
       <c r="D148" s="1" t="s">
-        <v>1205</v>
+        <v>1193</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>1365</v>
+        <v>1353</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>1631</v>
+        <v>1618</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>1206</v>
+        <v>1194</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>1207</v>
+        <v>1195</v>
       </c>
       <c r="I148" s="1" t="s">
-        <v>1208</v>
+        <v>1196</v>
       </c>
       <c r="J148" s="1" t="s">
+        <v>1186</v>
+      </c>
+      <c r="K148" s="1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="L148" s="1" t="s">
         <v>1198</v>
       </c>
-      <c r="K148" s="1" t="s">
-        <v>1209</v>
-      </c>
-      <c r="L148" s="1" t="s">
-        <v>1210</v>
-      </c>
       <c r="M148" s="1" t="s">
-        <v>1201</v>
+        <v>1189</v>
       </c>
       <c r="N148" s="1" t="s">
-        <v>1211</v>
+        <v>1199</v>
       </c>
       <c r="O148" s="1" t="s">
-        <v>1212</v>
+        <v>1200</v>
       </c>
       <c r="P148" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="149" spans="1:16" ht="409.5" x14ac:dyDescent="0.25">
@@ -13734,49 +13737,49 @@
         <v>148</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>1192</v>
+        <v>1180</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>1213</v>
+        <v>1201</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>1214</v>
+        <v>1202</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>1366</v>
+        <v>1354</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>1367</v>
+        <v>1355</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>1215</v>
+        <v>1203</v>
       </c>
       <c r="H149" s="1" t="s">
-        <v>1216</v>
+        <v>1204</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>1217</v>
+        <v>1205</v>
       </c>
       <c r="J149" s="1" t="s">
-        <v>1218</v>
+        <v>1206</v>
       </c>
       <c r="K149" s="1" t="s">
         <v>986</v>
       </c>
       <c r="L149" s="1" t="s">
-        <v>1219</v>
+        <v>1207</v>
       </c>
       <c r="M149" s="1" t="s">
-        <v>1201</v>
+        <v>1189</v>
       </c>
       <c r="N149" s="1" t="s">
-        <v>1220</v>
+        <v>1208</v>
       </c>
       <c r="O149" s="1" t="s">
-        <v>1221</v>
+        <v>1209</v>
       </c>
       <c r="P149" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="150" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
@@ -13784,28 +13787,28 @@
         <v>149</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>1192</v>
+        <v>1180</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>1222</v>
+        <v>1210</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>1223</v>
+        <v>1211</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>1224</v>
+        <v>1212</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>1632</v>
+        <v>1619</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>1225</v>
+        <v>1213</v>
       </c>
       <c r="H150" s="1" t="s">
-        <v>1226</v>
+        <v>1214</v>
       </c>
       <c r="I150" s="1" t="s">
-        <v>1227</v>
+        <v>1215</v>
       </c>
       <c r="J150" s="1" t="s">
         <v>994</v>
@@ -13814,16 +13817,16 @@
         <v>986</v>
       </c>
       <c r="L150" s="1" t="s">
-        <v>1228</v>
+        <v>1216</v>
       </c>
       <c r="M150" s="1" t="s">
-        <v>1201</v>
+        <v>1189</v>
       </c>
       <c r="N150" s="1" t="s">
-        <v>1229</v>
+        <v>1217</v>
       </c>
       <c r="O150" s="1" t="s">
-        <v>1230</v>
+        <v>1218</v>
       </c>
       <c r="P150" s="1" t="s">
         <v>28</v>
@@ -13834,46 +13837,46 @@
         <v>150</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>1192</v>
+        <v>1180</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>1231</v>
+        <v>1219</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>1232</v>
+        <v>1220</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>1233</v>
+        <v>1221</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>1633</v>
+        <v>1620</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>1234</v>
+        <v>1222</v>
       </c>
       <c r="H151" s="1" t="s">
-        <v>1235</v>
+        <v>1223</v>
       </c>
       <c r="I151" s="1" t="s">
-        <v>1236</v>
+        <v>1224</v>
       </c>
       <c r="J151" s="1" t="s">
-        <v>1237</v>
+        <v>1225</v>
       </c>
       <c r="K151" s="1" t="s">
-        <v>1238</v>
+        <v>1226</v>
       </c>
       <c r="L151" s="1" t="s">
-        <v>1239</v>
+        <v>1227</v>
       </c>
       <c r="M151" s="1" t="s">
-        <v>1201</v>
+        <v>1189</v>
       </c>
       <c r="N151" s="1" t="s">
-        <v>1229</v>
+        <v>1217</v>
       </c>
       <c r="O151" s="1" t="s">
-        <v>1240</v>
+        <v>1228</v>
       </c>
       <c r="P151" s="1" t="s">
         <v>28</v>
@@ -13884,46 +13887,46 @@
         <v>151</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>1192</v>
+        <v>1180</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>1241</v>
+        <v>1229</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>1242</v>
+        <v>1230</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>1634</v>
+        <v>1621</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>1635</v>
+        <v>1622</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>1243</v>
+        <v>1231</v>
       </c>
       <c r="H152" s="1" t="s">
-        <v>1244</v>
+        <v>1232</v>
       </c>
       <c r="I152" s="1" t="s">
-        <v>1245</v>
+        <v>1233</v>
       </c>
       <c r="J152" s="1" t="s">
-        <v>1246</v>
+        <v>1234</v>
       </c>
       <c r="K152" s="1" t="s">
         <v>630</v>
       </c>
       <c r="L152" s="1" t="s">
-        <v>1247</v>
+        <v>1235</v>
       </c>
       <c r="M152" s="1" t="s">
-        <v>1201</v>
+        <v>1189</v>
       </c>
       <c r="N152" s="1" t="s">
-        <v>1229</v>
+        <v>1217</v>
       </c>
       <c r="O152" s="1" t="s">
-        <v>1248</v>
+        <v>1236</v>
       </c>
       <c r="P152" s="1" t="s">
         <v>28</v>
@@ -13934,49 +13937,49 @@
         <v>152</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>1192</v>
+        <v>1180</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>1249</v>
+        <v>1237</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>1250</v>
+        <v>1238</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>1335</v>
+        <v>1323</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>1636</v>
+        <v>1623</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>1336</v>
+        <v>1324</v>
       </c>
       <c r="H153" s="1" t="s">
-        <v>1251</v>
+        <v>1239</v>
       </c>
       <c r="I153" s="1" t="s">
-        <v>1330</v>
+        <v>1318</v>
       </c>
       <c r="J153" s="1" t="s">
-        <v>1329</v>
+        <v>1317</v>
       </c>
       <c r="K153" s="1" t="s">
-        <v>1199</v>
+        <v>1187</v>
       </c>
       <c r="L153" s="1" t="s">
-        <v>1252</v>
+        <v>1240</v>
       </c>
       <c r="M153" s="1" t="s">
-        <v>1201</v>
+        <v>1189</v>
       </c>
       <c r="N153" s="1" t="s">
-        <v>1229</v>
+        <v>1217</v>
       </c>
       <c r="O153" s="1" t="s">
-        <v>1253</v>
+        <v>1241</v>
       </c>
       <c r="P153" s="1" t="s">
-        <v>1321</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="154" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -13984,46 +13987,46 @@
         <v>153</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>1192</v>
+        <v>1180</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>1254</v>
+        <v>1242</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>1255</v>
+        <v>1243</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>1637</v>
+        <v>1624</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>1638</v>
+        <v>1625</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>1256</v>
+        <v>1244</v>
       </c>
       <c r="H154" s="1" t="s">
-        <v>1257</v>
+        <v>1245</v>
       </c>
       <c r="I154" s="1" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="J154" s="1" t="s">
-        <v>1259</v>
+        <v>1247</v>
       </c>
       <c r="K154" s="1" t="s">
-        <v>1260</v>
+        <v>1248</v>
       </c>
       <c r="L154" s="1" t="s">
         <v>1035</v>
       </c>
       <c r="M154" s="1" t="s">
-        <v>1201</v>
+        <v>1189</v>
       </c>
       <c r="N154" s="1" t="s">
-        <v>1229</v>
+        <v>1217</v>
       </c>
       <c r="O154" s="1" t="s">
-        <v>1261</v>
+        <v>1249</v>
       </c>
       <c r="P154" s="1" t="s">
         <v>28</v>
@@ -14034,46 +14037,46 @@
         <v>154</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>1192</v>
+        <v>1180</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>1262</v>
+        <v>1250</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>1263</v>
+        <v>1251</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>1639</v>
+        <v>1626</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>1640</v>
+        <v>1627</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>1264</v>
+        <v>1252</v>
       </c>
       <c r="H155" s="1" t="s">
-        <v>1265</v>
+        <v>1253</v>
       </c>
       <c r="I155" s="1" t="s">
-        <v>1266</v>
+        <v>1254</v>
       </c>
       <c r="J155" s="1" t="s">
-        <v>1267</v>
+        <v>1255</v>
       </c>
       <c r="K155" s="1" t="s">
-        <v>1268</v>
+        <v>1256</v>
       </c>
       <c r="L155" s="1" t="s">
         <v>1043</v>
       </c>
       <c r="M155" s="1" t="s">
-        <v>1201</v>
+        <v>1189</v>
       </c>
       <c r="N155" s="1" t="s">
-        <v>1229</v>
+        <v>1217</v>
       </c>
       <c r="O155" s="1" t="s">
-        <v>1269</v>
+        <v>1257</v>
       </c>
       <c r="P155" s="1" t="s">
         <v>28</v>
@@ -14084,49 +14087,49 @@
         <v>155</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>1192</v>
+        <v>1180</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>1270</v>
+        <v>1258</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>1271</v>
+        <v>1259</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>1272</v>
+        <v>1260</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>1641</v>
+        <v>1628</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>1273</v>
+        <v>1261</v>
       </c>
       <c r="H156" s="1" t="s">
-        <v>1274</v>
+        <v>1262</v>
       </c>
       <c r="I156" s="1" t="s">
-        <v>1275</v>
+        <v>1263</v>
       </c>
       <c r="J156" s="1" t="s">
-        <v>1276</v>
+        <v>1264</v>
       </c>
       <c r="K156" s="1" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="L156" s="1" t="s">
-        <v>1278</v>
+        <v>1266</v>
       </c>
       <c r="M156" s="1" t="s">
-        <v>1201</v>
+        <v>1189</v>
       </c>
       <c r="N156" s="1" t="s">
-        <v>1229</v>
+        <v>1217</v>
       </c>
       <c r="O156" s="1" t="s">
-        <v>1279</v>
+        <v>1267</v>
       </c>
       <c r="P156" s="1" t="s">
-        <v>1333</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="157" spans="1:16" ht="252" x14ac:dyDescent="0.25">
@@ -14134,46 +14137,46 @@
         <v>156</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>1280</v>
+        <v>1268</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>1281</v>
+        <v>1269</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>1282</v>
+        <v>1270</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>1642</v>
+        <v>1629</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>1643</v>
+        <v>1630</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>1283</v>
+        <v>1271</v>
       </c>
       <c r="H157" s="1" t="s">
-        <v>1284</v>
+        <v>1272</v>
       </c>
       <c r="I157" s="1" t="s">
-        <v>1285</v>
+        <v>1273</v>
       </c>
       <c r="J157" s="1" t="s">
-        <v>1286</v>
+        <v>1274</v>
       </c>
       <c r="K157" s="1" t="s">
         <v>53</v>
       </c>
       <c r="L157" s="1" t="s">
-        <v>1287</v>
+        <v>1275</v>
       </c>
       <c r="M157" s="1" t="s">
-        <v>1288</v>
+        <v>1276</v>
       </c>
       <c r="N157" s="1" t="s">
-        <v>1289</v>
+        <v>1277</v>
       </c>
       <c r="O157" s="1" t="s">
-        <v>1290</v>
+        <v>1278</v>
       </c>
       <c r="P157" s="1" t="s">
         <v>28</v>
@@ -14184,49 +14187,49 @@
         <v>157</v>
       </c>
       <c r="B158" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D158" s="1" t="s">
         <v>1280</v>
       </c>
-      <c r="C158" s="1" t="s">
-        <v>1291</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>1292</v>
-      </c>
       <c r="E158" s="1" t="s">
-        <v>1331</v>
+        <v>1319</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>1644</v>
+        <v>1631</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>1332</v>
+        <v>1320</v>
       </c>
       <c r="H158" s="1" t="s">
-        <v>1339</v>
+        <v>1327</v>
       </c>
       <c r="I158" s="1" t="s">
-        <v>1338</v>
+        <v>1326</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>1337</v>
+        <v>1325</v>
       </c>
       <c r="K158" s="1" t="s">
         <v>812</v>
       </c>
       <c r="L158" s="1" t="s">
-        <v>1293</v>
+        <v>1281</v>
       </c>
       <c r="M158" s="1" t="s">
-        <v>1288</v>
+        <v>1276</v>
       </c>
       <c r="N158" s="1" t="s">
-        <v>1294</v>
+        <v>1282</v>
       </c>
       <c r="O158" s="1" t="s">
-        <v>1295</v>
+        <v>1283</v>
       </c>
       <c r="P158" s="1" t="s">
-        <v>1321</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="159" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -14234,46 +14237,46 @@
         <v>158</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>1280</v>
+        <v>1268</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>1296</v>
+        <v>1284</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>1297</v>
+        <v>1285</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>1645</v>
+        <v>1632</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>1646</v>
+        <v>1633</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>1298</v>
+        <v>1286</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>1299</v>
+        <v>1287</v>
       </c>
       <c r="I159" s="1" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="J159" s="1" t="s">
-        <v>1286</v>
+        <v>1274</v>
       </c>
       <c r="K159" s="1" t="s">
         <v>158</v>
       </c>
       <c r="L159" s="1" t="s">
-        <v>1287</v>
+        <v>1275</v>
       </c>
       <c r="M159" s="1" t="s">
-        <v>1288</v>
+        <v>1276</v>
       </c>
       <c r="N159" s="1" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="O159" s="1" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="P159" s="1" t="s">
         <v>28</v>
@@ -14284,49 +14287,49 @@
         <v>159</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>1280</v>
+        <v>1268</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>1303</v>
+        <v>1291</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>1304</v>
+        <v>1292</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>1647</v>
+        <v>1634</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>1648</v>
+        <v>1635</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>1305</v>
+        <v>1293</v>
       </c>
       <c r="H160" s="1" t="s">
-        <v>1306</v>
+        <v>1294</v>
       </c>
       <c r="I160" s="1" t="s">
-        <v>1307</v>
+        <v>1295</v>
       </c>
       <c r="J160" s="1" t="s">
-        <v>1286</v>
+        <v>1274</v>
       </c>
       <c r="K160" s="1" t="s">
-        <v>1308</v>
+        <v>1296</v>
       </c>
       <c r="L160" s="1" t="s">
-        <v>1309</v>
+        <v>1297</v>
       </c>
       <c r="M160" s="1" t="s">
-        <v>1288</v>
+        <v>1276</v>
       </c>
       <c r="N160" s="1" t="s">
-        <v>1310</v>
+        <v>1298</v>
       </c>
       <c r="O160" s="1" t="s">
-        <v>1311</v>
+        <v>1299</v>
       </c>
       <c r="P160" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="161" spans="1:16" ht="220.5" x14ac:dyDescent="0.25">
@@ -14334,56 +14337,56 @@
         <v>160</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>1280</v>
+        <v>1268</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>1312</v>
+        <v>1300</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>1313</v>
+        <v>1301</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>1649</v>
+        <v>1636</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>1650</v>
+        <v>1637</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>1314</v>
+        <v>1302</v>
       </c>
       <c r="H161" s="1" t="s">
-        <v>1315</v>
+        <v>1303</v>
       </c>
       <c r="I161" s="1" t="s">
-        <v>1316</v>
+        <v>1304</v>
       </c>
       <c r="J161" s="1" t="s">
-        <v>1317</v>
+        <v>1305</v>
       </c>
       <c r="K161" s="1" t="s">
         <v>647</v>
       </c>
       <c r="L161" s="1" t="s">
-        <v>1318</v>
+        <v>1306</v>
       </c>
       <c r="M161" s="1" t="s">
-        <v>1288</v>
+        <v>1276</v>
       </c>
       <c r="N161" s="1" t="s">
-        <v>1310</v>
+        <v>1298</v>
       </c>
       <c r="O161" s="1" t="s">
-        <v>1319</v>
+        <v>1307</v>
       </c>
       <c r="P161" s="1" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:P161" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:P1 A93:D93 A89:D89 H89:K89 M89:O89 A95:D95 A94:D94 H94:K94 M94:O94 A118:D118 A117:D117 I117:O117 A155:D155 A153:D153 K153:O153 A159:D159 A158:D158 A74:D74 A31:D31 A106:D106 A104:D104 A105:D105 A129:D129 A128:D128 A135:B135 A130:D130 A131:D131 A132:D132 A133:D133 A157:D157 A156:D156 H153 K158:O158 A8:D8 A5:D5 H5 K5 M5:O5 A6:D6 H6 K6 M6:O6 A7:D7 H7 K7 M7:O7 A30:D30 A16:D16 H16 K16 M16:O16 A81:D81 A78:D78 H78 K78 M78:O78 A79:D79 H79 K79 M79:O79 A80:D80 H80 K80 M80:O80 A84:D84 A82:D82 H82 K82 M82:O82 A83:D83 H83 K83 M83:O83 A88:D88 A85:D85 H85 K85 M85:O85 A86:D86 H86 K86 M86:O86 A87:D87 H87 K87 M87:O87 H88 K88 M88:O88 A90:D90 H90 K90 M90:O90 A91:D91 H91 K91 M91:O91 A100:D100 A96:D96 H96 K96 M96:O96 A97:D97 H97 K97 M97:O97 A98:D98 H98 K98 M98:O98 A103:D103 A101:D101 H101 K101 M101:O101 A102:D102 H102 K102 M102:O102 A109:D109 A107:D107 H107 K107 M107:O107 A108:D108 H108 K108 M108:O108 A116:D116 A110:D110 H110 K110 M110:O110 A111:D111 H111 K111 M111:O111 A112:D112 H112 K112 M112:O112 A113:D113 H113 K113 M113:O113 A114:D114 H114 K114 M114:O114 A115:D115 H115 K115 M115:O115 A124:D124 A119:D119 H119 K119 M119:O119 A120:D120 H120 K120 M120:O120 A121:D121 H121 K121 M121:O121 A122:D122 H122 K122 M122:O122 A123:D123 H123 K123 M123:O123 A126:D126 A125:D125 H125 K125 M125:O125 A127:D127 H127 K127 M127:O127 H129 K129 M129:O129 A140:D140 A136:D136 H136 K136 M136 A144:D144 A141:D141 H141 K141 M141:O141 A142:D142 H142 K142 M142:O142 A152:D152 A145:D145 H145 K145 M145:O145 A146:D146 H146 K146 M146:O146 A147:D147 H147 K147 M147:O147 A148:D148 H148 K148 M148:O148 A149:D149 H149 K149 M149:O149 A161:D161 A160:D160 H160 K160 M160:O160 H161 K161 M161:O161 A77:D77 A75:D75 H75 K75 M75:O75 H81 K81 M81:O81 A15:D15 A9:D9 H9 K9 M9:O9 A4:D4 A2:D2 G2:P2 A3:D3 G3:P3 G4:P4 G8:P8 A10:D10 G10:P10 A11:D11 G11:P11 A12:D12 G12:P12 A13:D13 G13:P13 A14:D14 G14:P14 G15:P15 A17:D17 G17:P17 A18:D18 G18:P18 A19:D19 G19:P19 A20:D20 G20:P20 A21:D21 G21:P21 A22:D22 G22:P22 A23:D23 G23:P23 A24:D24 G24:P24 A25:D25 G25:P25 A26:D26 G26:P26 A27:D27 G27:P27 A28:D28 G28:P28 A29:D29 G29:P29 G30:P30 G31:O31 A32:D32 G32:P32 A33:D33 G33:P33 A34:D34 G34:P34 A35:D35 G35:P35 A36:D36 G36:P36 A37:D37 G37:P37 A38:D38 G38:P38 A39:D39 G39:P39 A40:D40 G40:P40 A41:D41 G41:P41 A42:D42 G42:P42 A43:D43 G43:P43 A44:B44 G44:N44 A45:D45 G45:P45 A46:B46 G46:N46 A47:D47 G47:P47 A48:D48 G48:P48 A49:D49 G49:P49 A50:D50 G50:P50 A51:D51 G51:P51 A52:D52 G52:P52 A53:D53 G53:P53 A54:D54 G54:P54 A55:D55 G55:P55 A56:D56 G56:P56 A57:D57 G57:P57 A58:D58 G58:P58 A59:D59 G59:P59 A60:D60 G60:P60 A61:D61 G61:P61 A62:D62 G62:P62 A63:D63 G63:P63 A64:D64 G64:P64 A65:D65 G65:P65 A66:D66 G66:P66 A67:D67 G67:P67 A68:D68 G68:P68 A69:D69 G69:P69 A70:D70 G70:P70 A71:D71 G71:P71 A72:D72 G72:P72 A73:D73 G73:P73 G74:P74 A76:D76 G76:P76 G77:P77 G84:P84 A92:D92 G92:P92 G93:P93 G95:P95 A99:D99 G99:P99 G100:P100 G103:P103 G104:O104 G105:O105 G106:P106 G109:P109 G116:P116 G118:P118 G124:P124 G126:P126 G128:O128 G130:O130 G131:O131 G132:O132 G133:O133 A134:D134 G134:M134 G135:N135 A137:D137 G137:M137 A138:D138 G138:M138 A139:D139 G139:M139 G140:M140 A143:D143 G143:P143 G144:P144 A150:D150 G150:P150 A151:D151 G151:P151 G152:P152 A154:D154 G154:P154 G155:P155 G156:O156 G157:P157 G159:P159 D44 P44 D46 P46 D135 P135 O134:P134 O136 O137:P137 O138:P138 O139:P139 O140:P140" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:P1 A93:D93 A89:D89 H89:K89 M89:O89 A95:D95 A94:D94 H94:K94 M94:O94 A118:D118 A117:D117 I117:O117 A155:D155 A153:D153 K153:O153 A159:D159 A158:D158 A74:D74 A31:D31 A106:D106 A104:D104 A105:D105 A129:D129 A128:D128 A135:B135 A130:B130 A131:D131 A132:D132 A133:D133 A157:D157 A156:D156 H153 K158:O158 A8:D8 A5:D5 H5 K5 M5:O5 A6:D6 H6 K6 M6:O6 A7:D7 H7 K7 M7:O7 A30:D30 A16:D16 H16 K16 M16:O16 A81:D81 A78:D78 H78 K78 M78:O78 A79:D79 H79 K79 M79:O79 A80:D80 H80 K80 M80:O80 A84:D84 A82:D82 H82 K82 M82:O82 A83:D83 H83 K83 M83:O83 A88:D88 A85:D85 H85 K85 M85:O85 A86:D86 H86 K86 M86:O86 A87:D87 H87 K87 M87:O87 H88 K88 M88:O88 A90:D90 H90 K90 M90:O90 A91:D91 H91 K91 M91:O91 A100:D100 A96:D96 H96 K96 M96:O96 A97:D97 H97 K97 M97:O97 A98:D98 H98 K98 M98:O98 A103:D103 A101:D101 H101 K101 M101:O101 A102:D102 H102 K102 M102:O102 A109:D109 A107:D107 H107 K107 M107:O107 A108:D108 H108 K108 M108:O108 A116:D116 A110:D110 H110 K110 M110:O110 A111:D111 H111 K111 M111:O111 A112:D112 H112 K112 M112:O112 A113:D113 H113 K113 M113:O113 A114:D114 H114 K114 M114:O114 A115:D115 H115 K115 M115:O115 A124:D124 A119:D119 H119 K119 M119:O119 A120:D120 H120 K120 M120:O120 A121:D121 H121 K121 M121:O121 A122:D122 H122 K122 M122:O122 A123:D123 H123 K123 M123:O123 A126:D126 A125:D125 H125 K125 M125:O125 A127:D127 H127 K127 M127:O127 H129 K129 M129 A140:D140 A136:D136 H136 K136 M136 A144:D144 A141:D141 H141 K141 M141:O141 A142:D142 H142 K142 M142:O142 A152:D152 A145:D145 H145 K145 M145:O145 A146:D146 H146 K146 M146:O146 A147:D147 H147 K147 M147:O147 A148:D148 H148 K148 M148:O148 A149:D149 H149 K149 M149:O149 A161:D161 A160:D160 H160 K160 M160:O160 H161 K161 M161:O161 A77:D77 A75:D75 H75 K75 M75:O75 H81 K81 M81:O81 A15:D15 A9:D9 H9 K9 M9:O9 A4:D4 A2:D2 G2:P2 A3:D3 G3:P3 G4:P4 G8:P8 A10:D10 G10:P10 A11:D11 G11:P11 A12:D12 G12:P12 A13:D13 G13:P13 A14:D14 G14:P14 G15:P15 A17:D17 G17:P17 A18:D18 G18:P18 A19:D19 G19:P19 A20:D20 G20:P20 A21:D21 G21:P21 A22:D22 G22:P22 A23:D23 G23:P23 A24:D24 G24:P24 A25:D25 G25:P25 A26:D26 G26:P26 A27:D27 G27:P27 A28:D28 G28:P28 A29:D29 G29:P29 G30:P30 G31:O31 A32:D32 G32:P32 A33:D33 G33:P33 A34:D34 G34:P34 A35:D35 G35:P35 A36:D36 G36:P36 A37:D37 G37:P37 A38:D38 G38:P38 A39:D39 G39:P39 A40:D40 G40:P40 A41:D41 G41:P41 A42:D42 G42:P42 A43:D43 G43:P43 A44:B44 G44:N44 A45:D45 G45:P45 A46:B46 G46:N46 A47:D47 G47:P47 A48:D48 G48:P48 A49:D49 G49:P49 A50:D50 G50:P50 A51:D51 G51:P51 A52:D52 G52:P52 A53:D53 G53:P53 A54:D54 G54:P54 A55:D55 G55:P55 A56:D56 G56:P56 A57:D57 G57:P57 A58:D58 G58:P58 A59:D59 G59:P59 A60:D60 G60:P60 A61:D61 G61:P61 A62:D62 G62:P62 A63:D63 G63:P63 A64:D64 G64:P64 A65:D65 G65:P65 A66:D66 G66:P66 A67:D67 G67:P67 A68:D68 G68:P68 A69:D69 G69:P69 A70:D70 G70:P70 A71:D71 G71:P71 A72:D72 G72:P72 A73:D73 G73:P73 G74:P74 A76:D76 G76:P76 G77:P77 G84:P84 A92:D92 G92:P92 G93:P93 G95:P95 A99:D99 G99:P99 G100:P100 G103:P103 G104:O104 G105:O105 G106:P106 G109:P109 G116:P116 G118:P118 G124:P124 G126:P126 G128:O128 G131:M131 G132:M132 G133:M133 A134:D134 G134:M134 G135:N135 A137:D137 G137:M137 A138:D138 G138:M138 A139:D139 G139:M139 G140:M140 A143:D143 G143:P143 G144:P144 A150:D150 G150:P150 A151:D151 G151:P151 G152:P152 A154:D154 G154:P154 G155:P155 G156:O156 G157:P157 G159:P159 D44 P44 D46 P46 D135 P135 O134:P134 O136 O137:P137 O138:P138 O139:P139 O140:P140 O129 O131 O132 O133" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>